--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -214,7 +214,19 @@
     <t>2025-07-05</t>
   </si>
   <si>
-    <t>5122</t>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>5504</t>
   </si>
   <si>
     <t>N14</t>
@@ -602,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -633,7 +645,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -653,7 +665,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -673,7 +685,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -693,7 +705,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -713,7 +725,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -733,7 +745,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -753,7 +765,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -773,7 +785,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -793,7 +805,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -813,7 +825,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -833,7 +845,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -853,7 +865,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -873,7 +885,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -893,7 +905,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -913,7 +925,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -933,7 +945,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -953,7 +965,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -973,7 +985,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -993,7 +1005,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1013,7 +1025,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1033,7 +1045,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1053,7 +1065,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1073,7 +1085,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1093,7 +1105,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1113,7 +1125,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1133,7 +1145,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1153,7 +1165,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1173,7 +1185,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1193,7 +1205,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1213,7 +1225,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1233,7 +1245,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1253,7 +1265,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1273,7 +1285,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1293,7 +1305,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1313,7 +1325,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1333,7 +1345,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1353,7 +1365,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1373,7 +1385,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1393,7 +1405,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1413,7 +1425,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1433,7 +1445,7 @@
         <v>1125</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D42">
         <v>94</v>
@@ -1453,7 +1465,7 @@
         <v>2106</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1473,7 +1485,7 @@
         <v>3308</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D44">
         <v>11</v>
@@ -1493,7 +1505,7 @@
         <v>5216</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1513,7 +1525,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D46">
         <v>43</v>
@@ -1533,7 +1545,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1553,7 +1565,7 @@
         <v>2525</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D48">
         <v>18</v>
@@ -1573,7 +1585,7 @@
         <v>2526</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D49">
         <v>160</v>
@@ -1593,7 +1605,7 @@
         <v>2526</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D50">
         <v>103</v>
@@ -1613,7 +1625,7 @@
         <v>4104</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D51">
         <v>66</v>
@@ -1633,7 +1645,7 @@
         <v>4311</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -1653,7 +1665,7 @@
         <v>5216</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1673,7 +1685,7 @@
         <v>1125</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -1693,7 +1705,7 @@
         <v>2526</v>
       </c>
       <c r="C55" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -1713,7 +1725,7 @@
         <v>3308</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -1733,7 +1745,7 @@
         <v>4211</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D57">
         <v>101</v>
@@ -1753,7 +1765,7 @@
         <v>5301</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D58">
         <v>115</v>
@@ -1773,7 +1785,7 @@
         <v>5436</v>
       </c>
       <c r="C59" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D59">
         <v>79</v>
@@ -1793,7 +1805,7 @@
         <v>2525</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -1813,7 +1825,7 @@
         <v>4211</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D61">
         <v>109</v>
@@ -1833,7 +1845,7 @@
         <v>5301</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -1853,7 +1865,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D63">
         <v>18</v>
@@ -1873,7 +1885,7 @@
         <v>5442</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D64">
         <v>36</v>
@@ -1893,7 +1905,7 @@
         <v>5442</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D65">
         <v>36</v>
@@ -1913,7 +1925,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D66">
         <v>63</v>
@@ -1933,7 +1945,7 @@
         <v>3302</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D67">
         <v>257</v>
@@ -1953,7 +1965,7 @@
         <v>4211</v>
       </c>
       <c r="C68" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -1973,7 +1985,7 @@
         <v>5211</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D69">
         <v>42</v>
@@ -1993,7 +2005,7 @@
         <v>5218</v>
       </c>
       <c r="C70" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D70">
         <v>102</v>
@@ -2013,7 +2025,7 @@
         <v>3493</v>
       </c>
       <c r="C71" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D71">
         <v>125</v>
@@ -2033,7 +2045,7 @@
         <v>5454</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D72">
         <v>84</v>
@@ -2053,7 +2065,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D73">
         <v>18</v>
@@ -2073,7 +2085,7 @@
         <v>3120</v>
       </c>
       <c r="C74" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D74">
         <v>229</v>
@@ -2093,7 +2105,7 @@
         <v>5211</v>
       </c>
       <c r="C75" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D75">
         <v>6</v>
@@ -2113,7 +2125,7 @@
         <v>1211</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D76">
         <v>288</v>
@@ -2133,7 +2145,7 @@
         <v>3302</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D77">
         <v>18</v>
@@ -2153,7 +2165,7 @@
         <v>2307</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D78">
         <v>36</v>
@@ -2173,7 +2185,7 @@
         <v>5218</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -2193,7 +2205,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D80">
         <v>121</v>
@@ -2213,7 +2225,7 @@
         <v>3120</v>
       </c>
       <c r="C81" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D81">
         <v>8</v>
@@ -2233,7 +2245,7 @@
         <v>3120</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -2253,7 +2265,7 @@
         <v>3493</v>
       </c>
       <c r="C83" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -2273,7 +2285,7 @@
         <v>4208</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D84">
         <v>59</v>
@@ -2293,7 +2305,7 @@
         <v>5204</v>
       </c>
       <c r="C85" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D85">
         <v>18</v>
@@ -2313,7 +2325,7 @@
         <v>2302</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D86">
         <v>86</v>
@@ -2333,7 +2345,7 @@
         <v>4208</v>
       </c>
       <c r="C87" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D87">
         <v>71</v>
@@ -2353,7 +2365,7 @@
         <v>5204</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D88">
         <v>164</v>
@@ -2373,7 +2385,7 @@
         <v>5117</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D89">
         <v>21</v>
@@ -2393,7 +2405,7 @@
         <v>5101</v>
       </c>
       <c r="C90" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D90">
         <v>221</v>
@@ -2413,7 +2425,7 @@
         <v>1221</v>
       </c>
       <c r="C91" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D91">
         <v>139</v>
@@ -2433,7 +2445,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2453,7 +2465,7 @@
         <v>2307</v>
       </c>
       <c r="C93" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D93">
         <v>8</v>
@@ -2473,7 +2485,7 @@
         <v>2307</v>
       </c>
       <c r="C94" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D94">
         <v>8</v>
@@ -2493,7 +2505,7 @@
         <v>5112</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D95">
         <v>174</v>
@@ -2513,7 +2525,7 @@
         <v>1211</v>
       </c>
       <c r="C96" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -2533,7 +2545,7 @@
         <v>2515</v>
       </c>
       <c r="C97" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D97">
         <v>128</v>
@@ -2553,7 +2565,7 @@
         <v>5101</v>
       </c>
       <c r="C98" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2573,7 +2585,7 @@
         <v>5113</v>
       </c>
       <c r="C99" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -2593,7 +2605,7 @@
         <v>5209</v>
       </c>
       <c r="C100" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D100">
         <v>163</v>
@@ -2613,7 +2625,7 @@
         <v>5448</v>
       </c>
       <c r="C101" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D101">
         <v>61</v>
@@ -2633,7 +2645,7 @@
         <v>5408</v>
       </c>
       <c r="C102" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D102">
         <v>106</v>
@@ -2653,7 +2665,7 @@
         <v>1121</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D103">
         <v>96</v>
@@ -2673,7 +2685,7 @@
         <v>2515</v>
       </c>
       <c r="C104" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2693,7 +2705,7 @@
         <v>5209</v>
       </c>
       <c r="C105" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D105">
         <v>3</v>
@@ -2713,7 +2725,7 @@
         <v>5305</v>
       </c>
       <c r="C106" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D106">
         <v>145</v>
@@ -2733,7 +2745,7 @@
         <v>5111</v>
       </c>
       <c r="C107" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D107">
         <v>45</v>
@@ -2753,7 +2765,7 @@
         <v>5122</v>
       </c>
       <c r="C108" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D108">
         <v>6</v>
@@ -2773,7 +2785,7 @@
         <v>5204</v>
       </c>
       <c r="C109" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -2793,7 +2805,7 @@
         <v>5205</v>
       </c>
       <c r="C110" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D110">
         <v>153</v>
@@ -2813,7 +2825,7 @@
         <v>5408</v>
       </c>
       <c r="C111" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -2829,11 +2841,11 @@
       <c r="A112" t="s">
         <v>65</v>
       </c>
-      <c r="B112" t="s">
-        <v>66</v>
+      <c r="B112">
+        <v>5122</v>
       </c>
       <c r="C112" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D112">
         <v>76</v>
@@ -2843,6 +2855,146 @@
       </c>
       <c r="F112">
         <v>7.487</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>66</v>
+      </c>
+      <c r="B113">
+        <v>1121</v>
+      </c>
+      <c r="C113" t="s">
+        <v>73</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113">
+        <v>14.9</v>
+      </c>
+      <c r="F113">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>66</v>
+      </c>
+      <c r="B114">
+        <v>3314</v>
+      </c>
+      <c r="C114" t="s">
+        <v>74</v>
+      </c>
+      <c r="D114">
+        <v>107</v>
+      </c>
+      <c r="E114">
+        <v>679.78</v>
+      </c>
+      <c r="F114">
+        <v>6.353</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>66</v>
+      </c>
+      <c r="B115">
+        <v>5305</v>
+      </c>
+      <c r="C115" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115">
+        <v>98</v>
+      </c>
+      <c r="E115">
+        <v>558.48</v>
+      </c>
+      <c r="F115">
+        <v>5.699</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>67</v>
+      </c>
+      <c r="B116">
+        <v>5207</v>
+      </c>
+      <c r="C116" t="s">
+        <v>73</v>
+      </c>
+      <c r="D116">
+        <v>62</v>
+      </c>
+      <c r="E116">
+        <v>410.82</v>
+      </c>
+      <c r="F116">
+        <v>6.626</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>68</v>
+      </c>
+      <c r="B117">
+        <v>5203</v>
+      </c>
+      <c r="C117" t="s">
+        <v>73</v>
+      </c>
+      <c r="D117">
+        <v>183</v>
+      </c>
+      <c r="E117">
+        <v>1264.1</v>
+      </c>
+      <c r="F117">
+        <v>6.908</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>68</v>
+      </c>
+      <c r="B118">
+        <v>5105</v>
+      </c>
+      <c r="C118" t="s">
+        <v>75</v>
+      </c>
+      <c r="D118">
+        <v>215</v>
+      </c>
+      <c r="E118">
+        <v>1493.06</v>
+      </c>
+      <c r="F118">
+        <v>6.944</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>69</v>
+      </c>
+      <c r="B119" t="s">
+        <v>70</v>
+      </c>
+      <c r="C119" t="s">
+        <v>73</v>
+      </c>
+      <c r="D119">
+        <v>75</v>
+      </c>
+      <c r="E119">
+        <v>489.96</v>
+      </c>
+      <c r="F119">
+        <v>6.533</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -226,7 +226,22 @@
     <t>2025-07-10</t>
   </si>
   <si>
-    <t>5504</t>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>5115</t>
   </si>
   <si>
     <t>N14</t>
@@ -257,6 +272,9 @@
   </si>
   <si>
     <t>N32</t>
+  </si>
+  <si>
+    <t>MIX</t>
   </si>
 </sst>
 </file>
@@ -614,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -645,7 +663,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -665,7 +683,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -685,7 +703,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -705,7 +723,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -725,7 +743,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -745,7 +763,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -765,7 +783,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -785,7 +803,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -805,7 +823,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -825,7 +843,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -845,7 +863,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -865,7 +883,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -885,7 +903,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -905,7 +923,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -925,7 +943,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -945,7 +963,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -965,7 +983,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -985,7 +1003,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1005,7 +1023,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1025,7 +1043,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1045,7 +1063,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1065,7 +1083,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1085,7 +1103,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1105,7 +1123,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1125,7 +1143,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1145,7 +1163,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1165,7 +1183,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1185,7 +1203,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1205,7 +1223,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1225,7 +1243,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1245,7 +1263,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1265,7 +1283,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1285,7 +1303,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1305,7 +1323,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1325,7 +1343,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1345,7 +1363,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1365,7 +1383,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1385,7 +1403,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1405,7 +1423,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1425,7 +1443,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1445,7 +1463,7 @@
         <v>1125</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D42">
         <v>94</v>
@@ -1465,7 +1483,7 @@
         <v>2106</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1485,7 +1503,7 @@
         <v>3308</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D44">
         <v>11</v>
@@ -1505,7 +1523,7 @@
         <v>5216</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1525,7 +1543,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D46">
         <v>43</v>
@@ -1545,7 +1563,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1565,7 +1583,7 @@
         <v>2525</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D48">
         <v>18</v>
@@ -1585,7 +1603,7 @@
         <v>2526</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D49">
         <v>160</v>
@@ -1605,7 +1623,7 @@
         <v>2526</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D50">
         <v>103</v>
@@ -1625,7 +1643,7 @@
         <v>4104</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D51">
         <v>66</v>
@@ -1645,7 +1663,7 @@
         <v>4311</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -1665,7 +1683,7 @@
         <v>5216</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1685,7 +1703,7 @@
         <v>1125</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -1705,7 +1723,7 @@
         <v>2526</v>
       </c>
       <c r="C55" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -1725,7 +1743,7 @@
         <v>3308</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -1745,7 +1763,7 @@
         <v>4211</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D57">
         <v>101</v>
@@ -1765,7 +1783,7 @@
         <v>5301</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D58">
         <v>115</v>
@@ -1785,7 +1803,7 @@
         <v>5436</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D59">
         <v>79</v>
@@ -1805,7 +1823,7 @@
         <v>2525</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -1825,7 +1843,7 @@
         <v>4211</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D61">
         <v>109</v>
@@ -1845,7 +1863,7 @@
         <v>5301</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -1865,7 +1883,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D63">
         <v>18</v>
@@ -1885,7 +1903,7 @@
         <v>5442</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D64">
         <v>36</v>
@@ -1905,7 +1923,7 @@
         <v>5442</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D65">
         <v>36</v>
@@ -1925,7 +1943,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D66">
         <v>63</v>
@@ -1945,7 +1963,7 @@
         <v>3302</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D67">
         <v>257</v>
@@ -1965,7 +1983,7 @@
         <v>4211</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -1985,7 +2003,7 @@
         <v>5211</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D69">
         <v>42</v>
@@ -2005,7 +2023,7 @@
         <v>5218</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D70">
         <v>102</v>
@@ -2025,7 +2043,7 @@
         <v>3493</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D71">
         <v>125</v>
@@ -2045,7 +2063,7 @@
         <v>5454</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D72">
         <v>84</v>
@@ -2065,7 +2083,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D73">
         <v>18</v>
@@ -2085,7 +2103,7 @@
         <v>3120</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D74">
         <v>229</v>
@@ -2105,7 +2123,7 @@
         <v>5211</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D75">
         <v>6</v>
@@ -2125,7 +2143,7 @@
         <v>1211</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D76">
         <v>288</v>
@@ -2145,7 +2163,7 @@
         <v>3302</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D77">
         <v>18</v>
@@ -2165,7 +2183,7 @@
         <v>2307</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D78">
         <v>36</v>
@@ -2185,7 +2203,7 @@
         <v>5218</v>
       </c>
       <c r="C79" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -2205,7 +2223,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D80">
         <v>121</v>
@@ -2225,7 +2243,7 @@
         <v>3120</v>
       </c>
       <c r="C81" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D81">
         <v>8</v>
@@ -2245,7 +2263,7 @@
         <v>3120</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -2265,7 +2283,7 @@
         <v>3493</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -2285,7 +2303,7 @@
         <v>4208</v>
       </c>
       <c r="C84" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D84">
         <v>59</v>
@@ -2305,7 +2323,7 @@
         <v>5204</v>
       </c>
       <c r="C85" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D85">
         <v>18</v>
@@ -2325,7 +2343,7 @@
         <v>2302</v>
       </c>
       <c r="C86" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D86">
         <v>86</v>
@@ -2345,7 +2363,7 @@
         <v>4208</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D87">
         <v>71</v>
@@ -2365,7 +2383,7 @@
         <v>5204</v>
       </c>
       <c r="C88" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D88">
         <v>164</v>
@@ -2385,7 +2403,7 @@
         <v>5117</v>
       </c>
       <c r="C89" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D89">
         <v>21</v>
@@ -2405,7 +2423,7 @@
         <v>5101</v>
       </c>
       <c r="C90" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D90">
         <v>221</v>
@@ -2425,7 +2443,7 @@
         <v>1221</v>
       </c>
       <c r="C91" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D91">
         <v>139</v>
@@ -2445,7 +2463,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2465,7 +2483,7 @@
         <v>2307</v>
       </c>
       <c r="C93" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D93">
         <v>8</v>
@@ -2485,7 +2503,7 @@
         <v>2307</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D94">
         <v>8</v>
@@ -2505,7 +2523,7 @@
         <v>5112</v>
       </c>
       <c r="C95" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D95">
         <v>174</v>
@@ -2525,7 +2543,7 @@
         <v>1211</v>
       </c>
       <c r="C96" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -2545,7 +2563,7 @@
         <v>2515</v>
       </c>
       <c r="C97" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D97">
         <v>128</v>
@@ -2565,7 +2583,7 @@
         <v>5101</v>
       </c>
       <c r="C98" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2585,7 +2603,7 @@
         <v>5113</v>
       </c>
       <c r="C99" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -2605,7 +2623,7 @@
         <v>5209</v>
       </c>
       <c r="C100" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D100">
         <v>163</v>
@@ -2625,7 +2643,7 @@
         <v>5448</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D101">
         <v>61</v>
@@ -2645,7 +2663,7 @@
         <v>5408</v>
       </c>
       <c r="C102" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D102">
         <v>106</v>
@@ -2665,7 +2683,7 @@
         <v>1121</v>
       </c>
       <c r="C103" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D103">
         <v>96</v>
@@ -2685,7 +2703,7 @@
         <v>2515</v>
       </c>
       <c r="C104" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2705,7 +2723,7 @@
         <v>5209</v>
       </c>
       <c r="C105" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D105">
         <v>3</v>
@@ -2725,7 +2743,7 @@
         <v>5305</v>
       </c>
       <c r="C106" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D106">
         <v>145</v>
@@ -2745,7 +2763,7 @@
         <v>5111</v>
       </c>
       <c r="C107" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D107">
         <v>45</v>
@@ -2765,7 +2783,7 @@
         <v>5122</v>
       </c>
       <c r="C108" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D108">
         <v>6</v>
@@ -2785,7 +2803,7 @@
         <v>5204</v>
       </c>
       <c r="C109" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -2805,7 +2823,7 @@
         <v>5205</v>
       </c>
       <c r="C110" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D110">
         <v>153</v>
@@ -2825,7 +2843,7 @@
         <v>5408</v>
       </c>
       <c r="C111" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -2845,7 +2863,7 @@
         <v>5122</v>
       </c>
       <c r="C112" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D112">
         <v>76</v>
@@ -2865,7 +2883,7 @@
         <v>1121</v>
       </c>
       <c r="C113" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -2885,7 +2903,7 @@
         <v>3314</v>
       </c>
       <c r="C114" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D114">
         <v>107</v>
@@ -2905,7 +2923,7 @@
         <v>5305</v>
       </c>
       <c r="C115" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D115">
         <v>98</v>
@@ -2925,7 +2943,7 @@
         <v>5207</v>
       </c>
       <c r="C116" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D116">
         <v>62</v>
@@ -2945,7 +2963,7 @@
         <v>5203</v>
       </c>
       <c r="C117" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D117">
         <v>183</v>
@@ -2965,7 +2983,7 @@
         <v>5105</v>
       </c>
       <c r="C118" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D118">
         <v>215</v>
@@ -2981,11 +2999,11 @@
       <c r="A119" t="s">
         <v>69</v>
       </c>
-      <c r="B119" t="s">
-        <v>70</v>
+      <c r="B119">
+        <v>5504</v>
       </c>
       <c r="C119" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D119">
         <v>75</v>
@@ -2995,6 +3013,206 @@
       </c>
       <c r="F119">
         <v>6.533</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>70</v>
+      </c>
+      <c r="B120">
+        <v>2214</v>
+      </c>
+      <c r="C120" t="s">
+        <v>86</v>
+      </c>
+      <c r="D120">
+        <v>195</v>
+      </c>
+      <c r="E120">
+        <v>1464.06</v>
+      </c>
+      <c r="F120">
+        <v>7.508</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121">
+        <v>2214</v>
+      </c>
+      <c r="C121" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121">
+        <v>80</v>
+      </c>
+      <c r="E121">
+        <v>600.76</v>
+      </c>
+      <c r="F121">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>72</v>
+      </c>
+      <c r="B122">
+        <v>2214</v>
+      </c>
+      <c r="C122" t="s">
+        <v>86</v>
+      </c>
+      <c r="D122">
+        <v>8</v>
+      </c>
+      <c r="E122">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="F122">
+        <v>8.380000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>73</v>
+      </c>
+      <c r="B123">
+        <v>2214</v>
+      </c>
+      <c r="C123" t="s">
+        <v>86</v>
+      </c>
+      <c r="D123">
+        <v>10</v>
+      </c>
+      <c r="E123">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="F123">
+        <v>6.896</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>73</v>
+      </c>
+      <c r="B124">
+        <v>3403</v>
+      </c>
+      <c r="C124" t="s">
+        <v>80</v>
+      </c>
+      <c r="D124">
+        <v>94</v>
+      </c>
+      <c r="E124">
+        <v>627.72</v>
+      </c>
+      <c r="F124">
+        <v>6.678</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>73</v>
+      </c>
+      <c r="B125">
+        <v>5115</v>
+      </c>
+      <c r="C125" t="s">
+        <v>80</v>
+      </c>
+      <c r="D125">
+        <v>33</v>
+      </c>
+      <c r="E125">
+        <v>242.14</v>
+      </c>
+      <c r="F125">
+        <v>7.338</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>73</v>
+      </c>
+      <c r="B126">
+        <v>5409</v>
+      </c>
+      <c r="C126" t="s">
+        <v>80</v>
+      </c>
+      <c r="D126">
+        <v>41</v>
+      </c>
+      <c r="E126">
+        <v>296.12</v>
+      </c>
+      <c r="F126">
+        <v>7.222</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>74</v>
+      </c>
+      <c r="B127">
+        <v>2214</v>
+      </c>
+      <c r="C127" t="s">
+        <v>86</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>9.5</v>
+      </c>
+      <c r="F127">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>74</v>
+      </c>
+      <c r="B128">
+        <v>4117</v>
+      </c>
+      <c r="C128" t="s">
+        <v>80</v>
+      </c>
+      <c r="D128">
+        <v>72</v>
+      </c>
+      <c r="E128">
+        <v>462.78</v>
+      </c>
+      <c r="F128">
+        <v>6.427</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B129" t="s">
+        <v>75</v>
+      </c>
+      <c r="C129" t="s">
+        <v>80</v>
+      </c>
+      <c r="D129">
+        <v>55</v>
+      </c>
+      <c r="E129">
+        <v>360.9</v>
+      </c>
+      <c r="F129">
+        <v>6.562</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -109,6 +109,9 @@
     <t>2025-05-25</t>
   </si>
   <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
     <t>2025-05-27</t>
   </si>
   <si>
@@ -241,7 +244,43 @@
     <t>2025-07-20</t>
   </si>
   <si>
-    <t>5115</t>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>5621</t>
   </si>
   <si>
     <t>N14</t>
@@ -632,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -663,7 +702,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -683,7 +722,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -703,7 +742,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -723,7 +762,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -743,7 +782,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -763,7 +802,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -783,7 +822,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -803,7 +842,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -823,7 +862,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -843,7 +882,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -863,7 +902,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -883,7 +922,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -903,7 +942,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -923,7 +962,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -943,7 +982,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -963,7 +1002,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -983,7 +1022,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1003,7 +1042,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1023,7 +1062,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1043,7 +1082,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1063,7 +1102,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1083,7 +1122,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1103,7 +1142,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1123,7 +1162,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1143,7 +1182,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1163,7 +1202,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1183,7 +1222,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1203,7 +1242,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1223,7 +1262,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1243,7 +1282,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1263,7 +1302,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1283,7 +1322,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1303,7 +1342,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1323,7 +1362,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1343,7 +1382,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1363,7 +1402,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1383,7 +1422,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1403,7 +1442,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1423,7 +1462,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1443,7 +1482,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1460,19 +1499,19 @@
         <v>31</v>
       </c>
       <c r="B42">
-        <v>1125</v>
+        <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D42">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="E42">
-        <v>680.3</v>
+        <v>214.54</v>
       </c>
       <c r="F42">
-        <v>7.237</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1480,59 +1519,59 @@
         <v>31</v>
       </c>
       <c r="B43">
-        <v>2106</v>
+        <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E43">
-        <v>13.98</v>
+        <v>326.34</v>
       </c>
       <c r="F43">
-        <v>6.99</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B44">
-        <v>3308</v>
+        <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="E44">
-        <v>87.72</v>
+        <v>680.3</v>
       </c>
       <c r="F44">
-        <v>7.975</v>
+        <v>7.237</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B45">
-        <v>5216</v>
+        <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45">
-        <v>12.88</v>
+        <v>13.98</v>
       </c>
       <c r="F45">
-        <v>6.44</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1543,56 +1582,56 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D46">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>290.54</v>
+        <v>87.72</v>
       </c>
       <c r="F46">
-        <v>6.757</v>
+        <v>7.975</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
-        <v>14.98</v>
+        <v>12.88</v>
       </c>
       <c r="F47">
-        <v>7.49</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48">
-        <v>2525</v>
+        <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D48">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E48">
-        <v>107</v>
+        <v>290.54</v>
       </c>
       <c r="F48">
-        <v>5.944</v>
+        <v>6.757</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1600,19 +1639,19 @@
         <v>34</v>
       </c>
       <c r="B49">
-        <v>2526</v>
+        <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D49">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>961.9400000000001</v>
+        <v>14.98</v>
       </c>
       <c r="F49">
-        <v>6.012</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1620,19 +1659,19 @@
         <v>35</v>
       </c>
       <c r="B50">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D50">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E50">
-        <v>563.96</v>
+        <v>107</v>
       </c>
       <c r="F50">
-        <v>5.475</v>
+        <v>5.944</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1640,39 +1679,39 @@
         <v>35</v>
       </c>
       <c r="B51">
-        <v>4104</v>
+        <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D51">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="E51">
-        <v>499.12</v>
+        <v>961.9400000000001</v>
       </c>
       <c r="F51">
-        <v>7.562</v>
+        <v>6.012</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52">
-        <v>4311</v>
+        <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="E52">
-        <v>14.88</v>
+        <v>563.96</v>
       </c>
       <c r="F52">
-        <v>7.44</v>
+        <v>5.475</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1680,39 +1719,39 @@
         <v>36</v>
       </c>
       <c r="B53">
-        <v>5216</v>
+        <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="E53">
-        <v>8.380000000000001</v>
+        <v>499.12</v>
       </c>
       <c r="F53">
-        <v>8.380000000000001</v>
+        <v>7.562</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54">
-        <v>1125</v>
+        <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>28.1</v>
+        <v>14.88</v>
       </c>
       <c r="F54">
-        <v>7.025</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1720,19 +1759,19 @@
         <v>37</v>
       </c>
       <c r="B55">
-        <v>2526</v>
+        <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>12.98</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F55">
-        <v>6.49</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1740,19 +1779,19 @@
         <v>38</v>
       </c>
       <c r="B56">
-        <v>3308</v>
+        <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>10.52</v>
+        <v>28.1</v>
       </c>
       <c r="F56">
-        <v>5.26</v>
+        <v>7.025</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1760,79 +1799,79 @@
         <v>38</v>
       </c>
       <c r="B57">
-        <v>4211</v>
+        <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D57">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>764.08</v>
+        <v>12.98</v>
       </c>
       <c r="F57">
-        <v>7.565</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B58">
-        <v>5301</v>
+        <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D58">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>690.5</v>
+        <v>10.52</v>
       </c>
       <c r="F58">
-        <v>6.004</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59">
-        <v>5436</v>
+        <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D59">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E59">
-        <v>577.1</v>
+        <v>764.08</v>
       </c>
       <c r="F59">
-        <v>7.305</v>
+        <v>7.565</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60">
-        <v>2525</v>
+        <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="E60">
-        <v>24.92</v>
+        <v>690.5</v>
       </c>
       <c r="F60">
-        <v>6.23</v>
+        <v>6.004</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1840,79 +1879,79 @@
         <v>39</v>
       </c>
       <c r="B61">
-        <v>4211</v>
+        <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D61">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E61">
-        <v>773.26</v>
+        <v>577.1</v>
       </c>
       <c r="F61">
-        <v>7.094</v>
+        <v>7.305</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B62">
-        <v>5301</v>
+        <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>20.06</v>
+        <v>24.92</v>
       </c>
       <c r="F62">
-        <v>6.687</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63">
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D63">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E63">
-        <v>131.48</v>
+        <v>773.26</v>
       </c>
       <c r="F63">
-        <v>7.304</v>
+        <v>7.094</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64">
-        <v>5442</v>
+        <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D64">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>218.06</v>
+        <v>20.06</v>
       </c>
       <c r="F64">
-        <v>6.057</v>
+        <v>6.687</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1920,19 +1959,19 @@
         <v>42</v>
       </c>
       <c r="B65">
-        <v>5442</v>
+        <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D65">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E65">
-        <v>218.06</v>
+        <v>131.48</v>
       </c>
       <c r="F65">
-        <v>6.057</v>
+        <v>7.304</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1943,36 +1982,36 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D66">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E66">
-        <v>383.5</v>
+        <v>218.06</v>
       </c>
       <c r="F66">
-        <v>6.087</v>
+        <v>6.057</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B67">
-        <v>3302</v>
+        <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D67">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="E67">
-        <v>1716.24</v>
+        <v>218.06</v>
       </c>
       <c r="F67">
-        <v>6.678</v>
+        <v>6.057</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1980,39 +2019,39 @@
         <v>44</v>
       </c>
       <c r="B68">
-        <v>4211</v>
+        <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E68">
-        <v>28.5</v>
+        <v>383.5</v>
       </c>
       <c r="F68">
-        <v>7.125</v>
+        <v>6.087</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69">
-        <v>5211</v>
+        <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D69">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="E69">
-        <v>303.56</v>
+        <v>1716.24</v>
       </c>
       <c r="F69">
-        <v>7.228</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2020,39 +2059,39 @@
         <v>45</v>
       </c>
       <c r="B70">
-        <v>5218</v>
+        <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D70">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="E70">
-        <v>696.0599999999999</v>
+        <v>28.5</v>
       </c>
       <c r="F70">
-        <v>6.824</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71">
-        <v>3493</v>
+        <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D71">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="E71">
-        <v>745.15</v>
+        <v>303.56</v>
       </c>
       <c r="F71">
-        <v>5.961</v>
+        <v>7.228</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2060,19 +2099,19 @@
         <v>46</v>
       </c>
       <c r="B72">
-        <v>5454</v>
+        <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D72">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E72">
-        <v>570.22</v>
+        <v>696.0599999999999</v>
       </c>
       <c r="F72">
-        <v>6.788</v>
+        <v>6.824</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2083,36 +2122,36 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="E73">
-        <v>94.22</v>
+        <v>745.15</v>
       </c>
       <c r="F73">
-        <v>5.234</v>
+        <v>5.961</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74">
-        <v>3120</v>
+        <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D74">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="E74">
-        <v>1702.44</v>
+        <v>570.22</v>
       </c>
       <c r="F74">
-        <v>7.434</v>
+        <v>6.788</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2120,19 +2159,19 @@
         <v>48</v>
       </c>
       <c r="B75">
-        <v>5211</v>
+        <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E75">
-        <v>44.36</v>
+        <v>94.22</v>
       </c>
       <c r="F75">
-        <v>7.393</v>
+        <v>5.234</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2140,19 +2179,19 @@
         <v>49</v>
       </c>
       <c r="B76">
-        <v>1211</v>
+        <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D76">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="E76">
-        <v>1742.66</v>
+        <v>1702.44</v>
       </c>
       <c r="F76">
-        <v>6.051</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2160,19 +2199,19 @@
         <v>49</v>
       </c>
       <c r="B77">
-        <v>3302</v>
+        <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D77">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E77">
-        <v>120.66</v>
+        <v>44.36</v>
       </c>
       <c r="F77">
-        <v>6.703</v>
+        <v>7.393</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2180,19 +2219,19 @@
         <v>50</v>
       </c>
       <c r="B78">
-        <v>2307</v>
+        <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D78">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="E78">
-        <v>244.56</v>
+        <v>1742.66</v>
       </c>
       <c r="F78">
-        <v>6.793</v>
+        <v>6.051</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2200,19 +2239,19 @@
         <v>50</v>
       </c>
       <c r="B79">
-        <v>5218</v>
+        <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E79">
-        <v>12.06</v>
+        <v>120.66</v>
       </c>
       <c r="F79">
-        <v>6.03</v>
+        <v>6.703</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2223,56 +2262,56 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D80">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="E80">
-        <v>761.2</v>
+        <v>244.56</v>
       </c>
       <c r="F80">
-        <v>6.291</v>
+        <v>6.793</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B81">
-        <v>3120</v>
+        <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E81">
-        <v>59.04</v>
+        <v>12.06</v>
       </c>
       <c r="F81">
-        <v>7.38</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B82">
-        <v>3120</v>
+        <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="E82">
-        <v>13.86</v>
+        <v>761.2</v>
       </c>
       <c r="F82">
-        <v>6.93</v>
+        <v>6.291</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2280,59 +2319,59 @@
         <v>53</v>
       </c>
       <c r="B83">
-        <v>3493</v>
+        <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E83">
-        <v>32.9</v>
+        <v>59.04</v>
       </c>
       <c r="F83">
-        <v>6.58</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B84">
-        <v>4208</v>
+        <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D84">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>367.58</v>
+        <v>13.86</v>
       </c>
       <c r="F84">
-        <v>6.23</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B85">
-        <v>5204</v>
+        <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D85">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E85">
-        <v>90.45999999999999</v>
+        <v>32.9</v>
       </c>
       <c r="F85">
-        <v>5.026</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2340,19 +2379,19 @@
         <v>54</v>
       </c>
       <c r="B86">
-        <v>2302</v>
+        <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D86">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E86">
-        <v>483.14</v>
+        <v>367.58</v>
       </c>
       <c r="F86">
-        <v>5.618</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2360,59 +2399,59 @@
         <v>54</v>
       </c>
       <c r="B87">
-        <v>4208</v>
+        <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D87">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E87">
-        <v>484.48</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F87">
-        <v>6.824</v>
+        <v>5.026</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B88">
-        <v>5204</v>
+        <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D88">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="E88">
-        <v>1104.02</v>
+        <v>483.14</v>
       </c>
       <c r="F88">
-        <v>6.732</v>
+        <v>5.618</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B89">
-        <v>5117</v>
+        <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D89">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="E89">
-        <v>131</v>
+        <v>484.48</v>
       </c>
       <c r="F89">
-        <v>6.238</v>
+        <v>6.824</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2420,39 +2459,39 @@
         <v>55</v>
       </c>
       <c r="B90">
-        <v>5101</v>
+        <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D90">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="E90">
-        <v>1438.98</v>
+        <v>1104.02</v>
       </c>
       <c r="F90">
-        <v>6.511</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B91">
-        <v>1221</v>
+        <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D91">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="E91">
-        <v>976.02</v>
+        <v>131</v>
       </c>
       <c r="F91">
-        <v>7.022</v>
+        <v>6.238</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2463,16 +2502,16 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="E92">
-        <v>8.08</v>
+        <v>1438.98</v>
       </c>
       <c r="F92">
-        <v>8.08</v>
+        <v>6.511</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2480,19 +2519,19 @@
         <v>57</v>
       </c>
       <c r="B93">
-        <v>2307</v>
+        <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="E93">
-        <v>55.22</v>
+        <v>976.02</v>
       </c>
       <c r="F93">
-        <v>6.902</v>
+        <v>7.022</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2500,39 +2539,39 @@
         <v>57</v>
       </c>
       <c r="B94">
-        <v>2307</v>
+        <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>55.22</v>
+        <v>8.08</v>
       </c>
       <c r="F94">
-        <v>6.902</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B95">
-        <v>5112</v>
+        <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D95">
-        <v>174</v>
+        <v>8</v>
       </c>
       <c r="E95">
-        <v>1142.96</v>
+        <v>55.22</v>
       </c>
       <c r="F95">
-        <v>6.569</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2540,19 +2579,19 @@
         <v>58</v>
       </c>
       <c r="B96">
-        <v>1211</v>
+        <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="E96">
-        <v>9.460000000000001</v>
+        <v>1142.96</v>
       </c>
       <c r="F96">
-        <v>9.460000000000001</v>
+        <v>6.569</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2560,19 +2599,19 @@
         <v>59</v>
       </c>
       <c r="B97">
-        <v>2515</v>
+        <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D97">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>834.98</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F97">
-        <v>6.523</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2580,79 +2619,79 @@
         <v>60</v>
       </c>
       <c r="B98">
-        <v>5101</v>
+        <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="E98">
-        <v>7.1</v>
+        <v>834.98</v>
       </c>
       <c r="F98">
-        <v>7.1</v>
+        <v>6.523</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B99">
-        <v>5113</v>
+        <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>19.38</v>
+        <v>7.1</v>
       </c>
       <c r="F99">
-        <v>6.46</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B100">
-        <v>5209</v>
+        <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D100">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="E100">
-        <v>1058.52</v>
+        <v>19.38</v>
       </c>
       <c r="F100">
-        <v>6.494</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B101">
-        <v>5448</v>
+        <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D101">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="E101">
-        <v>328.2</v>
+        <v>1058.52</v>
       </c>
       <c r="F101">
-        <v>5.38</v>
+        <v>6.494</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2660,19 +2699,19 @@
         <v>61</v>
       </c>
       <c r="B102">
-        <v>5408</v>
+        <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D102">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="E102">
-        <v>650.9</v>
+        <v>328.2</v>
       </c>
       <c r="F102">
-        <v>6.141</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2680,39 +2719,39 @@
         <v>62</v>
       </c>
       <c r="B103">
-        <v>1121</v>
+        <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D103">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E103">
-        <v>698.5599999999999</v>
+        <v>650.9</v>
       </c>
       <c r="F103">
-        <v>7.277</v>
+        <v>6.141</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B104">
-        <v>2515</v>
+        <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="E104">
-        <v>46.78</v>
+        <v>698.5599999999999</v>
       </c>
       <c r="F104">
-        <v>6.683</v>
+        <v>7.277</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2720,39 +2759,39 @@
         <v>63</v>
       </c>
       <c r="B105">
-        <v>5209</v>
+        <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E105">
-        <v>18.12</v>
+        <v>46.78</v>
       </c>
       <c r="F105">
-        <v>6.04</v>
+        <v>6.683</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B106">
-        <v>5305</v>
+        <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D106">
-        <v>145</v>
+        <v>3</v>
       </c>
       <c r="E106">
-        <v>871.4400000000001</v>
+        <v>18.12</v>
       </c>
       <c r="F106">
-        <v>6.01</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2760,99 +2799,99 @@
         <v>64</v>
       </c>
       <c r="B107">
-        <v>5111</v>
+        <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D107">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="E107">
-        <v>291.1</v>
+        <v>871.4400000000001</v>
       </c>
       <c r="F107">
-        <v>6.469</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B108">
-        <v>5122</v>
+        <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D108">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E108">
-        <v>35.12</v>
+        <v>291.1</v>
       </c>
       <c r="F108">
-        <v>5.853</v>
+        <v>6.469</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B109">
-        <v>5204</v>
+        <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E109">
-        <v>18</v>
+        <v>35.12</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>5.853</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B110">
-        <v>5205</v>
+        <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D110">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="E110">
-        <v>1098.6</v>
+        <v>18</v>
       </c>
       <c r="F110">
-        <v>7.18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B111">
-        <v>5408</v>
+        <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E111">
-        <v>4.72</v>
+        <v>1098.6</v>
       </c>
       <c r="F111">
-        <v>4.72</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2860,19 +2899,19 @@
         <v>65</v>
       </c>
       <c r="B112">
-        <v>5122</v>
+        <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D112">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>568.98</v>
+        <v>4.72</v>
       </c>
       <c r="F112">
-        <v>7.487</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -2880,59 +2919,59 @@
         <v>66</v>
       </c>
       <c r="B113">
-        <v>1121</v>
+        <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="E113">
-        <v>14.9</v>
+        <v>568.98</v>
       </c>
       <c r="F113">
-        <v>7.45</v>
+        <v>7.487</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B114">
-        <v>3314</v>
+        <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D114">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="E114">
-        <v>679.78</v>
+        <v>14.9</v>
       </c>
       <c r="F114">
-        <v>6.353</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B115">
-        <v>5305</v>
+        <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D115">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E115">
-        <v>558.48</v>
+        <v>679.78</v>
       </c>
       <c r="F115">
-        <v>5.699</v>
+        <v>6.353</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -2940,19 +2979,19 @@
         <v>67</v>
       </c>
       <c r="B116">
-        <v>5207</v>
+        <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D116">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E116">
-        <v>410.82</v>
+        <v>558.48</v>
       </c>
       <c r="F116">
-        <v>6.626</v>
+        <v>5.699</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2960,39 +2999,39 @@
         <v>68</v>
       </c>
       <c r="B117">
-        <v>5203</v>
+        <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D117">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="E117">
-        <v>1264.1</v>
+        <v>410.82</v>
       </c>
       <c r="F117">
-        <v>6.908</v>
+        <v>6.626</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B118">
-        <v>5105</v>
+        <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D118">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="E118">
-        <v>1493.06</v>
+        <v>1264.1</v>
       </c>
       <c r="F118">
-        <v>6.944</v>
+        <v>6.908</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3000,19 +3039,19 @@
         <v>69</v>
       </c>
       <c r="B119">
-        <v>5504</v>
+        <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D119">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="E119">
-        <v>489.96</v>
+        <v>1493.06</v>
       </c>
       <c r="F119">
-        <v>6.533</v>
+        <v>6.944</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3020,19 +3059,19 @@
         <v>70</v>
       </c>
       <c r="B120">
-        <v>2214</v>
+        <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D120">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="E120">
-        <v>1464.06</v>
+        <v>489.96</v>
       </c>
       <c r="F120">
-        <v>7.508</v>
+        <v>6.533</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3043,16 +3082,16 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D121">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="E121">
-        <v>600.76</v>
+        <v>1464.06</v>
       </c>
       <c r="F121">
-        <v>7.51</v>
+        <v>7.508</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3063,16 +3102,16 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D122">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E122">
-        <v>67.04000000000001</v>
+        <v>600.76</v>
       </c>
       <c r="F122">
-        <v>8.380000000000001</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3083,76 +3122,76 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D123">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E123">
-        <v>68.95999999999999</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="F123">
-        <v>6.896</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B124">
-        <v>3403</v>
+        <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D124">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="E124">
-        <v>627.72</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="F124">
-        <v>6.678</v>
+        <v>6.896</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B125">
-        <v>5115</v>
+        <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D125">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="E125">
-        <v>242.14</v>
+        <v>627.72</v>
       </c>
       <c r="F125">
-        <v>7.338</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B126">
-        <v>5409</v>
+        <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D126">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E126">
-        <v>296.12</v>
+        <v>242.14</v>
       </c>
       <c r="F126">
-        <v>7.222</v>
+        <v>7.338</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3160,59 +3199,639 @@
         <v>74</v>
       </c>
       <c r="B127">
-        <v>2214</v>
+        <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E127">
-        <v>9.5</v>
+        <v>296.12</v>
       </c>
       <c r="F127">
-        <v>9.5</v>
+        <v>7.222</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B128">
-        <v>4117</v>
+        <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D128">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="E128">
-        <v>462.78</v>
+        <v>9.5</v>
       </c>
       <c r="F128">
-        <v>6.427</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
+        <v>75</v>
+      </c>
+      <c r="B129">
+        <v>4117</v>
+      </c>
+      <c r="C129" t="s">
+        <v>93</v>
+      </c>
+      <c r="D129">
+        <v>72</v>
+      </c>
+      <c r="E129">
+        <v>462.78</v>
+      </c>
+      <c r="F129">
+        <v>6.427</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>75</v>
+      </c>
+      <c r="B130">
+        <v>5115</v>
+      </c>
+      <c r="C130" t="s">
+        <v>93</v>
+      </c>
+      <c r="D130">
+        <v>55</v>
+      </c>
+      <c r="E130">
+        <v>360.9</v>
+      </c>
+      <c r="F130">
+        <v>6.562</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>76</v>
+      </c>
+      <c r="B131">
+        <v>5202</v>
+      </c>
+      <c r="C131" t="s">
+        <v>94</v>
+      </c>
+      <c r="D131">
+        <v>48</v>
+      </c>
+      <c r="E131">
+        <v>261.1</v>
+      </c>
+      <c r="F131">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>77</v>
+      </c>
+      <c r="B132">
+        <v>3110</v>
+      </c>
+      <c r="C132" t="s">
+        <v>99</v>
+      </c>
+      <c r="D132">
+        <v>156</v>
+      </c>
+      <c r="E132">
+        <v>980.74</v>
+      </c>
+      <c r="F132">
+        <v>6.287</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>77</v>
+      </c>
+      <c r="B133">
+        <v>5202</v>
+      </c>
+      <c r="C133" t="s">
+        <v>94</v>
+      </c>
+      <c r="D133">
+        <v>163</v>
+      </c>
+      <c r="E133">
+        <v>1011.08</v>
+      </c>
+      <c r="F133">
+        <v>6.203</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>78</v>
+      </c>
+      <c r="B134">
+        <v>3110</v>
+      </c>
+      <c r="C134" t="s">
+        <v>93</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134">
+        <v>15.94</v>
+      </c>
+      <c r="F134">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>78</v>
+      </c>
+      <c r="B135">
+        <v>5202</v>
+      </c>
+      <c r="C135" t="s">
+        <v>94</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135">
+        <v>13.96</v>
+      </c>
+      <c r="F135">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>79</v>
+      </c>
+      <c r="B136">
+        <v>1135</v>
+      </c>
+      <c r="C136" t="s">
+        <v>99</v>
+      </c>
+      <c r="D136">
+        <v>23</v>
+      </c>
+      <c r="E136">
+        <v>132.38</v>
+      </c>
+      <c r="F136">
+        <v>5.756</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>79</v>
+      </c>
+      <c r="B137">
+        <v>4111</v>
+      </c>
+      <c r="C137" t="s">
+        <v>91</v>
+      </c>
+      <c r="D137">
+        <v>48</v>
+      </c>
+      <c r="E137">
+        <v>327.54</v>
+      </c>
+      <c r="F137">
+        <v>6.824</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>79</v>
+      </c>
+      <c r="B138">
+        <v>4117</v>
+      </c>
+      <c r="C138" t="s">
+        <v>93</v>
+      </c>
+      <c r="D138">
+        <v>3</v>
+      </c>
+      <c r="E138">
+        <v>21.78</v>
+      </c>
+      <c r="F138">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>79</v>
+      </c>
+      <c r="B139">
+        <v>5202</v>
+      </c>
+      <c r="C139" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139">
+        <v>21.76</v>
+      </c>
+      <c r="F139">
+        <v>7.253</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>79</v>
+      </c>
+      <c r="B140">
+        <v>5624</v>
+      </c>
+      <c r="C140" t="s">
+        <v>91</v>
+      </c>
+      <c r="D140">
+        <v>103</v>
+      </c>
+      <c r="E140">
+        <v>688.24</v>
+      </c>
+      <c r="F140">
+        <v>6.682</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>80</v>
+      </c>
+      <c r="B141">
+        <v>4111</v>
+      </c>
+      <c r="C141" t="s">
+        <v>91</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>9.98</v>
+      </c>
+      <c r="F141">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>80</v>
+      </c>
+      <c r="B142">
+        <v>5624</v>
+      </c>
+      <c r="C142" t="s">
+        <v>91</v>
+      </c>
+      <c r="D142">
         <v>74</v>
       </c>
-      <c r="B129" t="s">
-        <v>75</v>
-      </c>
-      <c r="C129" t="s">
-        <v>80</v>
-      </c>
-      <c r="D129">
-        <v>55</v>
-      </c>
-      <c r="E129">
-        <v>360.9</v>
-      </c>
-      <c r="F129">
-        <v>6.562</v>
+      <c r="E142">
+        <v>478.5</v>
+      </c>
+      <c r="F142">
+        <v>6.466</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>81</v>
+      </c>
+      <c r="B143">
+        <v>3110</v>
+      </c>
+      <c r="C143" t="s">
+        <v>94</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>6.28</v>
+      </c>
+      <c r="F143">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>81</v>
+      </c>
+      <c r="B144">
+        <v>4317</v>
+      </c>
+      <c r="C144" t="s">
+        <v>93</v>
+      </c>
+      <c r="D144">
+        <v>54</v>
+      </c>
+      <c r="E144">
+        <v>365.78</v>
+      </c>
+      <c r="F144">
+        <v>6.774</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>81</v>
+      </c>
+      <c r="B145">
+        <v>5601</v>
+      </c>
+      <c r="C145" t="s">
+        <v>94</v>
+      </c>
+      <c r="D145">
+        <v>85</v>
+      </c>
+      <c r="E145">
+        <v>403.56</v>
+      </c>
+      <c r="F145">
+        <v>4.748</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>82</v>
+      </c>
+      <c r="B146">
+        <v>5624</v>
+      </c>
+      <c r="C146" t="s">
+        <v>91</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146">
+        <v>16.06</v>
+      </c>
+      <c r="F146">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>83</v>
+      </c>
+      <c r="B147">
+        <v>1223</v>
+      </c>
+      <c r="C147" t="s">
+        <v>94</v>
+      </c>
+      <c r="D147">
+        <v>49</v>
+      </c>
+      <c r="E147">
+        <v>274</v>
+      </c>
+      <c r="F147">
+        <v>5.592</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>83</v>
+      </c>
+      <c r="B148">
+        <v>5601</v>
+      </c>
+      <c r="C148" t="s">
+        <v>94</v>
+      </c>
+      <c r="D148">
+        <v>34</v>
+      </c>
+      <c r="E148">
+        <v>148.04</v>
+      </c>
+      <c r="F148">
+        <v>4.354</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>83</v>
+      </c>
+      <c r="B149">
+        <v>5621</v>
+      </c>
+      <c r="C149" t="s">
+        <v>91</v>
+      </c>
+      <c r="D149">
+        <v>152</v>
+      </c>
+      <c r="E149">
+        <v>1055.94</v>
+      </c>
+      <c r="F149">
+        <v>6.947</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>84</v>
+      </c>
+      <c r="B150">
+        <v>5601</v>
+      </c>
+      <c r="C150" t="s">
+        <v>94</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>11.74</v>
+      </c>
+      <c r="F150">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>84</v>
+      </c>
+      <c r="B151">
+        <v>5621</v>
+      </c>
+      <c r="C151" t="s">
+        <v>91</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151">
+        <v>14.72</v>
+      </c>
+      <c r="F151">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>84</v>
+      </c>
+      <c r="B152">
+        <v>5664</v>
+      </c>
+      <c r="C152" t="s">
+        <v>91</v>
+      </c>
+      <c r="D152">
+        <v>3</v>
+      </c>
+      <c r="E152">
+        <v>23.58</v>
+      </c>
+      <c r="F152">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>85</v>
+      </c>
+      <c r="B153">
+        <v>3491</v>
+      </c>
+      <c r="C153" t="s">
+        <v>93</v>
+      </c>
+      <c r="D153">
+        <v>85</v>
+      </c>
+      <c r="E153">
+        <v>591.46</v>
+      </c>
+      <c r="F153">
+        <v>6.958</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>86</v>
+      </c>
+      <c r="B154">
+        <v>4317</v>
+      </c>
+      <c r="C154" t="s">
+        <v>93</v>
+      </c>
+      <c r="D154">
+        <v>8</v>
+      </c>
+      <c r="E154">
+        <v>50.8</v>
+      </c>
+      <c r="F154">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155">
+        <v>5458</v>
+      </c>
+      <c r="C155" t="s">
+        <v>91</v>
+      </c>
+      <c r="D155">
+        <v>268</v>
+      </c>
+      <c r="E155">
+        <v>1818.92</v>
+      </c>
+      <c r="F155">
+        <v>6.787</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156">
+        <v>4317</v>
+      </c>
+      <c r="C156" t="s">
+        <v>93</v>
+      </c>
+      <c r="D156">
+        <v>16</v>
+      </c>
+      <c r="E156">
+        <v>88.7</v>
+      </c>
+      <c r="F156">
+        <v>5.544</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>87</v>
+      </c>
+      <c r="B157">
+        <v>5458</v>
+      </c>
+      <c r="C157" t="s">
+        <v>91</v>
+      </c>
+      <c r="D157">
+        <v>4</v>
+      </c>
+      <c r="E157">
+        <v>31.88</v>
+      </c>
+      <c r="F157">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>87</v>
+      </c>
+      <c r="B158" t="s">
+        <v>88</v>
+      </c>
+      <c r="C158" t="s">
+        <v>91</v>
+      </c>
+      <c r="D158">
+        <v>2</v>
+      </c>
+      <c r="E158">
+        <v>12.42</v>
+      </c>
+      <c r="F158">
+        <v>6.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -280,7 +280,49 @@
     <t>2025-07-31</t>
   </si>
   <si>
-    <t>5621</t>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2025-08-02</t>
+  </si>
+  <si>
+    <t>2025-08-03</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>4412</t>
   </si>
   <si>
     <t>N14</t>
@@ -314,6 +356,9 @@
   </si>
   <si>
     <t>MIX</t>
+  </si>
+  <si>
+    <t>CO62175</t>
   </si>
 </sst>
 </file>
@@ -671,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -702,7 +747,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -722,7 +767,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -742,7 +787,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -762,7 +807,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -782,7 +827,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -802,7 +847,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -822,7 +867,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -842,7 +887,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -862,7 +907,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -882,7 +927,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -902,7 +947,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -922,7 +967,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -942,7 +987,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -962,7 +1007,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -982,7 +1027,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1002,7 +1047,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1022,7 +1067,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1042,7 +1087,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1062,7 +1107,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1082,7 +1127,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1102,7 +1147,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1122,7 +1167,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1142,7 +1187,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1162,7 +1207,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1182,7 +1227,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1202,7 +1247,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1222,7 +1267,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1242,7 +1287,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1262,7 +1307,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1282,7 +1327,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1302,7 +1347,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1322,7 +1367,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1342,7 +1387,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1362,7 +1407,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1382,7 +1427,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1402,7 +1447,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1422,7 +1467,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1442,7 +1487,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1462,7 +1507,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1482,7 +1527,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1502,7 +1547,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1522,7 +1567,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1542,7 +1587,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1562,7 +1607,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1582,7 +1627,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1602,7 +1647,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1622,7 +1667,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1642,7 +1687,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1662,7 +1707,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -1682,7 +1727,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -1702,7 +1747,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -1722,7 +1767,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -1742,7 +1787,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -1762,7 +1807,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1782,7 +1827,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1802,7 +1847,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -1822,7 +1867,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -1842,7 +1887,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -1862,7 +1907,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -1882,7 +1927,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -1902,7 +1947,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -1922,7 +1967,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -1942,7 +1987,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -1962,7 +2007,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -1982,7 +2027,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2002,7 +2047,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2022,7 +2067,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2042,7 +2087,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2062,7 +2107,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2082,7 +2127,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2102,7 +2147,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2122,7 +2167,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2142,7 +2187,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2162,7 +2207,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2182,7 +2227,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2202,7 +2247,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2222,7 +2267,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2242,7 +2287,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2262,7 +2307,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2282,7 +2327,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2302,7 +2347,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2322,7 +2367,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2342,7 +2387,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2362,7 +2407,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2382,7 +2427,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2402,7 +2447,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2422,7 +2467,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2442,7 +2487,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2462,7 +2507,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2482,7 +2527,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2502,7 +2547,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2522,7 +2567,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2542,7 +2587,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2562,7 +2607,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2582,7 +2627,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2602,7 +2647,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2622,7 +2667,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2642,7 +2687,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2662,7 +2707,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2682,7 +2727,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -2702,7 +2747,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -2722,7 +2767,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -2742,7 +2787,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -2762,7 +2807,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -2782,7 +2827,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -2802,7 +2847,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -2822,7 +2867,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -2842,7 +2887,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -2862,7 +2907,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -2882,7 +2927,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -2902,7 +2947,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -2922,7 +2967,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -2942,7 +2987,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -2962,7 +3007,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -2982,7 +3027,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3002,7 +3047,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3022,7 +3067,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3042,7 +3087,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3062,7 +3107,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3082,7 +3127,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3102,7 +3147,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3122,7 +3167,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3142,7 +3187,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3162,7 +3207,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3182,7 +3227,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3202,7 +3247,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3222,7 +3267,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3242,7 +3287,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3262,7 +3307,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3282,7 +3327,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3302,7 +3347,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3322,7 +3367,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3342,7 +3387,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3362,7 +3407,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3382,7 +3427,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3402,7 +3447,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3422,7 +3467,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3442,7 +3487,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3462,7 +3507,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3482,7 +3527,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3502,7 +3547,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3522,7 +3567,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3542,7 +3587,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3562,7 +3607,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3582,7 +3627,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3602,7 +3647,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3622,7 +3667,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3642,7 +3687,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3662,7 +3707,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3682,7 +3727,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3702,7 +3747,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -3722,7 +3767,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -3742,7 +3787,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -3762,7 +3807,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -3782,7 +3827,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -3802,7 +3847,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -3818,11 +3863,11 @@
       <c r="A158" t="s">
         <v>87</v>
       </c>
-      <c r="B158" t="s">
-        <v>88</v>
+      <c r="B158">
+        <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -3832,6 +3877,646 @@
       </c>
       <c r="F158">
         <v>6.21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>88</v>
+      </c>
+      <c r="B159">
+        <v>2220</v>
+      </c>
+      <c r="C159" t="s">
+        <v>105</v>
+      </c>
+      <c r="D159">
+        <v>96</v>
+      </c>
+      <c r="E159">
+        <v>641.16</v>
+      </c>
+      <c r="F159">
+        <v>6.679</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>88</v>
+      </c>
+      <c r="B160">
+        <v>5601</v>
+      </c>
+      <c r="C160" t="s">
+        <v>108</v>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+      <c r="E160">
+        <v>20.78</v>
+      </c>
+      <c r="F160">
+        <v>4.156</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>89</v>
+      </c>
+      <c r="B161">
+        <v>2220</v>
+      </c>
+      <c r="C161" t="s">
+        <v>105</v>
+      </c>
+      <c r="D161">
+        <v>193</v>
+      </c>
+      <c r="E161">
+        <v>1462.46</v>
+      </c>
+      <c r="F161">
+        <v>7.578</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>89</v>
+      </c>
+      <c r="B162">
+        <v>2403</v>
+      </c>
+      <c r="C162" t="s">
+        <v>108</v>
+      </c>
+      <c r="D162">
+        <v>8</v>
+      </c>
+      <c r="E162">
+        <v>25.9</v>
+      </c>
+      <c r="F162">
+        <v>3.237</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>89</v>
+      </c>
+      <c r="B163">
+        <v>5458</v>
+      </c>
+      <c r="C163" t="s">
+        <v>105</v>
+      </c>
+      <c r="D163">
+        <v>6</v>
+      </c>
+      <c r="E163">
+        <v>49.24</v>
+      </c>
+      <c r="F163">
+        <v>8.207000000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>90</v>
+      </c>
+      <c r="B164">
+        <v>2220</v>
+      </c>
+      <c r="C164" t="s">
+        <v>105</v>
+      </c>
+      <c r="D164">
+        <v>54</v>
+      </c>
+      <c r="E164">
+        <v>351.44</v>
+      </c>
+      <c r="F164">
+        <v>6.508</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>90</v>
+      </c>
+      <c r="B165">
+        <v>5601</v>
+      </c>
+      <c r="C165" t="s">
+        <v>105</v>
+      </c>
+      <c r="D165">
+        <v>4</v>
+      </c>
+      <c r="E165">
+        <v>15.72</v>
+      </c>
+      <c r="F165">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>91</v>
+      </c>
+      <c r="B166">
+        <v>2220</v>
+      </c>
+      <c r="C166" t="s">
+        <v>105</v>
+      </c>
+      <c r="D166">
+        <v>44</v>
+      </c>
+      <c r="E166">
+        <v>313.92</v>
+      </c>
+      <c r="F166">
+        <v>7.135</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>91</v>
+      </c>
+      <c r="B167">
+        <v>5662</v>
+      </c>
+      <c r="C167" t="s">
+        <v>105</v>
+      </c>
+      <c r="D167">
+        <v>89</v>
+      </c>
+      <c r="E167">
+        <v>516.64</v>
+      </c>
+      <c r="F167">
+        <v>5.805</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>92</v>
+      </c>
+      <c r="B168">
+        <v>2220</v>
+      </c>
+      <c r="C168" t="s">
+        <v>105</v>
+      </c>
+      <c r="D168">
+        <v>4</v>
+      </c>
+      <c r="E168">
+        <v>31.62</v>
+      </c>
+      <c r="F168">
+        <v>7.905</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>92</v>
+      </c>
+      <c r="B169">
+        <v>2521</v>
+      </c>
+      <c r="C169" t="s">
+        <v>108</v>
+      </c>
+      <c r="D169">
+        <v>42</v>
+      </c>
+      <c r="E169">
+        <v>230.1</v>
+      </c>
+      <c r="F169">
+        <v>5.479</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>93</v>
+      </c>
+      <c r="B170">
+        <v>2512</v>
+      </c>
+      <c r="C170" t="s">
+        <v>108</v>
+      </c>
+      <c r="D170">
+        <v>78</v>
+      </c>
+      <c r="E170">
+        <v>483.46</v>
+      </c>
+      <c r="F170">
+        <v>6.198</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>93</v>
+      </c>
+      <c r="B171">
+        <v>2514</v>
+      </c>
+      <c r="C171" t="s">
+        <v>108</v>
+      </c>
+      <c r="D171">
+        <v>18</v>
+      </c>
+      <c r="E171">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="F171">
+        <v>5.442</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>94</v>
+      </c>
+      <c r="B172">
+        <v>2514</v>
+      </c>
+      <c r="C172" t="s">
+        <v>108</v>
+      </c>
+      <c r="D172">
+        <v>155</v>
+      </c>
+      <c r="E172">
+        <v>1063.98</v>
+      </c>
+      <c r="F172">
+        <v>6.864</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>95</v>
+      </c>
+      <c r="B173">
+        <v>2512</v>
+      </c>
+      <c r="C173" t="s">
+        <v>108</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>8.34</v>
+      </c>
+      <c r="F173">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>95</v>
+      </c>
+      <c r="B174">
+        <v>3106</v>
+      </c>
+      <c r="C174" t="s">
+        <v>107</v>
+      </c>
+      <c r="D174">
+        <v>40</v>
+      </c>
+      <c r="E174">
+        <v>252.6</v>
+      </c>
+      <c r="F174">
+        <v>6.315</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>95</v>
+      </c>
+      <c r="B175">
+        <v>4240</v>
+      </c>
+      <c r="C175" t="s">
+        <v>107</v>
+      </c>
+      <c r="D175">
+        <v>37</v>
+      </c>
+      <c r="E175">
+        <v>152.6</v>
+      </c>
+      <c r="F175">
+        <v>4.124</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B176">
+        <v>5661</v>
+      </c>
+      <c r="C176" t="s">
+        <v>105</v>
+      </c>
+      <c r="D176">
+        <v>42</v>
+      </c>
+      <c r="E176">
+        <v>301.36</v>
+      </c>
+      <c r="F176">
+        <v>7.175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>96</v>
+      </c>
+      <c r="B177">
+        <v>5661</v>
+      </c>
+      <c r="C177" t="s">
+        <v>105</v>
+      </c>
+      <c r="D177">
+        <v>48</v>
+      </c>
+      <c r="E177">
+        <v>328.38</v>
+      </c>
+      <c r="F177">
+        <v>6.841</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>96</v>
+      </c>
+      <c r="B178">
+        <v>5663</v>
+      </c>
+      <c r="C178" t="s">
+        <v>105</v>
+      </c>
+      <c r="D178">
+        <v>30</v>
+      </c>
+      <c r="E178">
+        <v>186.26</v>
+      </c>
+      <c r="F178">
+        <v>6.209</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>96</v>
+      </c>
+      <c r="B179">
+        <v>5664</v>
+      </c>
+      <c r="C179" t="s">
+        <v>105</v>
+      </c>
+      <c r="D179">
+        <v>114</v>
+      </c>
+      <c r="E179">
+        <v>734.42</v>
+      </c>
+      <c r="F179">
+        <v>6.442</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>97</v>
+      </c>
+      <c r="B180">
+        <v>5663</v>
+      </c>
+      <c r="C180" t="s">
+        <v>105</v>
+      </c>
+      <c r="D180">
+        <v>114</v>
+      </c>
+      <c r="E180">
+        <v>693.86</v>
+      </c>
+      <c r="F180">
+        <v>6.086</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>97</v>
+      </c>
+      <c r="B181">
+        <v>2514</v>
+      </c>
+      <c r="C181" t="s">
+        <v>108</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>5.14</v>
+      </c>
+      <c r="F181">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>98</v>
+      </c>
+      <c r="B182">
+        <v>5208</v>
+      </c>
+      <c r="C182" t="s">
+        <v>114</v>
+      </c>
+      <c r="D182">
+        <v>66</v>
+      </c>
+      <c r="E182">
+        <v>428.16</v>
+      </c>
+      <c r="F182">
+        <v>6.487</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>99</v>
+      </c>
+      <c r="B183">
+        <v>5208</v>
+      </c>
+      <c r="C183" t="s">
+        <v>114</v>
+      </c>
+      <c r="D183">
+        <v>6</v>
+      </c>
+      <c r="E183">
+        <v>37.72</v>
+      </c>
+      <c r="F183">
+        <v>6.287</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>99</v>
+      </c>
+      <c r="B184">
+        <v>5663</v>
+      </c>
+      <c r="C184" t="s">
+        <v>105</v>
+      </c>
+      <c r="D184">
+        <v>2</v>
+      </c>
+      <c r="E184">
+        <v>12.34</v>
+      </c>
+      <c r="F184">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>99</v>
+      </c>
+      <c r="B185">
+        <v>5664</v>
+      </c>
+      <c r="C185" t="s">
+        <v>105</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>10.68</v>
+      </c>
+      <c r="F185">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>100</v>
+      </c>
+      <c r="B186">
+        <v>1107</v>
+      </c>
+      <c r="C186" t="s">
+        <v>107</v>
+      </c>
+      <c r="D186">
+        <v>161</v>
+      </c>
+      <c r="E186">
+        <v>1007.24</v>
+      </c>
+      <c r="F186">
+        <v>6.256</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>100</v>
+      </c>
+      <c r="B187">
+        <v>4240</v>
+      </c>
+      <c r="C187" t="s">
+        <v>108</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>11.38</v>
+      </c>
+      <c r="F187">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B188">
+        <v>4241</v>
+      </c>
+      <c r="C188" t="s">
+        <v>108</v>
+      </c>
+      <c r="D188">
+        <v>24</v>
+      </c>
+      <c r="E188">
+        <v>73.44</v>
+      </c>
+      <c r="F188">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>100</v>
+      </c>
+      <c r="B189">
+        <v>5208</v>
+      </c>
+      <c r="C189" t="s">
+        <v>114</v>
+      </c>
+      <c r="D189">
+        <v>10</v>
+      </c>
+      <c r="E189">
+        <v>70.02</v>
+      </c>
+      <c r="F189">
+        <v>7.002</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>101</v>
+      </c>
+      <c r="B190" t="s">
+        <v>102</v>
+      </c>
+      <c r="C190" t="s">
+        <v>107</v>
+      </c>
+      <c r="D190">
+        <v>116</v>
+      </c>
+      <c r="E190">
+        <v>668.9400000000001</v>
+      </c>
+      <c r="F190">
+        <v>5.767</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -322,7 +322,10 @@
     <t>2025-08-15</t>
   </si>
   <si>
-    <t>4412</t>
+    <t>2025-08-16</t>
+  </si>
+  <si>
+    <t>5441</t>
   </si>
   <si>
     <t>N14</t>
@@ -716,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -747,7 +750,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -767,7 +770,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -787,7 +790,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -807,7 +810,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -827,7 +830,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -847,7 +850,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -867,7 +870,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -887,7 +890,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -907,7 +910,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -927,7 +930,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -947,7 +950,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -967,7 +970,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -987,7 +990,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1007,7 +1010,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1027,7 +1030,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1047,7 +1050,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1067,7 +1070,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1087,7 +1090,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1107,7 +1110,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1127,7 +1130,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1147,7 +1150,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1167,7 +1170,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1187,7 +1190,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1207,7 +1210,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1227,7 +1230,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1247,7 +1250,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1267,7 +1270,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1287,7 +1290,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1307,7 +1310,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1327,7 +1330,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1347,7 +1350,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1367,7 +1370,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1387,7 +1390,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1407,7 +1410,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1427,7 +1430,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1447,7 +1450,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1467,7 +1470,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1487,7 +1490,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1507,7 +1510,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1527,7 +1530,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1547,7 +1550,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1567,7 +1570,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1587,7 +1590,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1607,7 +1610,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1627,7 +1630,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1647,7 +1650,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1667,7 +1670,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1687,7 +1690,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1707,7 +1710,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -1727,7 +1730,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -1747,7 +1750,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -1767,7 +1770,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -1787,7 +1790,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -1807,7 +1810,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1827,7 +1830,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1847,7 +1850,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -1867,7 +1870,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -1887,7 +1890,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -1907,7 +1910,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -1927,7 +1930,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -1947,7 +1950,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -1967,7 +1970,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -1987,7 +1990,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2007,7 +2010,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -2027,7 +2030,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2047,7 +2050,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2067,7 +2070,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2087,7 +2090,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2107,7 +2110,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2127,7 +2130,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2147,7 +2150,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2167,7 +2170,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2187,7 +2190,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2207,7 +2210,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2227,7 +2230,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2247,7 +2250,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2267,7 +2270,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2287,7 +2290,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2307,7 +2310,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2327,7 +2330,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2347,7 +2350,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2367,7 +2370,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2387,7 +2390,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2407,7 +2410,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2427,7 +2430,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2447,7 +2450,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2467,7 +2470,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2487,7 +2490,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2507,7 +2510,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2527,7 +2530,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2547,7 +2550,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2567,7 +2570,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2587,7 +2590,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2607,7 +2610,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2627,7 +2630,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2647,7 +2650,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2667,7 +2670,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2687,7 +2690,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2707,7 +2710,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2727,7 +2730,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -2747,7 +2750,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -2767,7 +2770,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -2787,7 +2790,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -2807,7 +2810,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -2827,7 +2830,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -2847,7 +2850,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -2867,7 +2870,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -2887,7 +2890,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -2907,7 +2910,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -2927,7 +2930,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -2947,7 +2950,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -2967,7 +2970,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -2987,7 +2990,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3007,7 +3010,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3027,7 +3030,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3047,7 +3050,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3067,7 +3070,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3087,7 +3090,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3107,7 +3110,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3127,7 +3130,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3147,7 +3150,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3167,7 +3170,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3187,7 +3190,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3207,7 +3210,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3227,7 +3230,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3247,7 +3250,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3267,7 +3270,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3287,7 +3290,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3307,7 +3310,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3327,7 +3330,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3347,7 +3350,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3367,7 +3370,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3387,7 +3390,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3407,7 +3410,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3427,7 +3430,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3447,7 +3450,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3467,7 +3470,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3487,7 +3490,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3507,7 +3510,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3527,7 +3530,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3547,7 +3550,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3567,7 +3570,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3587,7 +3590,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3607,7 +3610,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3627,7 +3630,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3647,7 +3650,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3667,7 +3670,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3687,7 +3690,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3707,7 +3710,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3727,7 +3730,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3747,7 +3750,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -3767,7 +3770,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -3787,7 +3790,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -3807,7 +3810,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -3827,7 +3830,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -3847,7 +3850,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -3867,7 +3870,7 @@
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -3887,7 +3890,7 @@
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -3907,7 +3910,7 @@
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -3927,7 +3930,7 @@
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -3947,7 +3950,7 @@
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -3967,7 +3970,7 @@
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -3987,7 +3990,7 @@
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4007,7 +4010,7 @@
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4027,7 +4030,7 @@
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4047,7 +4050,7 @@
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4067,7 +4070,7 @@
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4087,7 +4090,7 @@
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4107,7 +4110,7 @@
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4127,7 +4130,7 @@
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D171">
         <v>18</v>
@@ -4147,7 +4150,7 @@
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4167,7 +4170,7 @@
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4187,7 +4190,7 @@
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4207,7 +4210,7 @@
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4227,7 +4230,7 @@
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4247,7 +4250,7 @@
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4267,7 +4270,7 @@
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4287,7 +4290,7 @@
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4307,7 +4310,7 @@
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4327,7 +4330,7 @@
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4347,7 +4350,7 @@
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4367,7 +4370,7 @@
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4387,7 +4390,7 @@
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4407,7 +4410,7 @@
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4427,7 +4430,7 @@
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4447,7 +4450,7 @@
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4467,7 +4470,7 @@
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4487,7 +4490,7 @@
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4503,11 +4506,11 @@
       <c r="A190" t="s">
         <v>101</v>
       </c>
-      <c r="B190" t="s">
-        <v>102</v>
+      <c r="B190">
+        <v>4412</v>
       </c>
       <c r="C190" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D190">
         <v>116</v>
@@ -4517,6 +4520,86 @@
       </c>
       <c r="F190">
         <v>5.767</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B191">
+        <v>1107</v>
+      </c>
+      <c r="C191" t="s">
+        <v>108</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>11.96</v>
+      </c>
+      <c r="F191">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>102</v>
+      </c>
+      <c r="B192">
+        <v>3115</v>
+      </c>
+      <c r="C192" t="s">
+        <v>106</v>
+      </c>
+      <c r="D192">
+        <v>148</v>
+      </c>
+      <c r="E192">
+        <v>1025.28</v>
+      </c>
+      <c r="F192">
+        <v>6.928</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>102</v>
+      </c>
+      <c r="B193">
+        <v>5440</v>
+      </c>
+      <c r="C193" t="s">
+        <v>114</v>
+      </c>
+      <c r="D193">
+        <v>114</v>
+      </c>
+      <c r="E193">
+        <v>657.4</v>
+      </c>
+      <c r="F193">
+        <v>5.767</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>102</v>
+      </c>
+      <c r="B194" t="s">
+        <v>103</v>
+      </c>
+      <c r="C194" t="s">
+        <v>108</v>
+      </c>
+      <c r="D194">
+        <v>57</v>
+      </c>
+      <c r="E194">
+        <v>388.16</v>
+      </c>
+      <c r="F194">
+        <v>6.81</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -319,13 +319,40 @@
     <t>2025-08-13</t>
   </si>
   <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
     <t>2025-08-15</t>
   </si>
   <si>
     <t>2025-08-16</t>
   </si>
   <si>
-    <t>5441</t>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>4209</t>
   </si>
   <si>
     <t>N14</t>
@@ -362,6 +389,9 @@
   </si>
   <si>
     <t>CO62175</t>
+  </si>
+  <si>
+    <t>90F0613</t>
   </si>
 </sst>
 </file>
@@ -719,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -750,7 +780,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -770,7 +800,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -790,7 +820,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -810,7 +840,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -830,7 +860,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -850,7 +880,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -870,7 +900,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -890,7 +920,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -910,7 +940,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -930,7 +960,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -950,7 +980,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -970,7 +1000,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -990,7 +1020,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1010,7 +1040,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1030,7 +1060,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1050,7 +1080,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1070,7 +1100,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1090,7 +1120,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1110,7 +1140,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1130,7 +1160,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1150,7 +1180,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1170,7 +1200,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1190,7 +1220,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1210,7 +1240,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1230,7 +1260,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1250,7 +1280,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1270,7 +1300,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1290,7 +1320,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1310,7 +1340,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1330,7 +1360,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1350,7 +1380,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1370,7 +1400,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1390,7 +1420,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1410,7 +1440,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1430,7 +1460,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1450,7 +1480,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1470,7 +1500,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1490,7 +1520,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1510,7 +1540,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1530,7 +1560,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1550,7 +1580,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1570,7 +1600,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1590,7 +1620,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1610,7 +1640,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1630,7 +1660,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1650,7 +1680,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1670,7 +1700,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1690,7 +1720,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1710,7 +1740,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -1730,7 +1760,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -1750,7 +1780,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -1770,7 +1800,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -1790,7 +1820,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -1810,7 +1840,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1830,7 +1860,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1850,7 +1880,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -1870,7 +1900,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -1890,7 +1920,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -1910,7 +1940,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -1930,7 +1960,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -1950,7 +1980,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -1970,7 +2000,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -1990,7 +2020,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2010,7 +2040,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -2030,7 +2060,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2050,7 +2080,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2070,7 +2100,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2090,7 +2120,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2110,7 +2140,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2130,7 +2160,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2150,7 +2180,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2170,7 +2200,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2190,7 +2220,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2210,7 +2240,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2230,7 +2260,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2250,7 +2280,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2270,7 +2300,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2290,7 +2320,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2310,7 +2340,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2330,7 +2360,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2350,7 +2380,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2370,7 +2400,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2390,7 +2420,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2410,7 +2440,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2430,7 +2460,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2450,7 +2480,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2470,7 +2500,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2490,7 +2520,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2510,7 +2540,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2530,7 +2560,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2550,7 +2580,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2570,7 +2600,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2590,7 +2620,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2610,7 +2640,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2630,7 +2660,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2650,7 +2680,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2670,7 +2700,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2690,7 +2720,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2710,7 +2740,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2730,7 +2760,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -2750,7 +2780,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -2770,7 +2800,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -2790,7 +2820,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -2810,7 +2840,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -2830,7 +2860,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -2850,7 +2880,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -2870,7 +2900,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -2890,7 +2920,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -2910,7 +2940,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -2930,7 +2960,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -2950,7 +2980,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -2970,7 +3000,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -2990,7 +3020,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3010,7 +3040,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3030,7 +3060,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3050,7 +3080,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3070,7 +3100,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3090,7 +3120,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3110,7 +3140,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3130,7 +3160,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3150,7 +3180,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3170,7 +3200,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3190,7 +3220,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3210,7 +3240,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3230,7 +3260,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3250,7 +3280,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3270,7 +3300,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3290,7 +3320,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3310,7 +3340,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3330,7 +3360,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3350,7 +3380,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3370,7 +3400,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3390,7 +3420,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3410,7 +3440,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3430,7 +3460,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3450,7 +3480,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3470,7 +3500,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3490,7 +3520,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3510,7 +3540,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3530,7 +3560,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3550,7 +3580,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3570,7 +3600,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3590,7 +3620,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3610,7 +3640,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3630,7 +3660,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3650,7 +3680,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3670,7 +3700,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3690,7 +3720,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3710,7 +3740,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3730,7 +3760,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3750,7 +3780,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -3770,7 +3800,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -3790,7 +3820,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -3810,7 +3840,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -3830,7 +3860,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -3850,7 +3880,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -3870,7 +3900,7 @@
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -3890,7 +3920,7 @@
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -3910,7 +3940,7 @@
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -3930,7 +3960,7 @@
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -3950,7 +3980,7 @@
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -3970,7 +4000,7 @@
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -3990,7 +4020,7 @@
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4010,7 +4040,7 @@
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4030,7 +4060,7 @@
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4050,7 +4080,7 @@
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4070,7 +4100,7 @@
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4090,7 +4120,7 @@
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4110,7 +4140,7 @@
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4130,7 +4160,7 @@
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D171">
         <v>18</v>
@@ -4150,7 +4180,7 @@
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4170,7 +4200,7 @@
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4190,7 +4220,7 @@
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4210,7 +4240,7 @@
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4230,7 +4260,7 @@
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4250,7 +4280,7 @@
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4270,7 +4300,7 @@
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4290,7 +4320,7 @@
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4310,7 +4340,7 @@
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4330,7 +4360,7 @@
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4350,7 +4380,7 @@
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4370,7 +4400,7 @@
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4390,7 +4420,7 @@
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4410,7 +4440,7 @@
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4430,7 +4460,7 @@
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4450,7 +4480,7 @@
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4470,7 +4500,7 @@
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4490,7 +4520,7 @@
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4507,59 +4537,59 @@
         <v>101</v>
       </c>
       <c r="B190">
-        <v>4412</v>
+        <v>4241</v>
       </c>
       <c r="C190" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D190">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="E190">
-        <v>668.9400000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F190">
-        <v>5.767</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B191">
-        <v>1107</v>
+        <v>4412</v>
       </c>
       <c r="C191" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D191">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E191">
-        <v>11.96</v>
+        <v>30.66</v>
       </c>
       <c r="F191">
-        <v>11.96</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B192">
-        <v>3115</v>
+        <v>5208</v>
       </c>
       <c r="C192" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D192">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="E192">
-        <v>1025.28</v>
+        <v>10.74</v>
       </c>
       <c r="F192">
-        <v>6.928</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4567,16 +4597,16 @@
         <v>102</v>
       </c>
       <c r="B193">
-        <v>5440</v>
+        <v>4412</v>
       </c>
       <c r="C193" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D193">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E193">
-        <v>657.4</v>
+        <v>668.9400000000001</v>
       </c>
       <c r="F193">
         <v>5.767</v>
@@ -4584,22 +4614,362 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>102</v>
-      </c>
-      <c r="B194" t="s">
         <v>103</v>
       </c>
+      <c r="B194">
+        <v>1107</v>
+      </c>
       <c r="C194" t="s">
+        <v>117</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>11.96</v>
+      </c>
+      <c r="F194">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>103</v>
+      </c>
+      <c r="B195">
+        <v>3115</v>
+      </c>
+      <c r="C195" t="s">
+        <v>115</v>
+      </c>
+      <c r="D195">
+        <v>148</v>
+      </c>
+      <c r="E195">
+        <v>1025.28</v>
+      </c>
+      <c r="F195">
+        <v>6.928</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>103</v>
+      </c>
+      <c r="B196">
+        <v>5440</v>
+      </c>
+      <c r="C196" t="s">
+        <v>123</v>
+      </c>
+      <c r="D196">
+        <v>114</v>
+      </c>
+      <c r="E196">
+        <v>657.4</v>
+      </c>
+      <c r="F196">
+        <v>5.767</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>103</v>
+      </c>
+      <c r="B197">
+        <v>5441</v>
+      </c>
+      <c r="C197" t="s">
+        <v>117</v>
+      </c>
+      <c r="D197">
+        <v>57</v>
+      </c>
+      <c r="E197">
+        <v>388.16</v>
+      </c>
+      <c r="F197">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>104</v>
+      </c>
+      <c r="B198">
+        <v>3115</v>
+      </c>
+      <c r="C198" t="s">
+        <v>115</v>
+      </c>
+      <c r="D198">
+        <v>40</v>
+      </c>
+      <c r="E198">
+        <v>282.88</v>
+      </c>
+      <c r="F198">
+        <v>7.072</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>104</v>
+      </c>
+      <c r="B199">
+        <v>5208</v>
+      </c>
+      <c r="C199" t="s">
+        <v>115</v>
+      </c>
+      <c r="D199">
+        <v>5</v>
+      </c>
+      <c r="E199">
+        <v>31.92</v>
+      </c>
+      <c r="F199">
+        <v>6.384</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>104</v>
+      </c>
+      <c r="B200">
+        <v>5440</v>
+      </c>
+      <c r="C200" t="s">
+        <v>123</v>
+      </c>
+      <c r="D200">
+        <v>111</v>
+      </c>
+      <c r="E200">
+        <v>608.96</v>
+      </c>
+      <c r="F200">
+        <v>5.486</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>105</v>
+      </c>
+      <c r="B201">
+        <v>3115</v>
+      </c>
+      <c r="C201" t="s">
+        <v>115</v>
+      </c>
+      <c r="D201">
+        <v>6</v>
+      </c>
+      <c r="E201">
+        <v>38.94</v>
+      </c>
+      <c r="F201">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>105</v>
+      </c>
+      <c r="B202">
+        <v>4129</v>
+      </c>
+      <c r="C202" t="s">
+        <v>115</v>
+      </c>
+      <c r="D202">
+        <v>89</v>
+      </c>
+      <c r="E202">
+        <v>527.22</v>
+      </c>
+      <c r="F202">
+        <v>5.924</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>106</v>
+      </c>
+      <c r="B203">
+        <v>4129</v>
+      </c>
+      <c r="C203" t="s">
+        <v>115</v>
+      </c>
+      <c r="D203">
+        <v>80</v>
+      </c>
+      <c r="E203">
+        <v>498.2</v>
+      </c>
+      <c r="F203">
+        <v>6.228</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>106</v>
+      </c>
+      <c r="B204">
+        <v>3317</v>
+      </c>
+      <c r="C204" t="s">
+        <v>123</v>
+      </c>
+      <c r="D204">
+        <v>204</v>
+      </c>
+      <c r="E204">
+        <v>1262.5</v>
+      </c>
+      <c r="F204">
+        <v>6.189</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>107</v>
+      </c>
+      <c r="B205">
+        <v>3317</v>
+      </c>
+      <c r="C205" t="s">
+        <v>123</v>
+      </c>
+      <c r="D205">
+        <v>3</v>
+      </c>
+      <c r="E205">
+        <v>20.78</v>
+      </c>
+      <c r="F205">
+        <v>6.927</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
         <v>108</v>
       </c>
-      <c r="D194">
-        <v>57</v>
-      </c>
-      <c r="E194">
-        <v>388.16</v>
-      </c>
-      <c r="F194">
-        <v>6.81</v>
+      <c r="B206">
+        <v>1215</v>
+      </c>
+      <c r="C206" t="s">
+        <v>123</v>
+      </c>
+      <c r="D206">
+        <v>151</v>
+      </c>
+      <c r="E206">
+        <v>975.84</v>
+      </c>
+      <c r="F206">
+        <v>6.463</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207">
+        <v>1215</v>
+      </c>
+      <c r="C207" t="s">
+        <v>123</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207">
+        <v>17.6</v>
+      </c>
+      <c r="F207">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>109</v>
+      </c>
+      <c r="B208">
+        <v>3317</v>
+      </c>
+      <c r="C208" t="s">
+        <v>123</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>4.26</v>
+      </c>
+      <c r="F208">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>109</v>
+      </c>
+      <c r="B209">
+        <v>4239</v>
+      </c>
+      <c r="C209" t="s">
+        <v>125</v>
+      </c>
+      <c r="D209">
+        <v>48</v>
+      </c>
+      <c r="E209">
+        <v>205.3</v>
+      </c>
+      <c r="F209">
+        <v>4.277</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>110</v>
+      </c>
+      <c r="B210">
+        <v>4209</v>
+      </c>
+      <c r="C210" t="s">
+        <v>115</v>
+      </c>
+      <c r="D210">
+        <v>69</v>
+      </c>
+      <c r="E210">
+        <v>529.66</v>
+      </c>
+      <c r="F210">
+        <v>7.676</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>111</v>
+      </c>
+      <c r="B211" t="s">
+        <v>112</v>
+      </c>
+      <c r="C211" t="s">
+        <v>115</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>9.24</v>
+      </c>
+      <c r="F211">
+        <v>9.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="183">
   <si>
     <t>Date</t>
   </si>
@@ -352,7 +352,178 @@
     <t>2025-08-24</t>
   </si>
   <si>
-    <t>4209</t>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>5701C</t>
+  </si>
+  <si>
+    <t>3122</t>
+  </si>
+  <si>
+    <t>5292</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>4239</t>
+  </si>
+  <si>
+    <t>5702</t>
+  </si>
+  <si>
+    <t>2319</t>
+  </si>
+  <si>
+    <t>4212</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>4291</t>
+  </si>
+  <si>
+    <t>5130</t>
+  </si>
+  <si>
+    <t>5406</t>
+  </si>
+  <si>
+    <t>2516</t>
+  </si>
+  <si>
+    <t>5501</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>5507</t>
+  </si>
+  <si>
+    <t>4230</t>
+  </si>
+  <si>
+    <t>5106</t>
+  </si>
+  <si>
+    <t>4228</t>
+  </si>
+  <si>
+    <t>4231</t>
+  </si>
+  <si>
+    <t>5118</t>
+  </si>
+  <si>
+    <t>5413</t>
+  </si>
+  <si>
+    <t>2513</t>
+  </si>
+  <si>
+    <t>5212</t>
+  </si>
+  <si>
+    <t>3402</t>
   </si>
   <si>
     <t>N14</t>
@@ -749,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -780,7 +951,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -800,7 +971,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -820,7 +991,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -840,7 +1011,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -860,7 +1031,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -880,7 +1051,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -900,7 +1071,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -920,7 +1091,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -940,7 +1111,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -960,7 +1131,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -980,7 +1151,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -1000,7 +1171,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -1020,7 +1191,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1040,7 +1211,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1060,7 +1231,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1080,7 +1251,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1100,7 +1271,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1120,7 +1291,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1140,7 +1311,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1160,7 +1331,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1180,7 +1351,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1200,7 +1371,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1220,7 +1391,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1240,7 +1411,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1260,7 +1431,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1280,7 +1451,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1300,7 +1471,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1320,7 +1491,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1340,7 +1511,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1360,7 +1531,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1380,7 +1551,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1400,7 +1571,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1420,7 +1591,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1440,7 +1611,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1460,7 +1631,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1480,7 +1651,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1500,7 +1671,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1520,7 +1691,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1540,7 +1711,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1560,7 +1731,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1580,7 +1751,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1600,7 +1771,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1620,7 +1791,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1640,7 +1811,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1660,7 +1831,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1680,7 +1851,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1700,7 +1871,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1720,7 +1891,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1740,7 +1911,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -1760,7 +1931,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -1780,7 +1951,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -1800,7 +1971,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -1820,7 +1991,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -1840,7 +2011,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1860,7 +2031,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1880,7 +2051,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -1900,7 +2071,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -1920,7 +2091,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -1940,7 +2111,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -1960,7 +2131,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -1980,7 +2151,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -2000,7 +2171,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -2020,7 +2191,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2040,7 +2211,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -2060,7 +2231,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2080,7 +2251,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2100,7 +2271,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2120,7 +2291,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2140,7 +2311,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2160,7 +2331,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2180,7 +2351,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2200,7 +2371,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2220,7 +2391,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2240,7 +2411,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2260,7 +2431,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2280,7 +2451,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2300,7 +2471,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2320,7 +2491,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2340,7 +2511,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2360,7 +2531,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2380,7 +2551,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2400,7 +2571,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2420,7 +2591,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2440,7 +2611,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2460,7 +2631,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2480,7 +2651,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2500,7 +2671,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2520,7 +2691,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2540,7 +2711,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2560,7 +2731,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2580,7 +2751,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2600,7 +2771,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2620,7 +2791,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2640,7 +2811,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2660,7 +2831,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2680,7 +2851,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2700,7 +2871,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2720,7 +2891,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2740,7 +2911,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2760,7 +2931,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -2780,7 +2951,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -2800,7 +2971,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -2820,7 +2991,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -2840,7 +3011,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -2860,7 +3031,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -2880,7 +3051,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -2900,7 +3071,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -2920,7 +3091,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -2940,7 +3111,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -2960,7 +3131,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -2980,7 +3151,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3000,7 +3171,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -3020,7 +3191,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3040,7 +3211,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3060,7 +3231,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3080,7 +3251,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3100,7 +3271,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3120,7 +3291,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3140,7 +3311,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3160,7 +3331,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3180,7 +3351,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3200,7 +3371,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3220,7 +3391,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3240,7 +3411,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3260,7 +3431,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3280,7 +3451,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3300,7 +3471,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3320,7 +3491,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3340,7 +3511,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3360,7 +3531,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3380,7 +3551,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3400,7 +3571,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3420,7 +3591,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3440,7 +3611,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3460,7 +3631,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3480,7 +3651,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3500,7 +3671,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3520,7 +3691,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3540,7 +3711,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3560,7 +3731,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3580,7 +3751,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3600,7 +3771,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3620,7 +3791,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3640,7 +3811,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3660,7 +3831,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3680,7 +3851,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3700,7 +3871,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3720,7 +3891,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3740,7 +3911,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3760,7 +3931,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3780,7 +3951,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -3800,7 +3971,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -3820,7 +3991,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -3840,7 +4011,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -3860,7 +4031,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -3880,7 +4051,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -3900,7 +4071,7 @@
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -3920,7 +4091,7 @@
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -3940,7 +4111,7 @@
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -3960,7 +4131,7 @@
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -3980,7 +4151,7 @@
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -4000,7 +4171,7 @@
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -4020,7 +4191,7 @@
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4040,7 +4211,7 @@
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4060,7 +4231,7 @@
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4080,7 +4251,7 @@
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4100,7 +4271,7 @@
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4120,7 +4291,7 @@
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4140,7 +4311,7 @@
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4160,7 +4331,7 @@
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D171">
         <v>18</v>
@@ -4180,7 +4351,7 @@
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4200,7 +4371,7 @@
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4220,7 +4391,7 @@
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4240,7 +4411,7 @@
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4260,7 +4431,7 @@
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4280,7 +4451,7 @@
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4300,7 +4471,7 @@
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4320,7 +4491,7 @@
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4340,7 +4511,7 @@
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4360,7 +4531,7 @@
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4380,7 +4551,7 @@
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4400,7 +4571,7 @@
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4420,7 +4591,7 @@
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4440,7 +4611,7 @@
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4460,7 +4631,7 @@
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4480,7 +4651,7 @@
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4500,7 +4671,7 @@
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4520,7 +4691,7 @@
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4540,7 +4711,7 @@
         <v>4241</v>
       </c>
       <c r="C190" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -4560,7 +4731,7 @@
         <v>4412</v>
       </c>
       <c r="C191" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D191">
         <v>4</v>
@@ -4580,7 +4751,7 @@
         <v>5208</v>
       </c>
       <c r="C192" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -4600,7 +4771,7 @@
         <v>4412</v>
       </c>
       <c r="C193" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D193">
         <v>116</v>
@@ -4620,7 +4791,7 @@
         <v>1107</v>
       </c>
       <c r="C194" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4640,7 +4811,7 @@
         <v>3115</v>
       </c>
       <c r="C195" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D195">
         <v>148</v>
@@ -4660,7 +4831,7 @@
         <v>5440</v>
       </c>
       <c r="C196" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D196">
         <v>114</v>
@@ -4680,7 +4851,7 @@
         <v>5441</v>
       </c>
       <c r="C197" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D197">
         <v>57</v>
@@ -4700,7 +4871,7 @@
         <v>3115</v>
       </c>
       <c r="C198" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D198">
         <v>40</v>
@@ -4720,7 +4891,7 @@
         <v>5208</v>
       </c>
       <c r="C199" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -4740,7 +4911,7 @@
         <v>5440</v>
       </c>
       <c r="C200" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D200">
         <v>111</v>
@@ -4760,7 +4931,7 @@
         <v>3115</v>
       </c>
       <c r="C201" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D201">
         <v>6</v>
@@ -4780,7 +4951,7 @@
         <v>4129</v>
       </c>
       <c r="C202" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D202">
         <v>89</v>
@@ -4800,7 +4971,7 @@
         <v>4129</v>
       </c>
       <c r="C203" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D203">
         <v>80</v>
@@ -4820,7 +4991,7 @@
         <v>3317</v>
       </c>
       <c r="C204" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D204">
         <v>204</v>
@@ -4840,7 +5011,7 @@
         <v>3317</v>
       </c>
       <c r="C205" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -4860,7 +5031,7 @@
         <v>1215</v>
       </c>
       <c r="C206" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D206">
         <v>151</v>
@@ -4880,7 +5051,7 @@
         <v>1215</v>
       </c>
       <c r="C207" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D207">
         <v>2</v>
@@ -4900,7 +5071,7 @@
         <v>3317</v>
       </c>
       <c r="C208" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -4920,7 +5091,7 @@
         <v>4239</v>
       </c>
       <c r="C209" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="D209">
         <v>48</v>
@@ -4940,7 +5111,7 @@
         <v>4209</v>
       </c>
       <c r="C210" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D210">
         <v>69</v>
@@ -4956,11 +5127,11 @@
       <c r="A211" t="s">
         <v>111</v>
       </c>
-      <c r="B211" t="s">
-        <v>112</v>
+      <c r="B211">
+        <v>4209</v>
       </c>
       <c r="C211" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -4970,6 +5141,1266 @@
       </c>
       <c r="F211">
         <v>9.24</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>112</v>
+      </c>
+      <c r="B212" t="s">
+        <v>144</v>
+      </c>
+      <c r="C212" t="s">
+        <v>172</v>
+      </c>
+      <c r="D212">
+        <v>137</v>
+      </c>
+      <c r="E212">
+        <v>906.34</v>
+      </c>
+      <c r="F212">
+        <v>6.616</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>113</v>
+      </c>
+      <c r="B213" t="s">
+        <v>145</v>
+      </c>
+      <c r="C213" t="s">
+        <v>172</v>
+      </c>
+      <c r="D213">
+        <v>178</v>
+      </c>
+      <c r="E213">
+        <v>1032.1</v>
+      </c>
+      <c r="F213">
+        <v>5.798</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>113</v>
+      </c>
+      <c r="B214" t="s">
+        <v>146</v>
+      </c>
+      <c r="C214" t="s">
+        <v>172</v>
+      </c>
+      <c r="D214">
+        <v>22</v>
+      </c>
+      <c r="E214">
+        <v>97.48</v>
+      </c>
+      <c r="F214">
+        <v>4.431</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>114</v>
+      </c>
+      <c r="B215" t="s">
+        <v>147</v>
+      </c>
+      <c r="C215" t="s">
+        <v>172</v>
+      </c>
+      <c r="D215">
+        <v>29</v>
+      </c>
+      <c r="E215">
+        <v>183.84</v>
+      </c>
+      <c r="F215">
+        <v>6.339</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>114</v>
+      </c>
+      <c r="B216" t="s">
+        <v>148</v>
+      </c>
+      <c r="C216" t="s">
+        <v>172</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216">
+        <v>160.26</v>
+      </c>
+      <c r="F216">
+        <v>6.968</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>114</v>
+      </c>
+      <c r="B217" t="s">
+        <v>149</v>
+      </c>
+      <c r="C217" t="s">
+        <v>182</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+      <c r="E217">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="F217">
+        <v>8.539999999999999</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>115</v>
+      </c>
+      <c r="B218" t="s">
+        <v>148</v>
+      </c>
+      <c r="C218" t="s">
+        <v>172</v>
+      </c>
+      <c r="D218">
+        <v>4</v>
+      </c>
+      <c r="E218">
+        <v>27.56</v>
+      </c>
+      <c r="F218">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>115</v>
+      </c>
+      <c r="B219" t="s">
+        <v>146</v>
+      </c>
+      <c r="C219" t="s">
+        <v>172</v>
+      </c>
+      <c r="D219">
+        <v>216</v>
+      </c>
+      <c r="E219">
+        <v>1188.18</v>
+      </c>
+      <c r="F219">
+        <v>5.501</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>116</v>
+      </c>
+      <c r="B220" t="s">
+        <v>146</v>
+      </c>
+      <c r="C220" t="s">
+        <v>172</v>
+      </c>
+      <c r="D220">
+        <v>3</v>
+      </c>
+      <c r="E220">
+        <v>19.54</v>
+      </c>
+      <c r="F220">
+        <v>6.513</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>117</v>
+      </c>
+      <c r="B221" t="s">
+        <v>146</v>
+      </c>
+      <c r="C221" t="s">
+        <v>172</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>6.82</v>
+      </c>
+      <c r="F221">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>117</v>
+      </c>
+      <c r="B222" t="s">
+        <v>150</v>
+      </c>
+      <c r="C222" t="s">
+        <v>172</v>
+      </c>
+      <c r="D222">
+        <v>263</v>
+      </c>
+      <c r="E222">
+        <v>1489.22</v>
+      </c>
+      <c r="F222">
+        <v>5.662</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>118</v>
+      </c>
+      <c r="B223" t="s">
+        <v>151</v>
+      </c>
+      <c r="C223" t="s">
+        <v>174</v>
+      </c>
+      <c r="D223">
+        <v>38</v>
+      </c>
+      <c r="E223">
+        <v>243.56</v>
+      </c>
+      <c r="F223">
+        <v>6.409</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>118</v>
+      </c>
+      <c r="B224" t="s">
+        <v>152</v>
+      </c>
+      <c r="C224" t="s">
+        <v>174</v>
+      </c>
+      <c r="D224">
+        <v>152</v>
+      </c>
+      <c r="E224">
+        <v>1015.74</v>
+      </c>
+      <c r="F224">
+        <v>6.683</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>119</v>
+      </c>
+      <c r="B225" t="s">
+        <v>151</v>
+      </c>
+      <c r="C225" t="s">
+        <v>174</v>
+      </c>
+      <c r="D225">
+        <v>184</v>
+      </c>
+      <c r="E225">
+        <v>1268.3</v>
+      </c>
+      <c r="F225">
+        <v>6.893</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>119</v>
+      </c>
+      <c r="B226" t="s">
+        <v>152</v>
+      </c>
+      <c r="C226" t="s">
+        <v>174</v>
+      </c>
+      <c r="D226">
+        <v>2</v>
+      </c>
+      <c r="E226">
+        <v>13.78</v>
+      </c>
+      <c r="F226">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>120</v>
+      </c>
+      <c r="B227" t="s">
+        <v>151</v>
+      </c>
+      <c r="C227" t="s">
+        <v>174</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+      <c r="E227">
+        <v>15.4</v>
+      </c>
+      <c r="F227">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>120</v>
+      </c>
+      <c r="B228" t="s">
+        <v>150</v>
+      </c>
+      <c r="C228" t="s">
+        <v>172</v>
+      </c>
+      <c r="D228">
+        <v>2</v>
+      </c>
+      <c r="E228">
+        <v>14.52</v>
+      </c>
+      <c r="F228">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>121</v>
+      </c>
+      <c r="B229" t="s">
+        <v>150</v>
+      </c>
+      <c r="C229" t="s">
+        <v>172</v>
+      </c>
+      <c r="D229">
+        <v>44</v>
+      </c>
+      <c r="E229">
+        <v>242.26</v>
+      </c>
+      <c r="F229">
+        <v>5.506</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>122</v>
+      </c>
+      <c r="B230" t="s">
+        <v>153</v>
+      </c>
+      <c r="C230" t="s">
+        <v>172</v>
+      </c>
+      <c r="D230">
+        <v>36</v>
+      </c>
+      <c r="E230">
+        <v>220.28</v>
+      </c>
+      <c r="F230">
+        <v>6.119</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>122</v>
+      </c>
+      <c r="B231" t="s">
+        <v>154</v>
+      </c>
+      <c r="C231" t="s">
+        <v>175</v>
+      </c>
+      <c r="D231">
+        <v>12</v>
+      </c>
+      <c r="E231">
+        <v>52.38</v>
+      </c>
+      <c r="F231">
+        <v>4.365</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>123</v>
+      </c>
+      <c r="B232" t="s">
+        <v>151</v>
+      </c>
+      <c r="C232" t="s">
+        <v>174</v>
+      </c>
+      <c r="D232">
+        <v>1</v>
+      </c>
+      <c r="E232">
+        <v>2.98</v>
+      </c>
+      <c r="F232">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>123</v>
+      </c>
+      <c r="B233" t="s">
+        <v>154</v>
+      </c>
+      <c r="C233" t="s">
+        <v>172</v>
+      </c>
+      <c r="D233">
+        <v>2</v>
+      </c>
+      <c r="E233">
+        <v>9.42</v>
+      </c>
+      <c r="F233">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>123</v>
+      </c>
+      <c r="B234" t="s">
+        <v>153</v>
+      </c>
+      <c r="C234" t="s">
+        <v>172</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234">
+        <v>251.82</v>
+      </c>
+      <c r="F234">
+        <v>6.142</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>123</v>
+      </c>
+      <c r="B235" t="s">
+        <v>155</v>
+      </c>
+      <c r="C235" t="s">
+        <v>175</v>
+      </c>
+      <c r="D235">
+        <v>83</v>
+      </c>
+      <c r="E235">
+        <v>604.46</v>
+      </c>
+      <c r="F235">
+        <v>7.283</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>123</v>
+      </c>
+      <c r="B236" t="s">
+        <v>156</v>
+      </c>
+      <c r="C236" t="s">
+        <v>180</v>
+      </c>
+      <c r="D236">
+        <v>55</v>
+      </c>
+      <c r="E236">
+        <v>349.1</v>
+      </c>
+      <c r="F236">
+        <v>6.347</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>124</v>
+      </c>
+      <c r="B237" t="s">
+        <v>155</v>
+      </c>
+      <c r="C237" t="s">
+        <v>175</v>
+      </c>
+      <c r="D237">
+        <v>52</v>
+      </c>
+      <c r="E237">
+        <v>349.46</v>
+      </c>
+      <c r="F237">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>125</v>
+      </c>
+      <c r="B238" t="s">
+        <v>157</v>
+      </c>
+      <c r="C238" t="s">
+        <v>175</v>
+      </c>
+      <c r="D238">
+        <v>137</v>
+      </c>
+      <c r="E238">
+        <v>841.64</v>
+      </c>
+      <c r="F238">
+        <v>6.143</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>125</v>
+      </c>
+      <c r="B239" t="s">
+        <v>156</v>
+      </c>
+      <c r="C239" t="s">
+        <v>175</v>
+      </c>
+      <c r="D239">
+        <v>2</v>
+      </c>
+      <c r="E239">
+        <v>14.58</v>
+      </c>
+      <c r="F239">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>126</v>
+      </c>
+      <c r="B240" t="s">
+        <v>157</v>
+      </c>
+      <c r="C240" t="s">
+        <v>175</v>
+      </c>
+      <c r="D240">
+        <v>110</v>
+      </c>
+      <c r="E240">
+        <v>651.9400000000001</v>
+      </c>
+      <c r="F240">
+        <v>5.927</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>126</v>
+      </c>
+      <c r="B241" t="s">
+        <v>158</v>
+      </c>
+      <c r="C241" t="s">
+        <v>172</v>
+      </c>
+      <c r="D241">
+        <v>194</v>
+      </c>
+      <c r="E241">
+        <v>1319.78</v>
+      </c>
+      <c r="F241">
+        <v>6.803</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>127</v>
+      </c>
+      <c r="B242" t="s">
+        <v>158</v>
+      </c>
+      <c r="C242" t="s">
+        <v>172</v>
+      </c>
+      <c r="D242">
+        <v>4</v>
+      </c>
+      <c r="E242">
+        <v>31.22</v>
+      </c>
+      <c r="F242">
+        <v>7.805</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>128</v>
+      </c>
+      <c r="B243" t="s">
+        <v>158</v>
+      </c>
+      <c r="C243" t="s">
+        <v>172</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+      <c r="E243">
+        <v>12.18</v>
+      </c>
+      <c r="F243">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>129</v>
+      </c>
+      <c r="B244" t="s">
+        <v>159</v>
+      </c>
+      <c r="C244" t="s">
+        <v>175</v>
+      </c>
+      <c r="D244">
+        <v>142</v>
+      </c>
+      <c r="E244">
+        <v>959.0599999999999</v>
+      </c>
+      <c r="F244">
+        <v>6.754</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>130</v>
+      </c>
+      <c r="B245" t="s">
+        <v>159</v>
+      </c>
+      <c r="C245" t="s">
+        <v>175</v>
+      </c>
+      <c r="D245">
+        <v>28</v>
+      </c>
+      <c r="E245">
+        <v>198.2</v>
+      </c>
+      <c r="F245">
+        <v>7.079</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>130</v>
+      </c>
+      <c r="B246" t="s">
+        <v>160</v>
+      </c>
+      <c r="C246" t="s">
+        <v>172</v>
+      </c>
+      <c r="D246">
+        <v>153</v>
+      </c>
+      <c r="E246">
+        <v>1086.42</v>
+      </c>
+      <c r="F246">
+        <v>7.101</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>131</v>
+      </c>
+      <c r="B247" t="s">
+        <v>161</v>
+      </c>
+      <c r="C247" t="s">
+        <v>174</v>
+      </c>
+      <c r="D247">
+        <v>138</v>
+      </c>
+      <c r="E247">
+        <v>967.38</v>
+      </c>
+      <c r="F247">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>132</v>
+      </c>
+      <c r="B248" t="s">
+        <v>162</v>
+      </c>
+      <c r="C248" t="s">
+        <v>172</v>
+      </c>
+      <c r="D248">
+        <v>153</v>
+      </c>
+      <c r="E248">
+        <v>973.72</v>
+      </c>
+      <c r="F248">
+        <v>6.364</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>133</v>
+      </c>
+      <c r="B249" t="s">
+        <v>163</v>
+      </c>
+      <c r="C249" t="s">
+        <v>172</v>
+      </c>
+      <c r="D249">
+        <v>30</v>
+      </c>
+      <c r="E249">
+        <v>184.64</v>
+      </c>
+      <c r="F249">
+        <v>6.155</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>133</v>
+      </c>
+      <c r="B250" t="s">
+        <v>161</v>
+      </c>
+      <c r="C250" t="s">
+        <v>174</v>
+      </c>
+      <c r="D250">
+        <v>1</v>
+      </c>
+      <c r="E250">
+        <v>10.62</v>
+      </c>
+      <c r="F250">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>133</v>
+      </c>
+      <c r="B251" t="s">
+        <v>164</v>
+      </c>
+      <c r="C251" t="s">
+        <v>174</v>
+      </c>
+      <c r="D251">
+        <v>102</v>
+      </c>
+      <c r="E251">
+        <v>705.24</v>
+      </c>
+      <c r="F251">
+        <v>6.914</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>133</v>
+      </c>
+      <c r="B252" t="s">
+        <v>162</v>
+      </c>
+      <c r="C252" t="s">
+        <v>172</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+      <c r="E252">
+        <v>11.42</v>
+      </c>
+      <c r="F252">
+        <v>11.42</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>133</v>
+      </c>
+      <c r="B253" t="s">
+        <v>160</v>
+      </c>
+      <c r="C253" t="s">
+        <v>172</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+      <c r="E253">
+        <v>6.52</v>
+      </c>
+      <c r="F253">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
+        <v>134</v>
+      </c>
+      <c r="B254" t="s">
+        <v>157</v>
+      </c>
+      <c r="C254" t="s">
+        <v>175</v>
+      </c>
+      <c r="D254">
+        <v>24</v>
+      </c>
+      <c r="E254">
+        <v>159.2</v>
+      </c>
+      <c r="F254">
+        <v>6.633</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>134</v>
+      </c>
+      <c r="B255" t="s">
+        <v>162</v>
+      </c>
+      <c r="C255" t="s">
+        <v>172</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+      <c r="E255">
+        <v>9.1</v>
+      </c>
+      <c r="F255">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>135</v>
+      </c>
+      <c r="B256" t="s">
+        <v>157</v>
+      </c>
+      <c r="C256" t="s">
+        <v>175</v>
+      </c>
+      <c r="D256">
+        <v>102</v>
+      </c>
+      <c r="E256">
+        <v>688</v>
+      </c>
+      <c r="F256">
+        <v>6.745</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>135</v>
+      </c>
+      <c r="B257" t="s">
+        <v>162</v>
+      </c>
+      <c r="C257" t="s">
+        <v>172</v>
+      </c>
+      <c r="D257">
+        <v>142</v>
+      </c>
+      <c r="E257">
+        <v>1368.72</v>
+      </c>
+      <c r="F257">
+        <v>9.638999999999999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>136</v>
+      </c>
+      <c r="B258" t="s">
+        <v>164</v>
+      </c>
+      <c r="C258" t="s">
+        <v>174</v>
+      </c>
+      <c r="D258">
+        <v>4</v>
+      </c>
+      <c r="E258">
+        <v>31.7</v>
+      </c>
+      <c r="F258">
+        <v>7.925</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>137</v>
+      </c>
+      <c r="B259" t="s">
+        <v>159</v>
+      </c>
+      <c r="C259" t="s">
+        <v>175</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259">
+        <v>1.84</v>
+      </c>
+      <c r="F259">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>137</v>
+      </c>
+      <c r="B260" t="s">
+        <v>157</v>
+      </c>
+      <c r="C260" t="s">
+        <v>175</v>
+      </c>
+      <c r="D260">
+        <v>5</v>
+      </c>
+      <c r="E260">
+        <v>30.06</v>
+      </c>
+      <c r="F260">
+        <v>6.012</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>138</v>
+      </c>
+      <c r="B261" t="s">
+        <v>162</v>
+      </c>
+      <c r="C261" t="s">
+        <v>172</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+      <c r="E261">
+        <v>15.18</v>
+      </c>
+      <c r="F261">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>138</v>
+      </c>
+      <c r="B262" t="s">
+        <v>165</v>
+      </c>
+      <c r="C262" t="s">
+        <v>172</v>
+      </c>
+      <c r="D262">
+        <v>118</v>
+      </c>
+      <c r="E262">
+        <v>779.3200000000001</v>
+      </c>
+      <c r="F262">
+        <v>6.604</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>139</v>
+      </c>
+      <c r="B263" t="s">
+        <v>157</v>
+      </c>
+      <c r="C263" t="s">
+        <v>175</v>
+      </c>
+      <c r="D263">
+        <v>2</v>
+      </c>
+      <c r="E263">
+        <v>20.92</v>
+      </c>
+      <c r="F263">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>139</v>
+      </c>
+      <c r="B264" t="s">
+        <v>166</v>
+      </c>
+      <c r="C264" t="s">
+        <v>174</v>
+      </c>
+      <c r="D264">
+        <v>76</v>
+      </c>
+      <c r="E264">
+        <v>465.5</v>
+      </c>
+      <c r="F264">
+        <v>6.125</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>139</v>
+      </c>
+      <c r="B265" t="s">
+        <v>167</v>
+      </c>
+      <c r="C265" t="s">
+        <v>175</v>
+      </c>
+      <c r="D265">
+        <v>6</v>
+      </c>
+      <c r="E265">
+        <v>38.58</v>
+      </c>
+      <c r="F265">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>140</v>
+      </c>
+      <c r="B266" t="s">
+        <v>167</v>
+      </c>
+      <c r="C266" t="s">
+        <v>175</v>
+      </c>
+      <c r="D266">
+        <v>210</v>
+      </c>
+      <c r="E266">
+        <v>1339.1</v>
+      </c>
+      <c r="F266">
+        <v>6.377</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>140</v>
+      </c>
+      <c r="B267" t="s">
+        <v>165</v>
+      </c>
+      <c r="C267" t="s">
+        <v>172</v>
+      </c>
+      <c r="D267">
+        <v>1</v>
+      </c>
+      <c r="E267">
+        <v>8.9</v>
+      </c>
+      <c r="F267">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>140</v>
+      </c>
+      <c r="B268" t="s">
+        <v>166</v>
+      </c>
+      <c r="C268" t="s">
+        <v>174</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+      <c r="E268">
+        <v>12.54</v>
+      </c>
+      <c r="F268">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>141</v>
+      </c>
+      <c r="B269" t="s">
+        <v>167</v>
+      </c>
+      <c r="C269" t="s">
+        <v>175</v>
+      </c>
+      <c r="D269">
+        <v>157</v>
+      </c>
+      <c r="E269">
+        <v>986.16</v>
+      </c>
+      <c r="F269">
+        <v>6.281</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>141</v>
+      </c>
+      <c r="B270" t="s">
+        <v>166</v>
+      </c>
+      <c r="C270" t="s">
+        <v>174</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+      <c r="E270">
+        <v>9.02</v>
+      </c>
+      <c r="F270">
+        <v>9.02</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>142</v>
+      </c>
+      <c r="B271" t="s">
+        <v>167</v>
+      </c>
+      <c r="C271" t="s">
+        <v>175</v>
+      </c>
+      <c r="D271">
+        <v>5</v>
+      </c>
+      <c r="E271">
+        <v>33.94</v>
+      </c>
+      <c r="F271">
+        <v>6.788</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>142</v>
+      </c>
+      <c r="B272" t="s">
+        <v>168</v>
+      </c>
+      <c r="C272" t="s">
+        <v>174</v>
+      </c>
+      <c r="D272">
+        <v>129</v>
+      </c>
+      <c r="E272">
+        <v>1016.3</v>
+      </c>
+      <c r="F272">
+        <v>7.878</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>143</v>
+      </c>
+      <c r="B273" t="s">
+        <v>169</v>
+      </c>
+      <c r="C273" t="s">
+        <v>175</v>
+      </c>
+      <c r="D273">
+        <v>93</v>
+      </c>
+      <c r="E273">
+        <v>559.24</v>
+      </c>
+      <c r="F273">
+        <v>6.013</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>143</v>
+      </c>
+      <c r="B274" t="s">
+        <v>168</v>
+      </c>
+      <c r="C274" t="s">
+        <v>174</v>
+      </c>
+      <c r="D274">
+        <v>102</v>
+      </c>
+      <c r="E274">
+        <v>751.72</v>
+      </c>
+      <c r="F274">
+        <v>7.37</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="206">
   <si>
     <t>Date</t>
   </si>
@@ -448,6 +448,36 @@
     <t>2025-09-28</t>
   </si>
   <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>2025-10-12</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -524,6 +554,45 @@
   </si>
   <si>
     <t>3402</t>
+  </si>
+  <si>
+    <t>5128</t>
+  </si>
+  <si>
+    <t>5404</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>5120</t>
+  </si>
+  <si>
+    <t>5509</t>
+  </si>
+  <si>
+    <t>5411</t>
+  </si>
+  <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>4319</t>
+  </si>
+  <si>
+    <t>5214</t>
+  </si>
+  <si>
+    <t>5435</t>
+  </si>
+  <si>
+    <t>5291</t>
+  </si>
+  <si>
+    <t>5390</t>
   </si>
   <si>
     <t>N14</t>
@@ -920,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -951,7 +1020,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -971,7 +1040,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -991,7 +1060,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -1011,7 +1080,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -1031,7 +1100,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -1051,7 +1120,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1071,7 +1140,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -1091,7 +1160,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1111,7 +1180,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -1131,7 +1200,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1151,7 +1220,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -1171,7 +1240,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -1191,7 +1260,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1211,7 +1280,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1231,7 +1300,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1251,7 +1320,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1271,7 +1340,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1291,7 +1360,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1311,7 +1380,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1331,7 +1400,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1351,7 +1420,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1371,7 +1440,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1391,7 +1460,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1411,7 +1480,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1431,7 +1500,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1451,7 +1520,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1471,7 +1540,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1491,7 +1560,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1511,7 +1580,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1531,7 +1600,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1551,7 +1620,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1571,7 +1640,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1591,7 +1660,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1611,7 +1680,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1631,7 +1700,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1651,7 +1720,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1671,7 +1740,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1691,7 +1760,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1711,7 +1780,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1731,7 +1800,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1751,7 +1820,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1771,7 +1840,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1791,7 +1860,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1811,7 +1880,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1831,7 +1900,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1851,7 +1920,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1871,7 +1940,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1891,7 +1960,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1911,7 +1980,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -1931,7 +2000,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -1951,7 +2020,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -1971,7 +2040,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -1991,7 +2060,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2011,7 +2080,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2031,7 +2100,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2051,7 +2120,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2071,7 +2140,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2091,7 +2160,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -2111,7 +2180,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -2131,7 +2200,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -2151,7 +2220,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -2171,7 +2240,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -2191,7 +2260,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2211,7 +2280,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -2231,7 +2300,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2251,7 +2320,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2271,7 +2340,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2291,7 +2360,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2311,7 +2380,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2331,7 +2400,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2351,7 +2420,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2371,7 +2440,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2391,7 +2460,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2411,7 +2480,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2431,7 +2500,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2451,7 +2520,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2471,7 +2540,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2491,7 +2560,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2511,7 +2580,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2531,7 +2600,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2551,7 +2620,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2571,7 +2640,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2591,7 +2660,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2611,7 +2680,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2631,7 +2700,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2651,7 +2720,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2671,7 +2740,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2691,7 +2760,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2711,7 +2780,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2731,7 +2800,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2751,7 +2820,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2771,7 +2840,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2791,7 +2860,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2811,7 +2880,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2831,7 +2900,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2851,7 +2920,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2871,7 +2940,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2891,7 +2960,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2911,7 +2980,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2931,7 +3000,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -2951,7 +3020,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -2971,7 +3040,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -2991,7 +3060,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -3011,7 +3080,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -3031,7 +3100,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -3051,7 +3120,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -3071,7 +3140,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -3091,7 +3160,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -3111,7 +3180,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -3131,7 +3200,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -3151,7 +3220,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3171,7 +3240,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -3191,7 +3260,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3211,7 +3280,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3231,7 +3300,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3251,7 +3320,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3271,7 +3340,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3291,7 +3360,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3311,7 +3380,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3331,7 +3400,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3351,7 +3420,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3371,7 +3440,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3391,7 +3460,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3411,7 +3480,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3431,7 +3500,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3451,7 +3520,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3471,7 +3540,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3491,7 +3560,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3511,7 +3580,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3531,7 +3600,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3551,7 +3620,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3571,7 +3640,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3591,7 +3660,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3611,7 +3680,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3631,7 +3700,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3651,7 +3720,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3671,7 +3740,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3691,7 +3760,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3711,7 +3780,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3731,7 +3800,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3751,7 +3820,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3771,7 +3840,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3791,7 +3860,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3811,7 +3880,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3831,7 +3900,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3851,7 +3920,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3871,7 +3940,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3891,7 +3960,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3911,7 +3980,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3931,7 +4000,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3951,7 +4020,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -3971,7 +4040,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -3991,7 +4060,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -4011,7 +4080,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -4031,7 +4100,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -4051,7 +4120,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -4071,7 +4140,7 @@
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -4091,7 +4160,7 @@
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -4111,7 +4180,7 @@
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -4131,7 +4200,7 @@
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -4151,7 +4220,7 @@
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -4171,7 +4240,7 @@
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -4191,7 +4260,7 @@
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4211,7 +4280,7 @@
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4231,7 +4300,7 @@
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4251,7 +4320,7 @@
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4271,7 +4340,7 @@
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4291,7 +4360,7 @@
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4311,7 +4380,7 @@
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4331,7 +4400,7 @@
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D171">
         <v>18</v>
@@ -4351,7 +4420,7 @@
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4371,7 +4440,7 @@
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4391,7 +4460,7 @@
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4411,7 +4480,7 @@
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4431,7 +4500,7 @@
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4451,7 +4520,7 @@
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4471,7 +4540,7 @@
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4491,7 +4560,7 @@
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4511,7 +4580,7 @@
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4531,7 +4600,7 @@
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4551,7 +4620,7 @@
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4571,7 +4640,7 @@
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4591,7 +4660,7 @@
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4611,7 +4680,7 @@
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4631,7 +4700,7 @@
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4651,7 +4720,7 @@
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4671,7 +4740,7 @@
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4691,7 +4760,7 @@
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4711,7 +4780,7 @@
         <v>4241</v>
       </c>
       <c r="C190" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -4731,7 +4800,7 @@
         <v>4412</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D191">
         <v>4</v>
@@ -4751,7 +4820,7 @@
         <v>5208</v>
       </c>
       <c r="C192" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -4771,7 +4840,7 @@
         <v>4412</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D193">
         <v>116</v>
@@ -4791,7 +4860,7 @@
         <v>1107</v>
       </c>
       <c r="C194" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4811,7 +4880,7 @@
         <v>3115</v>
       </c>
       <c r="C195" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D195">
         <v>148</v>
@@ -4831,7 +4900,7 @@
         <v>5440</v>
       </c>
       <c r="C196" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D196">
         <v>114</v>
@@ -4851,7 +4920,7 @@
         <v>5441</v>
       </c>
       <c r="C197" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D197">
         <v>57</v>
@@ -4871,7 +4940,7 @@
         <v>3115</v>
       </c>
       <c r="C198" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D198">
         <v>40</v>
@@ -4891,7 +4960,7 @@
         <v>5208</v>
       </c>
       <c r="C199" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -4911,7 +4980,7 @@
         <v>5440</v>
       </c>
       <c r="C200" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D200">
         <v>111</v>
@@ -4931,7 +5000,7 @@
         <v>3115</v>
       </c>
       <c r="C201" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D201">
         <v>6</v>
@@ -4951,7 +5020,7 @@
         <v>4129</v>
       </c>
       <c r="C202" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D202">
         <v>89</v>
@@ -4971,7 +5040,7 @@
         <v>4129</v>
       </c>
       <c r="C203" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D203">
         <v>80</v>
@@ -4991,7 +5060,7 @@
         <v>3317</v>
       </c>
       <c r="C204" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D204">
         <v>204</v>
@@ -5011,7 +5080,7 @@
         <v>3317</v>
       </c>
       <c r="C205" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -5031,7 +5100,7 @@
         <v>1215</v>
       </c>
       <c r="C206" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D206">
         <v>151</v>
@@ -5051,7 +5120,7 @@
         <v>1215</v>
       </c>
       <c r="C207" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D207">
         <v>2</v>
@@ -5071,7 +5140,7 @@
         <v>3317</v>
       </c>
       <c r="C208" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -5091,7 +5160,7 @@
         <v>4239</v>
       </c>
       <c r="C209" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="D209">
         <v>48</v>
@@ -5111,7 +5180,7 @@
         <v>4209</v>
       </c>
       <c r="C210" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D210">
         <v>69</v>
@@ -5131,7 +5200,7 @@
         <v>4209</v>
       </c>
       <c r="C211" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -5148,10 +5217,10 @@
         <v>112</v>
       </c>
       <c r="B212" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C212" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D212">
         <v>137</v>
@@ -5168,10 +5237,10 @@
         <v>113</v>
       </c>
       <c r="B213" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C213" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D213">
         <v>178</v>
@@ -5188,10 +5257,10 @@
         <v>113</v>
       </c>
       <c r="B214" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C214" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D214">
         <v>22</v>
@@ -5208,10 +5277,10 @@
         <v>114</v>
       </c>
       <c r="B215" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C215" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D215">
         <v>29</v>
@@ -5228,10 +5297,10 @@
         <v>114</v>
       </c>
       <c r="B216" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C216" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -5248,10 +5317,10 @@
         <v>114</v>
       </c>
       <c r="B217" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C217" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -5268,10 +5337,10 @@
         <v>115</v>
       </c>
       <c r="B218" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C218" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -5288,10 +5357,10 @@
         <v>115</v>
       </c>
       <c r="B219" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C219" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D219">
         <v>216</v>
@@ -5308,10 +5377,10 @@
         <v>116</v>
       </c>
       <c r="B220" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C220" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -5328,10 +5397,10 @@
         <v>117</v>
       </c>
       <c r="B221" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C221" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5348,10 +5417,10 @@
         <v>117</v>
       </c>
       <c r="B222" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C222" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D222">
         <v>263</v>
@@ -5368,10 +5437,10 @@
         <v>118</v>
       </c>
       <c r="B223" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C223" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D223">
         <v>38</v>
@@ -5388,10 +5457,10 @@
         <v>118</v>
       </c>
       <c r="B224" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C224" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D224">
         <v>152</v>
@@ -5408,10 +5477,10 @@
         <v>119</v>
       </c>
       <c r="B225" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C225" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D225">
         <v>184</v>
@@ -5428,10 +5497,10 @@
         <v>119</v>
       </c>
       <c r="B226" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C226" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D226">
         <v>2</v>
@@ -5448,10 +5517,10 @@
         <v>120</v>
       </c>
       <c r="B227" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C227" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D227">
         <v>2</v>
@@ -5468,10 +5537,10 @@
         <v>120</v>
       </c>
       <c r="B228" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C228" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D228">
         <v>2</v>
@@ -5488,10 +5557,10 @@
         <v>121</v>
       </c>
       <c r="B229" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C229" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D229">
         <v>44</v>
@@ -5508,10 +5577,10 @@
         <v>122</v>
       </c>
       <c r="B230" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C230" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D230">
         <v>36</v>
@@ -5528,10 +5597,10 @@
         <v>122</v>
       </c>
       <c r="B231" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C231" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D231">
         <v>12</v>
@@ -5548,10 +5617,10 @@
         <v>123</v>
       </c>
       <c r="B232" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C232" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5568,10 +5637,10 @@
         <v>123</v>
       </c>
       <c r="B233" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C233" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D233">
         <v>2</v>
@@ -5588,10 +5657,10 @@
         <v>123</v>
       </c>
       <c r="B234" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C234" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5608,10 +5677,10 @@
         <v>123</v>
       </c>
       <c r="B235" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C235" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D235">
         <v>83</v>
@@ -5628,10 +5697,10 @@
         <v>123</v>
       </c>
       <c r="B236" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C236" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D236">
         <v>55</v>
@@ -5648,10 +5717,10 @@
         <v>124</v>
       </c>
       <c r="B237" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C237" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D237">
         <v>52</v>
@@ -5668,10 +5737,10 @@
         <v>125</v>
       </c>
       <c r="B238" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C238" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D238">
         <v>137</v>
@@ -5688,10 +5757,10 @@
         <v>125</v>
       </c>
       <c r="B239" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C239" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -5708,10 +5777,10 @@
         <v>126</v>
       </c>
       <c r="B240" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C240" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D240">
         <v>110</v>
@@ -5728,10 +5797,10 @@
         <v>126</v>
       </c>
       <c r="B241" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C241" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D241">
         <v>194</v>
@@ -5748,10 +5817,10 @@
         <v>127</v>
       </c>
       <c r="B242" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C242" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D242">
         <v>4</v>
@@ -5768,10 +5837,10 @@
         <v>128</v>
       </c>
       <c r="B243" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C243" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D243">
         <v>2</v>
@@ -5788,10 +5857,10 @@
         <v>129</v>
       </c>
       <c r="B244" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C244" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D244">
         <v>142</v>
@@ -5808,10 +5877,10 @@
         <v>130</v>
       </c>
       <c r="B245" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C245" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D245">
         <v>28</v>
@@ -5828,10 +5897,10 @@
         <v>130</v>
       </c>
       <c r="B246" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C246" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D246">
         <v>153</v>
@@ -5848,10 +5917,10 @@
         <v>131</v>
       </c>
       <c r="B247" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C247" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D247">
         <v>138</v>
@@ -5868,10 +5937,10 @@
         <v>132</v>
       </c>
       <c r="B248" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C248" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D248">
         <v>153</v>
@@ -5888,10 +5957,10 @@
         <v>133</v>
       </c>
       <c r="B249" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C249" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D249">
         <v>30</v>
@@ -5908,10 +5977,10 @@
         <v>133</v>
       </c>
       <c r="B250" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C250" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -5928,10 +5997,10 @@
         <v>133</v>
       </c>
       <c r="B251" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C251" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D251">
         <v>102</v>
@@ -5948,10 +6017,10 @@
         <v>133</v>
       </c>
       <c r="B252" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C252" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -5968,10 +6037,10 @@
         <v>133</v>
       </c>
       <c r="B253" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C253" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -5988,10 +6057,10 @@
         <v>134</v>
       </c>
       <c r="B254" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C254" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D254">
         <v>24</v>
@@ -6008,10 +6077,10 @@
         <v>134</v>
       </c>
       <c r="B255" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C255" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -6028,10 +6097,10 @@
         <v>135</v>
       </c>
       <c r="B256" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C256" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D256">
         <v>102</v>
@@ -6048,10 +6117,10 @@
         <v>135</v>
       </c>
       <c r="B257" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C257" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D257">
         <v>142</v>
@@ -6068,10 +6137,10 @@
         <v>136</v>
       </c>
       <c r="B258" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C258" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D258">
         <v>4</v>
@@ -6088,10 +6157,10 @@
         <v>137</v>
       </c>
       <c r="B259" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C259" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -6108,10 +6177,10 @@
         <v>137</v>
       </c>
       <c r="B260" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C260" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D260">
         <v>5</v>
@@ -6128,10 +6197,10 @@
         <v>138</v>
       </c>
       <c r="B261" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C261" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D261">
         <v>2</v>
@@ -6148,10 +6217,10 @@
         <v>138</v>
       </c>
       <c r="B262" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C262" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D262">
         <v>118</v>
@@ -6168,10 +6237,10 @@
         <v>139</v>
       </c>
       <c r="B263" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C263" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D263">
         <v>2</v>
@@ -6188,10 +6257,10 @@
         <v>139</v>
       </c>
       <c r="B264" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C264" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D264">
         <v>76</v>
@@ -6208,10 +6277,10 @@
         <v>139</v>
       </c>
       <c r="B265" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C265" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D265">
         <v>6</v>
@@ -6228,10 +6297,10 @@
         <v>140</v>
       </c>
       <c r="B266" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C266" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D266">
         <v>210</v>
@@ -6248,10 +6317,10 @@
         <v>140</v>
       </c>
       <c r="B267" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C267" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -6268,10 +6337,10 @@
         <v>140</v>
       </c>
       <c r="B268" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C268" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -6288,10 +6357,10 @@
         <v>141</v>
       </c>
       <c r="B269" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C269" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D269">
         <v>157</v>
@@ -6308,10 +6377,10 @@
         <v>141</v>
       </c>
       <c r="B270" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C270" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -6328,10 +6397,10 @@
         <v>142</v>
       </c>
       <c r="B271" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C271" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D271">
         <v>5</v>
@@ -6348,10 +6417,10 @@
         <v>142</v>
       </c>
       <c r="B272" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C272" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D272">
         <v>129</v>
@@ -6368,10 +6437,10 @@
         <v>143</v>
       </c>
       <c r="B273" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C273" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D273">
         <v>93</v>
@@ -6388,10 +6457,10 @@
         <v>143</v>
       </c>
       <c r="B274" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C274" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D274">
         <v>102</v>
@@ -6401,6 +6470,586 @@
       </c>
       <c r="F274">
         <v>7.37</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>144</v>
+      </c>
+      <c r="B275" t="s">
+        <v>177</v>
+      </c>
+      <c r="C275" t="s">
+        <v>198</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+      <c r="E275">
+        <v>7.02</v>
+      </c>
+      <c r="F275">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>144</v>
+      </c>
+      <c r="B276" t="s">
+        <v>173</v>
+      </c>
+      <c r="C276" t="s">
+        <v>195</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+      <c r="E276">
+        <v>4.9</v>
+      </c>
+      <c r="F276">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>144</v>
+      </c>
+      <c r="B277" t="s">
+        <v>180</v>
+      </c>
+      <c r="C277" t="s">
+        <v>198</v>
+      </c>
+      <c r="D277">
+        <v>2</v>
+      </c>
+      <c r="E277">
+        <v>14.12</v>
+      </c>
+      <c r="F277">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>144</v>
+      </c>
+      <c r="B278" t="s">
+        <v>181</v>
+      </c>
+      <c r="C278" t="s">
+        <v>203</v>
+      </c>
+      <c r="D278">
+        <v>102</v>
+      </c>
+      <c r="E278">
+        <v>726.8</v>
+      </c>
+      <c r="F278">
+        <v>7.125</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>145</v>
+      </c>
+      <c r="B279" t="s">
+        <v>182</v>
+      </c>
+      <c r="C279" t="s">
+        <v>198</v>
+      </c>
+      <c r="D279">
+        <v>202</v>
+      </c>
+      <c r="E279">
+        <v>1184.6</v>
+      </c>
+      <c r="F279">
+        <v>5.864</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>145</v>
+      </c>
+      <c r="B280" t="s">
+        <v>180</v>
+      </c>
+      <c r="C280" t="s">
+        <v>198</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+      <c r="E280">
+        <v>3.72</v>
+      </c>
+      <c r="F280">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>146</v>
+      </c>
+      <c r="B281" t="s">
+        <v>183</v>
+      </c>
+      <c r="C281" t="s">
+        <v>195</v>
+      </c>
+      <c r="D281">
+        <v>205</v>
+      </c>
+      <c r="E281">
+        <v>1424.26</v>
+      </c>
+      <c r="F281">
+        <v>6.948</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>146</v>
+      </c>
+      <c r="B282" t="s">
+        <v>180</v>
+      </c>
+      <c r="C282" t="s">
+        <v>198</v>
+      </c>
+      <c r="D282">
+        <v>1</v>
+      </c>
+      <c r="E282">
+        <v>2.36</v>
+      </c>
+      <c r="F282">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>146</v>
+      </c>
+      <c r="B283" t="s">
+        <v>181</v>
+      </c>
+      <c r="C283" t="s">
+        <v>203</v>
+      </c>
+      <c r="D283">
+        <v>9</v>
+      </c>
+      <c r="E283">
+        <v>55.42</v>
+      </c>
+      <c r="F283">
+        <v>6.158</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>147</v>
+      </c>
+      <c r="B284" t="s">
+        <v>182</v>
+      </c>
+      <c r="C284" t="s">
+        <v>198</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
+      </c>
+      <c r="E284">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="F284">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>147</v>
+      </c>
+      <c r="B285" t="s">
+        <v>183</v>
+      </c>
+      <c r="C285" t="s">
+        <v>195</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+      <c r="E285">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="F285">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>147</v>
+      </c>
+      <c r="B286" t="s">
+        <v>180</v>
+      </c>
+      <c r="C286" t="s">
+        <v>198</v>
+      </c>
+      <c r="D286">
+        <v>1</v>
+      </c>
+      <c r="E286">
+        <v>7.74</v>
+      </c>
+      <c r="F286">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>147</v>
+      </c>
+      <c r="B287" t="s">
+        <v>184</v>
+      </c>
+      <c r="C287" t="s">
+        <v>195</v>
+      </c>
+      <c r="D287">
+        <v>180</v>
+      </c>
+      <c r="E287">
+        <v>1311.9</v>
+      </c>
+      <c r="F287">
+        <v>7.288</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>148</v>
+      </c>
+      <c r="B288" t="s">
+        <v>185</v>
+      </c>
+      <c r="C288" t="s">
+        <v>195</v>
+      </c>
+      <c r="D288">
+        <v>2</v>
+      </c>
+      <c r="E288">
+        <v>17.86</v>
+      </c>
+      <c r="F288">
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>148</v>
+      </c>
+      <c r="B289" t="s">
+        <v>184</v>
+      </c>
+      <c r="C289" t="s">
+        <v>195</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+      <c r="E289">
+        <v>14.26</v>
+      </c>
+      <c r="F289">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>149</v>
+      </c>
+      <c r="B290" t="s">
+        <v>186</v>
+      </c>
+      <c r="C290" t="s">
+        <v>195</v>
+      </c>
+      <c r="D290">
+        <v>96</v>
+      </c>
+      <c r="E290">
+        <v>627.34</v>
+      </c>
+      <c r="F290">
+        <v>6.535</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>149</v>
+      </c>
+      <c r="B291" t="s">
+        <v>187</v>
+      </c>
+      <c r="C291" t="s">
+        <v>195</v>
+      </c>
+      <c r="D291">
+        <v>6</v>
+      </c>
+      <c r="E291">
+        <v>37.7</v>
+      </c>
+      <c r="F291">
+        <v>6.283</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>149</v>
+      </c>
+      <c r="B292" t="s">
+        <v>188</v>
+      </c>
+      <c r="C292" t="s">
+        <v>197</v>
+      </c>
+      <c r="D292">
+        <v>51</v>
+      </c>
+      <c r="E292">
+        <v>332.16</v>
+      </c>
+      <c r="F292">
+        <v>6.513</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>149</v>
+      </c>
+      <c r="B293" t="s">
+        <v>184</v>
+      </c>
+      <c r="C293" t="s">
+        <v>195</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293">
+        <v>25.44</v>
+      </c>
+      <c r="F293">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>150</v>
+      </c>
+      <c r="B294" t="s">
+        <v>186</v>
+      </c>
+      <c r="C294" t="s">
+        <v>195</v>
+      </c>
+      <c r="D294">
+        <v>136</v>
+      </c>
+      <c r="E294">
+        <v>946.72</v>
+      </c>
+      <c r="F294">
+        <v>6.961</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>150</v>
+      </c>
+      <c r="B295" t="s">
+        <v>187</v>
+      </c>
+      <c r="C295" t="s">
+        <v>195</v>
+      </c>
+      <c r="D295">
+        <v>35</v>
+      </c>
+      <c r="E295">
+        <v>230.6</v>
+      </c>
+      <c r="F295">
+        <v>6.589</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>150</v>
+      </c>
+      <c r="B296" t="s">
+        <v>189</v>
+      </c>
+      <c r="C296" t="s">
+        <v>195</v>
+      </c>
+      <c r="D296">
+        <v>59</v>
+      </c>
+      <c r="E296">
+        <v>353.08</v>
+      </c>
+      <c r="F296">
+        <v>5.984</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>151</v>
+      </c>
+      <c r="B297" t="s">
+        <v>187</v>
+      </c>
+      <c r="C297" t="s">
+        <v>195</v>
+      </c>
+      <c r="D297">
+        <v>17</v>
+      </c>
+      <c r="E297">
+        <v>116.7</v>
+      </c>
+      <c r="F297">
+        <v>6.865</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>151</v>
+      </c>
+      <c r="B298" t="s">
+        <v>190</v>
+      </c>
+      <c r="C298" t="s">
+        <v>197</v>
+      </c>
+      <c r="D298">
+        <v>106</v>
+      </c>
+      <c r="E298">
+        <v>733.38</v>
+      </c>
+      <c r="F298">
+        <v>6.919</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>152</v>
+      </c>
+      <c r="B299" t="s">
+        <v>191</v>
+      </c>
+      <c r="C299" t="s">
+        <v>198</v>
+      </c>
+      <c r="D299">
+        <v>247</v>
+      </c>
+      <c r="E299">
+        <v>1511.22</v>
+      </c>
+      <c r="F299">
+        <v>6.118</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>153</v>
+      </c>
+      <c r="B300" t="s">
+        <v>189</v>
+      </c>
+      <c r="C300" t="s">
+        <v>195</v>
+      </c>
+      <c r="D300">
+        <v>2</v>
+      </c>
+      <c r="E300">
+        <v>14.4</v>
+      </c>
+      <c r="F300">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>153</v>
+      </c>
+      <c r="B301" t="s">
+        <v>191</v>
+      </c>
+      <c r="C301" t="s">
+        <v>198</v>
+      </c>
+      <c r="D301">
+        <v>66</v>
+      </c>
+      <c r="E301">
+        <v>424.06</v>
+      </c>
+      <c r="F301">
+        <v>6.425</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>153</v>
+      </c>
+      <c r="B302" t="s">
+        <v>192</v>
+      </c>
+      <c r="C302" t="s">
+        <v>197</v>
+      </c>
+      <c r="D302">
+        <v>1</v>
+      </c>
+      <c r="E302">
+        <v>3.96</v>
+      </c>
+      <c r="F302">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>153</v>
+      </c>
+      <c r="B303" t="s">
+        <v>190</v>
+      </c>
+      <c r="C303" t="s">
+        <v>197</v>
+      </c>
+      <c r="D303">
+        <v>3</v>
+      </c>
+      <c r="E303">
+        <v>16.32</v>
+      </c>
+      <c r="F303">
+        <v>5.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="229">
   <si>
     <t>Date</t>
   </si>
@@ -478,6 +478,45 @@
     <t>2025-10-12</t>
   </si>
   <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>2025-10-20</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>2025-10-26</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -593,6 +632,36 @@
   </si>
   <si>
     <t>5390</t>
+  </si>
+  <si>
+    <t>5461</t>
+  </si>
+  <si>
+    <t>5508</t>
+  </si>
+  <si>
+    <t>3413</t>
+  </si>
+  <si>
+    <t>3113</t>
+  </si>
+  <si>
+    <t>1219</t>
+  </si>
+  <si>
+    <t>4320</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>4126</t>
+  </si>
+  <si>
+    <t>4390</t>
+  </si>
+  <si>
+    <t>5304</t>
   </si>
   <si>
     <t>N14</t>
@@ -989,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F328"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1020,7 +1089,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1040,7 +1109,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -1060,7 +1129,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -1080,7 +1149,7 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -1100,7 +1169,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -1120,7 +1189,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1140,7 +1209,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -1160,7 +1229,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1180,7 +1249,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -1200,7 +1269,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1220,7 +1289,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -1240,7 +1309,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -1260,7 +1329,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1280,7 +1349,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1300,7 +1369,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1320,7 +1389,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1340,7 +1409,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1360,7 +1429,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1380,7 +1449,7 @@
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1400,7 +1469,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1420,7 +1489,7 @@
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1440,7 +1509,7 @@
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1460,7 +1529,7 @@
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1480,7 +1549,7 @@
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1500,7 +1569,7 @@
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1520,7 +1589,7 @@
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1540,7 +1609,7 @@
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1560,7 +1629,7 @@
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1580,7 +1649,7 @@
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1600,7 +1669,7 @@
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1620,7 +1689,7 @@
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1640,7 +1709,7 @@
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1660,7 +1729,7 @@
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1680,7 +1749,7 @@
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1700,7 +1769,7 @@
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1720,7 +1789,7 @@
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1740,7 +1809,7 @@
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1760,7 +1829,7 @@
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1780,7 +1849,7 @@
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1800,7 +1869,7 @@
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1820,7 +1889,7 @@
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1840,7 +1909,7 @@
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D43">
         <v>50</v>
@@ -1860,7 +1929,7 @@
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1880,7 +1949,7 @@
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1900,7 +1969,7 @@
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1920,7 +1989,7 @@
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1940,7 +2009,7 @@
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -1960,7 +2029,7 @@
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1980,7 +2049,7 @@
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -2000,7 +2069,7 @@
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D51">
         <v>160</v>
@@ -2020,7 +2089,7 @@
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -2040,7 +2109,7 @@
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -2060,7 +2129,7 @@
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2080,7 +2149,7 @@
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2100,7 +2169,7 @@
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2120,7 +2189,7 @@
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2140,7 +2209,7 @@
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2160,7 +2229,7 @@
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -2180,7 +2249,7 @@
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -2200,7 +2269,7 @@
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -2220,7 +2289,7 @@
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -2240,7 +2309,7 @@
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -2260,7 +2329,7 @@
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2280,7 +2349,7 @@
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -2300,7 +2369,7 @@
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2320,7 +2389,7 @@
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2340,7 +2409,7 @@
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2360,7 +2429,7 @@
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2380,7 +2449,7 @@
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2400,7 +2469,7 @@
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2420,7 +2489,7 @@
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D72">
         <v>102</v>
@@ -2440,7 +2509,7 @@
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2460,7 +2529,7 @@
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2480,7 +2549,7 @@
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2500,7 +2569,7 @@
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2520,7 +2589,7 @@
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2540,7 +2609,7 @@
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2560,7 +2629,7 @@
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2580,7 +2649,7 @@
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2600,7 +2669,7 @@
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2620,7 +2689,7 @@
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2640,7 +2709,7 @@
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2660,7 +2729,7 @@
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2680,7 +2749,7 @@
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2700,7 +2769,7 @@
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2720,7 +2789,7 @@
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D87">
         <v>18</v>
@@ -2740,7 +2809,7 @@
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2760,7 +2829,7 @@
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2780,7 +2849,7 @@
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2800,7 +2869,7 @@
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2820,7 +2889,7 @@
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2840,7 +2909,7 @@
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2860,7 +2929,7 @@
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2880,7 +2949,7 @@
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2900,7 +2969,7 @@
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2920,7 +2989,7 @@
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -2940,7 +3009,7 @@
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -2960,7 +3029,7 @@
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -2980,7 +3049,7 @@
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -3000,7 +3069,7 @@
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -3020,7 +3089,7 @@
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -3040,7 +3109,7 @@
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -3060,7 +3129,7 @@
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D104">
         <v>96</v>
@@ -3080,7 +3149,7 @@
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -3100,7 +3169,7 @@
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -3120,7 +3189,7 @@
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D107">
         <v>145</v>
@@ -3140,7 +3209,7 @@
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D108">
         <v>45</v>
@@ -3160,7 +3229,7 @@
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -3180,7 +3249,7 @@
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -3200,7 +3269,7 @@
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D111">
         <v>153</v>
@@ -3220,7 +3289,7 @@
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3240,7 +3309,7 @@
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -3260,7 +3329,7 @@
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3280,7 +3349,7 @@
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3300,7 +3369,7 @@
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3320,7 +3389,7 @@
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3340,7 +3409,7 @@
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D118">
         <v>183</v>
@@ -3360,7 +3429,7 @@
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3380,7 +3449,7 @@
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3400,7 +3469,7 @@
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3420,7 +3489,7 @@
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3440,7 +3509,7 @@
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -3460,7 +3529,7 @@
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D124">
         <v>10</v>
@@ -3480,7 +3549,7 @@
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3500,7 +3569,7 @@
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3520,7 +3589,7 @@
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3540,7 +3609,7 @@
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3560,7 +3629,7 @@
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3580,7 +3649,7 @@
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3600,7 +3669,7 @@
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D131">
         <v>48</v>
@@ -3620,7 +3689,7 @@
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3640,7 +3709,7 @@
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3660,7 +3729,7 @@
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3680,7 +3749,7 @@
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3700,7 +3769,7 @@
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3720,7 +3789,7 @@
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D137">
         <v>48</v>
@@ -3740,7 +3809,7 @@
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3760,7 +3829,7 @@
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3780,7 +3849,7 @@
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3800,7 +3869,7 @@
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3820,7 +3889,7 @@
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3840,7 +3909,7 @@
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3860,7 +3929,7 @@
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3880,7 +3949,7 @@
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3900,7 +3969,7 @@
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -3920,7 +3989,7 @@
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3940,7 +4009,7 @@
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -3960,7 +4029,7 @@
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -3980,7 +4049,7 @@
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -4000,7 +4069,7 @@
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -4020,7 +4089,7 @@
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -4040,7 +4109,7 @@
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -4060,7 +4129,7 @@
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -4080,7 +4149,7 @@
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -4100,7 +4169,7 @@
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -4120,7 +4189,7 @@
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -4140,7 +4209,7 @@
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -4160,7 +4229,7 @@
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -4180,7 +4249,7 @@
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -4200,7 +4269,7 @@
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -4220,7 +4289,7 @@
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -4240,7 +4309,7 @@
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -4260,7 +4329,7 @@
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4280,7 +4349,7 @@
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4300,7 +4369,7 @@
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4320,7 +4389,7 @@
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4340,7 +4409,7 @@
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4360,7 +4429,7 @@
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4380,7 +4449,7 @@
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4400,7 +4469,7 @@
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D171">
         <v>18</v>
@@ -4420,7 +4489,7 @@
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4440,7 +4509,7 @@
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4460,7 +4529,7 @@
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4480,7 +4549,7 @@
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4500,7 +4569,7 @@
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4520,7 +4589,7 @@
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4540,7 +4609,7 @@
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4560,7 +4629,7 @@
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4580,7 +4649,7 @@
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4600,7 +4669,7 @@
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4620,7 +4689,7 @@
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4640,7 +4709,7 @@
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4660,7 +4729,7 @@
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4680,7 +4749,7 @@
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4700,7 +4769,7 @@
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4720,7 +4789,7 @@
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4740,7 +4809,7 @@
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4760,7 +4829,7 @@
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4780,7 +4849,7 @@
         <v>4241</v>
       </c>
       <c r="C190" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -4800,7 +4869,7 @@
         <v>4412</v>
       </c>
       <c r="C191" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D191">
         <v>4</v>
@@ -4820,7 +4889,7 @@
         <v>5208</v>
       </c>
       <c r="C192" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -4840,7 +4909,7 @@
         <v>4412</v>
       </c>
       <c r="C193" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D193">
         <v>116</v>
@@ -4860,7 +4929,7 @@
         <v>1107</v>
       </c>
       <c r="C194" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4880,7 +4949,7 @@
         <v>3115</v>
       </c>
       <c r="C195" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D195">
         <v>148</v>
@@ -4900,7 +4969,7 @@
         <v>5440</v>
       </c>
       <c r="C196" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D196">
         <v>114</v>
@@ -4920,7 +4989,7 @@
         <v>5441</v>
       </c>
       <c r="C197" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D197">
         <v>57</v>
@@ -4940,7 +5009,7 @@
         <v>3115</v>
       </c>
       <c r="C198" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D198">
         <v>40</v>
@@ -4960,7 +5029,7 @@
         <v>5208</v>
       </c>
       <c r="C199" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -4980,7 +5049,7 @@
         <v>5440</v>
       </c>
       <c r="C200" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D200">
         <v>111</v>
@@ -5000,7 +5069,7 @@
         <v>3115</v>
       </c>
       <c r="C201" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D201">
         <v>6</v>
@@ -5020,7 +5089,7 @@
         <v>4129</v>
       </c>
       <c r="C202" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D202">
         <v>89</v>
@@ -5040,7 +5109,7 @@
         <v>4129</v>
       </c>
       <c r="C203" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D203">
         <v>80</v>
@@ -5060,7 +5129,7 @@
         <v>3317</v>
       </c>
       <c r="C204" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D204">
         <v>204</v>
@@ -5080,7 +5149,7 @@
         <v>3317</v>
       </c>
       <c r="C205" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -5100,7 +5169,7 @@
         <v>1215</v>
       </c>
       <c r="C206" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D206">
         <v>151</v>
@@ -5120,7 +5189,7 @@
         <v>1215</v>
       </c>
       <c r="C207" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D207">
         <v>2</v>
@@ -5140,7 +5209,7 @@
         <v>3317</v>
       </c>
       <c r="C208" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -5160,7 +5229,7 @@
         <v>4239</v>
       </c>
       <c r="C209" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="D209">
         <v>48</v>
@@ -5180,7 +5249,7 @@
         <v>4209</v>
       </c>
       <c r="C210" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D210">
         <v>69</v>
@@ -5200,7 +5269,7 @@
         <v>4209</v>
       </c>
       <c r="C211" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -5217,10 +5286,10 @@
         <v>112</v>
       </c>
       <c r="B212" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C212" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D212">
         <v>137</v>
@@ -5237,10 +5306,10 @@
         <v>113</v>
       </c>
       <c r="B213" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C213" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D213">
         <v>178</v>
@@ -5257,10 +5326,10 @@
         <v>113</v>
       </c>
       <c r="B214" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C214" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D214">
         <v>22</v>
@@ -5277,10 +5346,10 @@
         <v>114</v>
       </c>
       <c r="B215" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C215" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D215">
         <v>29</v>
@@ -5297,10 +5366,10 @@
         <v>114</v>
       </c>
       <c r="B216" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C216" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -5317,10 +5386,10 @@
         <v>114</v>
       </c>
       <c r="B217" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C217" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -5337,10 +5406,10 @@
         <v>115</v>
       </c>
       <c r="B218" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C218" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -5357,10 +5426,10 @@
         <v>115</v>
       </c>
       <c r="B219" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C219" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D219">
         <v>216</v>
@@ -5377,10 +5446,10 @@
         <v>116</v>
       </c>
       <c r="B220" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C220" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -5397,10 +5466,10 @@
         <v>117</v>
       </c>
       <c r="B221" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C221" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5417,10 +5486,10 @@
         <v>117</v>
       </c>
       <c r="B222" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C222" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D222">
         <v>263</v>
@@ -5437,10 +5506,10 @@
         <v>118</v>
       </c>
       <c r="B223" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C223" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D223">
         <v>38</v>
@@ -5457,10 +5526,10 @@
         <v>118</v>
       </c>
       <c r="B224" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C224" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D224">
         <v>152</v>
@@ -5477,10 +5546,10 @@
         <v>119</v>
       </c>
       <c r="B225" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C225" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D225">
         <v>184</v>
@@ -5497,10 +5566,10 @@
         <v>119</v>
       </c>
       <c r="B226" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C226" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D226">
         <v>2</v>
@@ -5517,10 +5586,10 @@
         <v>120</v>
       </c>
       <c r="B227" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C227" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D227">
         <v>2</v>
@@ -5537,10 +5606,10 @@
         <v>120</v>
       </c>
       <c r="B228" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C228" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D228">
         <v>2</v>
@@ -5557,10 +5626,10 @@
         <v>121</v>
       </c>
       <c r="B229" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C229" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D229">
         <v>44</v>
@@ -5577,10 +5646,10 @@
         <v>122</v>
       </c>
       <c r="B230" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C230" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D230">
         <v>36</v>
@@ -5597,10 +5666,10 @@
         <v>122</v>
       </c>
       <c r="B231" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C231" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D231">
         <v>12</v>
@@ -5617,10 +5686,10 @@
         <v>123</v>
       </c>
       <c r="B232" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C232" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5637,10 +5706,10 @@
         <v>123</v>
       </c>
       <c r="B233" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C233" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D233">
         <v>2</v>
@@ -5657,10 +5726,10 @@
         <v>123</v>
       </c>
       <c r="B234" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C234" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5677,10 +5746,10 @@
         <v>123</v>
       </c>
       <c r="B235" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C235" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D235">
         <v>83</v>
@@ -5697,10 +5766,10 @@
         <v>123</v>
       </c>
       <c r="B236" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C236" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D236">
         <v>55</v>
@@ -5717,10 +5786,10 @@
         <v>124</v>
       </c>
       <c r="B237" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C237" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D237">
         <v>52</v>
@@ -5737,10 +5806,10 @@
         <v>125</v>
       </c>
       <c r="B238" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C238" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D238">
         <v>137</v>
@@ -5757,10 +5826,10 @@
         <v>125</v>
       </c>
       <c r="B239" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C239" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -5777,10 +5846,10 @@
         <v>126</v>
       </c>
       <c r="B240" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C240" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D240">
         <v>110</v>
@@ -5797,10 +5866,10 @@
         <v>126</v>
       </c>
       <c r="B241" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C241" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D241">
         <v>194</v>
@@ -5817,10 +5886,10 @@
         <v>127</v>
       </c>
       <c r="B242" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C242" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D242">
         <v>4</v>
@@ -5837,10 +5906,10 @@
         <v>128</v>
       </c>
       <c r="B243" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C243" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D243">
         <v>2</v>
@@ -5857,10 +5926,10 @@
         <v>129</v>
       </c>
       <c r="B244" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C244" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D244">
         <v>142</v>
@@ -5877,10 +5946,10 @@
         <v>130</v>
       </c>
       <c r="B245" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C245" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D245">
         <v>28</v>
@@ -5897,10 +5966,10 @@
         <v>130</v>
       </c>
       <c r="B246" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C246" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D246">
         <v>153</v>
@@ -5917,10 +5986,10 @@
         <v>131</v>
       </c>
       <c r="B247" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C247" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D247">
         <v>138</v>
@@ -5937,10 +6006,10 @@
         <v>132</v>
       </c>
       <c r="B248" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C248" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D248">
         <v>153</v>
@@ -5957,10 +6026,10 @@
         <v>133</v>
       </c>
       <c r="B249" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C249" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D249">
         <v>30</v>
@@ -5977,10 +6046,10 @@
         <v>133</v>
       </c>
       <c r="B250" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C250" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -5997,10 +6066,10 @@
         <v>133</v>
       </c>
       <c r="B251" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C251" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D251">
         <v>102</v>
@@ -6017,10 +6086,10 @@
         <v>133</v>
       </c>
       <c r="B252" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C252" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -6037,10 +6106,10 @@
         <v>133</v>
       </c>
       <c r="B253" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C253" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -6057,10 +6126,10 @@
         <v>134</v>
       </c>
       <c r="B254" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C254" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D254">
         <v>24</v>
@@ -6077,10 +6146,10 @@
         <v>134</v>
       </c>
       <c r="B255" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C255" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -6097,10 +6166,10 @@
         <v>135</v>
       </c>
       <c r="B256" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C256" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D256">
         <v>102</v>
@@ -6117,10 +6186,10 @@
         <v>135</v>
       </c>
       <c r="B257" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C257" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D257">
         <v>142</v>
@@ -6137,10 +6206,10 @@
         <v>136</v>
       </c>
       <c r="B258" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C258" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D258">
         <v>4</v>
@@ -6157,10 +6226,10 @@
         <v>137</v>
       </c>
       <c r="B259" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C259" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -6177,10 +6246,10 @@
         <v>137</v>
       </c>
       <c r="B260" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C260" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D260">
         <v>5</v>
@@ -6197,10 +6266,10 @@
         <v>138</v>
       </c>
       <c r="B261" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C261" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D261">
         <v>2</v>
@@ -6217,10 +6286,10 @@
         <v>138</v>
       </c>
       <c r="B262" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C262" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D262">
         <v>118</v>
@@ -6237,10 +6306,10 @@
         <v>139</v>
       </c>
       <c r="B263" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C263" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D263">
         <v>2</v>
@@ -6257,10 +6326,10 @@
         <v>139</v>
       </c>
       <c r="B264" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C264" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D264">
         <v>76</v>
@@ -6277,10 +6346,10 @@
         <v>139</v>
       </c>
       <c r="B265" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C265" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D265">
         <v>6</v>
@@ -6297,10 +6366,10 @@
         <v>140</v>
       </c>
       <c r="B266" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C266" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D266">
         <v>210</v>
@@ -6317,10 +6386,10 @@
         <v>140</v>
       </c>
       <c r="B267" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C267" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -6337,10 +6406,10 @@
         <v>140</v>
       </c>
       <c r="B268" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C268" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -6357,10 +6426,10 @@
         <v>141</v>
       </c>
       <c r="B269" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C269" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D269">
         <v>157</v>
@@ -6377,10 +6446,10 @@
         <v>141</v>
       </c>
       <c r="B270" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C270" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -6397,10 +6466,10 @@
         <v>142</v>
       </c>
       <c r="B271" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C271" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D271">
         <v>5</v>
@@ -6417,10 +6486,10 @@
         <v>142</v>
       </c>
       <c r="B272" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C272" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D272">
         <v>129</v>
@@ -6437,10 +6506,10 @@
         <v>143</v>
       </c>
       <c r="B273" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C273" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D273">
         <v>93</v>
@@ -6457,10 +6526,10 @@
         <v>143</v>
       </c>
       <c r="B274" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C274" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D274">
         <v>102</v>
@@ -6477,10 +6546,10 @@
         <v>144</v>
       </c>
       <c r="B275" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C275" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -6497,10 +6566,10 @@
         <v>144</v>
       </c>
       <c r="B276" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C276" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -6517,10 +6586,10 @@
         <v>144</v>
       </c>
       <c r="B277" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C277" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D277">
         <v>2</v>
@@ -6537,10 +6606,10 @@
         <v>144</v>
       </c>
       <c r="B278" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C278" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D278">
         <v>102</v>
@@ -6557,10 +6626,10 @@
         <v>145</v>
       </c>
       <c r="B279" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C279" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D279">
         <v>202</v>
@@ -6577,10 +6646,10 @@
         <v>145</v>
       </c>
       <c r="B280" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C280" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D280">
         <v>1</v>
@@ -6597,10 +6666,10 @@
         <v>146</v>
       </c>
       <c r="B281" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C281" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D281">
         <v>205</v>
@@ -6617,10 +6686,10 @@
         <v>146</v>
       </c>
       <c r="B282" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C282" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D282">
         <v>1</v>
@@ -6637,10 +6706,10 @@
         <v>146</v>
       </c>
       <c r="B283" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C283" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D283">
         <v>9</v>
@@ -6657,10 +6726,10 @@
         <v>147</v>
       </c>
       <c r="B284" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C284" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D284">
         <v>1</v>
@@ -6677,10 +6746,10 @@
         <v>147</v>
       </c>
       <c r="B285" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C285" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -6697,10 +6766,10 @@
         <v>147</v>
       </c>
       <c r="B286" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C286" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -6717,10 +6786,10 @@
         <v>147</v>
       </c>
       <c r="B287" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C287" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D287">
         <v>180</v>
@@ -6737,10 +6806,10 @@
         <v>148</v>
       </c>
       <c r="B288" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C288" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D288">
         <v>2</v>
@@ -6757,10 +6826,10 @@
         <v>148</v>
       </c>
       <c r="B289" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C289" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D289">
         <v>2</v>
@@ -6777,10 +6846,10 @@
         <v>149</v>
       </c>
       <c r="B290" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C290" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D290">
         <v>96</v>
@@ -6797,10 +6866,10 @@
         <v>149</v>
       </c>
       <c r="B291" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C291" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D291">
         <v>6</v>
@@ -6817,10 +6886,10 @@
         <v>149</v>
       </c>
       <c r="B292" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C292" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D292">
         <v>51</v>
@@ -6837,10 +6906,10 @@
         <v>149</v>
       </c>
       <c r="B293" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C293" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D293">
         <v>4</v>
@@ -6857,10 +6926,10 @@
         <v>150</v>
       </c>
       <c r="B294" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C294" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D294">
         <v>136</v>
@@ -6877,10 +6946,10 @@
         <v>150</v>
       </c>
       <c r="B295" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C295" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D295">
         <v>35</v>
@@ -6897,10 +6966,10 @@
         <v>150</v>
       </c>
       <c r="B296" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C296" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D296">
         <v>59</v>
@@ -6917,10 +6986,10 @@
         <v>151</v>
       </c>
       <c r="B297" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C297" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D297">
         <v>17</v>
@@ -6937,10 +7006,10 @@
         <v>151</v>
       </c>
       <c r="B298" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C298" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D298">
         <v>106</v>
@@ -6957,10 +7026,10 @@
         <v>152</v>
       </c>
       <c r="B299" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C299" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D299">
         <v>247</v>
@@ -6977,10 +7046,10 @@
         <v>153</v>
       </c>
       <c r="B300" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C300" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="D300">
         <v>2</v>
@@ -6997,10 +7066,10 @@
         <v>153</v>
       </c>
       <c r="B301" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C301" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="D301">
         <v>66</v>
@@ -7017,10 +7086,10 @@
         <v>153</v>
       </c>
       <c r="B302" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C302" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -7037,10 +7106,10 @@
         <v>153</v>
       </c>
       <c r="B303" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C303" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D303">
         <v>3</v>
@@ -7050,6 +7119,506 @@
       </c>
       <c r="F303">
         <v>5.44</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>154</v>
+      </c>
+      <c r="B304" t="s">
+        <v>204</v>
+      </c>
+      <c r="C304" t="s">
+        <v>221</v>
+      </c>
+      <c r="D304">
+        <v>7</v>
+      </c>
+      <c r="E304">
+        <v>42.48</v>
+      </c>
+      <c r="F304">
+        <v>6.069</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" t="s">
+        <v>155</v>
+      </c>
+      <c r="B305" t="s">
+        <v>204</v>
+      </c>
+      <c r="C305" t="s">
+        <v>221</v>
+      </c>
+      <c r="D305">
+        <v>5</v>
+      </c>
+      <c r="E305">
+        <v>37.38</v>
+      </c>
+      <c r="F305">
+        <v>7.476</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" t="s">
+        <v>156</v>
+      </c>
+      <c r="B306" t="s">
+        <v>206</v>
+      </c>
+      <c r="C306" t="s">
+        <v>221</v>
+      </c>
+      <c r="D306">
+        <v>30</v>
+      </c>
+      <c r="E306">
+        <v>123.36</v>
+      </c>
+      <c r="F306">
+        <v>4.112</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" t="s">
+        <v>156</v>
+      </c>
+      <c r="B307" t="s">
+        <v>207</v>
+      </c>
+      <c r="C307" t="s">
+        <v>220</v>
+      </c>
+      <c r="D307">
+        <v>192</v>
+      </c>
+      <c r="E307">
+        <v>1154.76</v>
+      </c>
+      <c r="F307">
+        <v>6.014</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" t="s">
+        <v>157</v>
+      </c>
+      <c r="B308" t="s">
+        <v>208</v>
+      </c>
+      <c r="C308" t="s">
+        <v>221</v>
+      </c>
+      <c r="D308">
+        <v>88</v>
+      </c>
+      <c r="E308">
+        <v>528.22</v>
+      </c>
+      <c r="F308">
+        <v>6.003</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" t="s">
+        <v>157</v>
+      </c>
+      <c r="B309" t="s">
+        <v>206</v>
+      </c>
+      <c r="C309" t="s">
+        <v>221</v>
+      </c>
+      <c r="D309">
+        <v>91</v>
+      </c>
+      <c r="E309">
+        <v>378.34</v>
+      </c>
+      <c r="F309">
+        <v>4.158</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" t="s">
+        <v>157</v>
+      </c>
+      <c r="B310" t="s">
+        <v>207</v>
+      </c>
+      <c r="C310" t="s">
+        <v>221</v>
+      </c>
+      <c r="D310">
+        <v>1</v>
+      </c>
+      <c r="E310">
+        <v>13.14</v>
+      </c>
+      <c r="F310">
+        <v>13.14</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" t="s">
+        <v>158</v>
+      </c>
+      <c r="B311" t="s">
+        <v>209</v>
+      </c>
+      <c r="C311" t="s">
+        <v>226</v>
+      </c>
+      <c r="D311">
+        <v>72</v>
+      </c>
+      <c r="E311">
+        <v>424.58</v>
+      </c>
+      <c r="F311">
+        <v>5.897</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" t="s">
+        <v>158</v>
+      </c>
+      <c r="B312" t="s">
+        <v>208</v>
+      </c>
+      <c r="C312" t="s">
+        <v>221</v>
+      </c>
+      <c r="D312">
+        <v>70</v>
+      </c>
+      <c r="E312">
+        <v>438.7</v>
+      </c>
+      <c r="F312">
+        <v>6.267</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>158</v>
+      </c>
+      <c r="B313" t="s">
+        <v>206</v>
+      </c>
+      <c r="C313" t="s">
+        <v>221</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313">
+        <v>102.52</v>
+      </c>
+      <c r="F313">
+        <v>4.272</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" t="s">
+        <v>159</v>
+      </c>
+      <c r="B314" t="s">
+        <v>210</v>
+      </c>
+      <c r="C314" t="s">
+        <v>218</v>
+      </c>
+      <c r="D314">
+        <v>143</v>
+      </c>
+      <c r="E314">
+        <v>981.1</v>
+      </c>
+      <c r="F314">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" t="s">
+        <v>159</v>
+      </c>
+      <c r="B315" t="s">
+        <v>209</v>
+      </c>
+      <c r="C315" t="s">
+        <v>218</v>
+      </c>
+      <c r="D315">
+        <v>96</v>
+      </c>
+      <c r="E315">
+        <v>573.04</v>
+      </c>
+      <c r="F315">
+        <v>5.969</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" t="s">
+        <v>159</v>
+      </c>
+      <c r="B316" t="s">
+        <v>208</v>
+      </c>
+      <c r="C316" t="s">
+        <v>218</v>
+      </c>
+      <c r="D316">
+        <v>3</v>
+      </c>
+      <c r="E316">
+        <v>21.18</v>
+      </c>
+      <c r="F316">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" t="s">
+        <v>159</v>
+      </c>
+      <c r="B317" t="s">
+        <v>206</v>
+      </c>
+      <c r="C317" t="s">
+        <v>221</v>
+      </c>
+      <c r="D317">
+        <v>5</v>
+      </c>
+      <c r="E317">
+        <v>27.22</v>
+      </c>
+      <c r="F317">
+        <v>5.444</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" t="s">
+        <v>160</v>
+      </c>
+      <c r="B318" t="s">
+        <v>209</v>
+      </c>
+      <c r="C318" t="s">
+        <v>218</v>
+      </c>
+      <c r="D318">
+        <v>2</v>
+      </c>
+      <c r="E318">
+        <v>13.02</v>
+      </c>
+      <c r="F318">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" t="s">
+        <v>160</v>
+      </c>
+      <c r="B319" t="s">
+        <v>211</v>
+      </c>
+      <c r="C319" t="s">
+        <v>220</v>
+      </c>
+      <c r="D319">
+        <v>102</v>
+      </c>
+      <c r="E319">
+        <v>660.1</v>
+      </c>
+      <c r="F319">
+        <v>6.472</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" t="s">
+        <v>161</v>
+      </c>
+      <c r="B320" t="s">
+        <v>209</v>
+      </c>
+      <c r="C320" t="s">
+        <v>218</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
+      </c>
+      <c r="E320">
+        <v>9.24</v>
+      </c>
+      <c r="F320">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" t="s">
+        <v>162</v>
+      </c>
+      <c r="B321" t="s">
+        <v>211</v>
+      </c>
+      <c r="C321" t="s">
+        <v>221</v>
+      </c>
+      <c r="D321">
+        <v>4</v>
+      </c>
+      <c r="E321">
+        <v>30.52</v>
+      </c>
+      <c r="F321">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" t="s">
+        <v>163</v>
+      </c>
+      <c r="B322" t="s">
+        <v>212</v>
+      </c>
+      <c r="C322" t="s">
+        <v>218</v>
+      </c>
+      <c r="D322">
+        <v>199</v>
+      </c>
+      <c r="E322">
+        <v>1393.88</v>
+      </c>
+      <c r="F322">
+        <v>7.004</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" t="s">
+        <v>164</v>
+      </c>
+      <c r="B323" t="s">
+        <v>212</v>
+      </c>
+      <c r="C323" t="s">
+        <v>218</v>
+      </c>
+      <c r="D323">
+        <v>6</v>
+      </c>
+      <c r="E323">
+        <v>38.46</v>
+      </c>
+      <c r="F323">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" t="s">
+        <v>164</v>
+      </c>
+      <c r="B324" t="s">
+        <v>213</v>
+      </c>
+      <c r="C324" t="s">
+        <v>218</v>
+      </c>
+      <c r="D324">
+        <v>184</v>
+      </c>
+      <c r="E324">
+        <v>1300.74</v>
+      </c>
+      <c r="F324">
+        <v>7.069</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" t="s">
+        <v>164</v>
+      </c>
+      <c r="B325" t="s">
+        <v>214</v>
+      </c>
+      <c r="C325" t="s">
+        <v>221</v>
+      </c>
+      <c r="D325">
+        <v>18</v>
+      </c>
+      <c r="E325">
+        <v>42.36</v>
+      </c>
+      <c r="F325">
+        <v>2.353</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" t="s">
+        <v>165</v>
+      </c>
+      <c r="B326" t="s">
+        <v>212</v>
+      </c>
+      <c r="C326" t="s">
+        <v>218</v>
+      </c>
+      <c r="D326">
+        <v>1</v>
+      </c>
+      <c r="E326">
+        <v>9.76</v>
+      </c>
+      <c r="F326">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" t="s">
+        <v>165</v>
+      </c>
+      <c r="B327" t="s">
+        <v>215</v>
+      </c>
+      <c r="C327" t="s">
+        <v>218</v>
+      </c>
+      <c r="D327">
+        <v>310</v>
+      </c>
+      <c r="E327">
+        <v>1950.6</v>
+      </c>
+      <c r="F327">
+        <v>6.292</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" t="s">
+        <v>166</v>
+      </c>
+      <c r="B328" t="s">
+        <v>213</v>
+      </c>
+      <c r="C328" t="s">
+        <v>218</v>
+      </c>
+      <c r="D328">
+        <v>7</v>
+      </c>
+      <c r="E328">
+        <v>52.54</v>
+      </c>
+      <c r="F328">
+        <v>7.506</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="277">
   <si>
     <t>Date</t>
   </si>
@@ -73,9 +78,6 @@
     <t>2025-05-11</t>
   </si>
   <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
     <t>2025-05-14</t>
   </si>
   <si>
@@ -517,6 +519,93 @@
     <t>2025-10-27</t>
   </si>
   <si>
+    <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-01</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>2025-11-08</t>
+  </si>
+  <si>
+    <t>2025-11-09</t>
+  </si>
+  <si>
+    <t>2025-11-16</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-11-29</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
     <t>5701C</t>
   </si>
   <si>
@@ -662,6 +751,66 @@
   </si>
   <si>
     <t>5304</t>
+  </si>
+  <si>
+    <t>5652</t>
+  </si>
+  <si>
+    <t>5653</t>
+  </si>
+  <si>
+    <t>5108</t>
+  </si>
+  <si>
+    <t>4124</t>
+  </si>
+  <si>
+    <t>5402</t>
+  </si>
+  <si>
+    <t>3111</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>5632</t>
+  </si>
+  <si>
+    <t>3313</t>
+  </si>
+  <si>
+    <t>5502</t>
+  </si>
+  <si>
+    <t>5307</t>
+  </si>
+  <si>
+    <t>4314</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2215</t>
+  </si>
+  <si>
+    <t>2321</t>
+  </si>
+  <si>
+    <t>4214</t>
+  </si>
+  <si>
+    <t>3416</t>
+  </si>
+  <si>
+    <t>5633</t>
+  </si>
+  <si>
+    <t>5459</t>
+  </si>
+  <si>
+    <t>2112</t>
   </si>
   <si>
     <t>N14</t>
@@ -706,8 +855,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,17 +908,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -816,7 +974,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -848,9 +1006,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -882,6 +1041,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1057,11 +1217,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F328"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F373"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1089,7 +1252,7 @@
         <v>5290</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1101,7 +1264,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1109,7 +1272,7 @@
         <v>5290</v>
       </c>
       <c r="C3" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -1118,10 +1281,10 @@
         <v>441.88</v>
       </c>
       <c r="F3">
-        <v>7.127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>7.1269999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1292,7 @@
         <v>5290</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D4">
         <v>18</v>
@@ -1138,10 +1301,10 @@
         <v>111.36</v>
       </c>
       <c r="F4">
-        <v>6.187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>6.1870000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1149,19 +1312,19 @@
         <v>3109</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D5">
         <v>80</v>
       </c>
       <c r="E5">
-        <v>565.2</v>
+        <v>565.20000000000005</v>
       </c>
       <c r="F5">
-        <v>7.065</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>7.0650000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1169,7 +1332,7 @@
         <v>5217</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D6">
         <v>58</v>
@@ -1178,10 +1341,10 @@
         <v>394.9</v>
       </c>
       <c r="F6">
-        <v>6.809</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>6.8090000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1189,7 +1352,7 @@
         <v>5217</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1201,7 +1364,7 @@
         <v>7.048</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1209,7 +1372,7 @@
         <v>2405</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D8">
         <v>136</v>
@@ -1218,10 +1381,10 @@
         <v>907.66</v>
       </c>
       <c r="F8">
-        <v>6.674</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>6.6740000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1229,7 +1392,7 @@
         <v>5217</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1238,10 +1401,10 @@
         <v>28.46</v>
       </c>
       <c r="F9">
-        <v>7.115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>7.1150000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1412,7 @@
         <v>4222</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D10">
         <v>87</v>
@@ -1258,10 +1421,10 @@
         <v>471.2</v>
       </c>
       <c r="F10">
-        <v>5.416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>5.4160000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1269,7 +1432,7 @@
         <v>3109</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1281,7 +1444,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1289,7 +1452,7 @@
         <v>4224</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D12">
         <v>51</v>
@@ -1298,10 +1461,10 @@
         <v>298.52</v>
       </c>
       <c r="F12">
-        <v>5.853</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>5.8529999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1472,7 @@
         <v>5217</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D13">
         <v>89</v>
@@ -1318,10 +1481,10 @@
         <v>563.28</v>
       </c>
       <c r="F13">
-        <v>6.329</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>6.3289999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1492,7 @@
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1338,10 +1501,10 @@
         <v>53.3</v>
       </c>
       <c r="F14">
-        <v>7.614</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>7.6139999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1349,7 +1512,7 @@
         <v>2205</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D15">
         <v>42</v>
@@ -1358,10 +1521,10 @@
         <v>292.26</v>
       </c>
       <c r="F15">
-        <v>6.959</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>6.9589999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1369,7 +1532,7 @@
         <v>2405</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1378,10 +1541,10 @@
         <v>58.26</v>
       </c>
       <c r="F16">
-        <v>5.826</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>5.8259999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1389,7 +1552,7 @@
         <v>5217</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1398,10 +1561,10 @@
         <v>35.06</v>
       </c>
       <c r="F17">
-        <v>7.012</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>7.0119999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1409,7 +1572,7 @@
         <v>2405</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1421,7 +1584,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1429,7 +1592,7 @@
         <v>2205</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D19">
         <v>173</v>
@@ -1441,15 +1604,15 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>19</v>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45788</v>
       </c>
       <c r="B20">
         <v>2304</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D20">
         <v>77</v>
@@ -1458,10 +1621,10 @@
         <v>480.8</v>
       </c>
       <c r="F20">
-        <v>6.244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>6.2439999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1469,7 +1632,7 @@
         <v>4224</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1478,18 +1641,18 @@
         <v>24.62</v>
       </c>
       <c r="F21">
-        <v>8.207000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>8.2070000000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22">
         <v>2205</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1498,18 +1661,18 @@
         <v>20.02</v>
       </c>
       <c r="F22">
-        <v>5.005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>5.0049999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>2207</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D23">
         <v>54</v>
@@ -1518,18 +1681,18 @@
         <v>252.5</v>
       </c>
       <c r="F23">
-        <v>4.676</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>4.6760000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>2207</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D24">
         <v>87</v>
@@ -1541,15 +1704,15 @@
         <v>4.306</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>1112</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -1558,18 +1721,18 @@
         <v>623.54</v>
       </c>
       <c r="F25">
-        <v>6.235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>6.2350000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26">
         <v>2205</v>
       </c>
       <c r="C26" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -1578,18 +1741,18 @@
         <v>60.34</v>
       </c>
       <c r="F26">
-        <v>5.028</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>5.0279999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27">
         <v>2207</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D27">
         <v>21</v>
@@ -1601,15 +1764,15 @@
         <v>3.931</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28">
         <v>4107</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -1618,18 +1781,18 @@
         <v>285.12</v>
       </c>
       <c r="F28">
-        <v>7.706</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>7.7060000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29">
         <v>2207</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D29">
         <v>22</v>
@@ -1638,58 +1801,58 @@
         <v>91.5</v>
       </c>
       <c r="F29">
-        <v>4.159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>4.1589999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30">
         <v>2205</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>38.34</v>
+        <v>38.340000000000003</v>
       </c>
       <c r="F30">
-        <v>7.668</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>7.6680000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31">
         <v>4107</v>
       </c>
       <c r="C31" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31">
-        <v>37.12</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="F31">
-        <v>6.187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>6.1870000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32">
         <v>5219</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D32">
         <v>69</v>
@@ -1698,18 +1861,18 @@
         <v>501.74</v>
       </c>
       <c r="F32">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>7.2720000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33">
         <v>2207</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1721,15 +1884,15 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <v>2207</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1741,15 +1904,15 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35">
         <v>5219</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D35">
         <v>17</v>
@@ -1758,18 +1921,18 @@
         <v>119.64</v>
       </c>
       <c r="F35">
-        <v>7.038</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>7.0380000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36">
         <v>4311</v>
       </c>
       <c r="C36" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D36">
         <v>121</v>
@@ -1778,18 +1941,18 @@
         <v>821.88</v>
       </c>
       <c r="F36">
-        <v>6.792</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>6.7919999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37">
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1801,15 +1964,15 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>1112</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1821,15 +1984,15 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>2106</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D39">
         <v>54</v>
@@ -1838,18 +2001,18 @@
         <v>356.74</v>
       </c>
       <c r="F39">
-        <v>6.606</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>6.6059999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>4107</v>
       </c>
       <c r="C40" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1861,15 +2024,15 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>5216</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -1878,18 +2041,18 @@
         <v>564.5</v>
       </c>
       <c r="F41">
-        <v>6.969</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>6.9690000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>5510</v>
       </c>
       <c r="C42" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D42">
         <v>31</v>
@@ -1901,35 +2064,35 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>5513</v>
       </c>
       <c r="C43" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D43">
         <v>50</v>
       </c>
       <c r="E43">
-        <v>326.34</v>
+        <v>326.33999999999997</v>
       </c>
       <c r="F43">
         <v>6.53</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44">
         <v>1125</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D44">
         <v>94</v>
@@ -1938,18 +2101,18 @@
         <v>680.3</v>
       </c>
       <c r="F44">
-        <v>7.237</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>7.2370000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45">
         <v>2106</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1961,15 +2124,15 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46">
         <v>3308</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -1978,18 +2141,18 @@
         <v>87.72</v>
       </c>
       <c r="F46">
-        <v>7.975</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>7.9749999999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>5216</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2001,35 +2164,35 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>3308</v>
       </c>
       <c r="C48" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D48">
         <v>43</v>
       </c>
       <c r="E48">
-        <v>290.54</v>
+        <v>290.54000000000002</v>
       </c>
       <c r="F48">
-        <v>6.757</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>6.7569999999999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>5216</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2041,15 +2204,15 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>2525</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D50">
         <v>18</v>
@@ -2061,35 +2224,35 @@
         <v>5.944</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>2526</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D51">
         <v>160</v>
       </c>
       <c r="E51">
-        <v>961.9400000000001</v>
+        <v>961.94</v>
       </c>
       <c r="F51">
-        <v>6.012</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>6.0119999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>2526</v>
       </c>
       <c r="C52" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D52">
         <v>103</v>
@@ -2098,18 +2261,18 @@
         <v>563.96</v>
       </c>
       <c r="F52">
-        <v>5.475</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>5.4749999999999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53">
         <v>4104</v>
       </c>
       <c r="C53" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D53">
         <v>66</v>
@@ -2118,18 +2281,18 @@
         <v>499.12</v>
       </c>
       <c r="F53">
-        <v>7.562</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>7.5620000000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54">
         <v>4311</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2141,35 +2304,35 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55">
         <v>5216</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="E55">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="F55">
-        <v>8.380000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56">
         <v>1125</v>
       </c>
       <c r="C56" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2178,18 +2341,18 @@
         <v>28.1</v>
       </c>
       <c r="F56">
-        <v>7.025</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57">
         <v>2526</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2201,15 +2364,15 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58">
         <v>3308</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2221,15 +2384,15 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59">
         <v>4211</v>
       </c>
       <c r="C59" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D59">
         <v>101</v>
@@ -2238,18 +2401,18 @@
         <v>764.08</v>
       </c>
       <c r="F59">
-        <v>7.565</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>7.5650000000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60">
         <v>5301</v>
       </c>
       <c r="C60" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="D60">
         <v>115</v>
@@ -2258,18 +2421,18 @@
         <v>690.5</v>
       </c>
       <c r="F60">
-        <v>6.004</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>6.0039999999999996</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61">
         <v>5436</v>
       </c>
       <c r="C61" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D61">
         <v>79</v>
@@ -2278,18 +2441,18 @@
         <v>577.1</v>
       </c>
       <c r="F61">
-        <v>7.305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>7.3049999999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62">
         <v>2525</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -2301,15 +2464,15 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63">
         <v>4211</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D63">
         <v>109</v>
@@ -2318,58 +2481,58 @@
         <v>773.26</v>
       </c>
       <c r="F63">
-        <v>7.094</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>7.0940000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64">
         <v>5301</v>
       </c>
       <c r="C64" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
       <c r="E64">
-        <v>20.06</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="F64">
-        <v>6.687</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>6.6870000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65">
         <v>4211</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D65">
         <v>18</v>
       </c>
       <c r="E65">
-        <v>131.48</v>
+        <v>131.47999999999999</v>
       </c>
       <c r="F65">
-        <v>7.304</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>7.3040000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B66">
         <v>5442</v>
       </c>
       <c r="C66" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D66">
         <v>36</v>
@@ -2378,18 +2541,18 @@
         <v>218.06</v>
       </c>
       <c r="F66">
-        <v>6.057</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>6.0570000000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B67">
         <v>5442</v>
       </c>
       <c r="C67" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -2398,18 +2561,18 @@
         <v>218.06</v>
       </c>
       <c r="F67">
-        <v>6.057</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>6.0570000000000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B68">
         <v>5442</v>
       </c>
       <c r="C68" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D68">
         <v>63</v>
@@ -2418,18 +2581,18 @@
         <v>383.5</v>
       </c>
       <c r="F68">
-        <v>6.087</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>6.0869999999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69">
         <v>3302</v>
       </c>
       <c r="C69" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="D69">
         <v>257</v>
@@ -2438,18 +2601,18 @@
         <v>1716.24</v>
       </c>
       <c r="F69">
-        <v>6.678</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>6.6779999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70">
         <v>4211</v>
       </c>
       <c r="C70" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2461,15 +2624,15 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71">
         <v>5211</v>
       </c>
       <c r="C71" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="D71">
         <v>42</v>
@@ -2478,38 +2641,38 @@
         <v>303.56</v>
       </c>
       <c r="F71">
-        <v>7.228</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>7.2279999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72">
         <v>5218</v>
       </c>
       <c r="C72" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D72">
         <v>102</v>
       </c>
       <c r="E72">
-        <v>696.0599999999999</v>
+        <v>696.06</v>
       </c>
       <c r="F72">
-        <v>6.824</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>6.8239999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73">
         <v>3493</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D73">
         <v>125</v>
@@ -2518,18 +2681,18 @@
         <v>745.15</v>
       </c>
       <c r="F73">
-        <v>5.961</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>5.9610000000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B74">
         <v>5454</v>
       </c>
       <c r="C74" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="D74">
         <v>84</v>
@@ -2538,18 +2701,18 @@
         <v>570.22</v>
       </c>
       <c r="F74">
-        <v>6.788</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>6.7880000000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B75">
         <v>3493</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D75">
         <v>18</v>
@@ -2561,15 +2724,15 @@
         <v>5.234</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76">
         <v>3120</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D76">
         <v>229</v>
@@ -2578,18 +2741,18 @@
         <v>1702.44</v>
       </c>
       <c r="F76">
-        <v>7.434</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>7.4340000000000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77">
         <v>5211</v>
       </c>
       <c r="C77" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2598,18 +2761,18 @@
         <v>44.36</v>
       </c>
       <c r="F77">
-        <v>7.393</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>7.3929999999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78">
         <v>1211</v>
       </c>
       <c r="C78" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D78">
         <v>288</v>
@@ -2618,18 +2781,18 @@
         <v>1742.66</v>
       </c>
       <c r="F78">
-        <v>6.051</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>6.0510000000000002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B79">
         <v>3302</v>
       </c>
       <c r="C79" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="D79">
         <v>18</v>
@@ -2638,18 +2801,18 @@
         <v>120.66</v>
       </c>
       <c r="F79">
-        <v>6.703</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>6.7030000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B80">
         <v>2307</v>
       </c>
       <c r="C80" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D80">
         <v>36</v>
@@ -2658,18 +2821,18 @@
         <v>244.56</v>
       </c>
       <c r="F80">
-        <v>6.793</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>6.7930000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B81">
         <v>5218</v>
       </c>
       <c r="C81" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2681,15 +2844,15 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82">
         <v>2307</v>
       </c>
       <c r="C82" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D82">
         <v>121</v>
@@ -2698,18 +2861,18 @@
         <v>761.2</v>
       </c>
       <c r="F82">
-        <v>6.291</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>6.2910000000000004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B83">
         <v>3120</v>
       </c>
       <c r="C83" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D83">
         <v>8</v>
@@ -2721,15 +2884,15 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B84">
         <v>3120</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2741,15 +2904,15 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B85">
         <v>3493</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2761,15 +2924,15 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B86">
         <v>4208</v>
       </c>
       <c r="C86" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D86">
         <v>59</v>
@@ -2781,35 +2944,35 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B87">
         <v>5204</v>
       </c>
       <c r="C87" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="D87">
         <v>18</v>
       </c>
       <c r="E87">
-        <v>90.45999999999999</v>
+        <v>90.46</v>
       </c>
       <c r="F87">
-        <v>5.026</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+        <v>5.0259999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B88">
         <v>2302</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D88">
         <v>86</v>
@@ -2818,18 +2981,18 @@
         <v>483.14</v>
       </c>
       <c r="F88">
-        <v>5.618</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+        <v>5.6180000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B89">
         <v>4208</v>
       </c>
       <c r="C89" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D89">
         <v>71</v>
@@ -2838,18 +3001,18 @@
         <v>484.48</v>
       </c>
       <c r="F89">
-        <v>6.824</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>6.8239999999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B90">
         <v>5204</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="D90">
         <v>164</v>
@@ -2858,18 +3021,18 @@
         <v>1104.02</v>
       </c>
       <c r="F90">
-        <v>6.732</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>6.7320000000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B91">
         <v>5117</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2878,18 +3041,18 @@
         <v>131</v>
       </c>
       <c r="F91">
-        <v>6.238</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>6.2380000000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B92">
         <v>5101</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D92">
         <v>221</v>
@@ -2898,18 +3061,18 @@
         <v>1438.98</v>
       </c>
       <c r="F92">
-        <v>6.511</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>6.5110000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B93">
         <v>1221</v>
       </c>
       <c r="C93" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D93">
         <v>139</v>
@@ -2918,18 +3081,18 @@
         <v>976.02</v>
       </c>
       <c r="F93">
-        <v>7.022</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>7.0220000000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B94">
         <v>5101</v>
       </c>
       <c r="C94" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2941,15 +3104,15 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B95">
         <v>2307</v>
       </c>
       <c r="C95" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -2958,18 +3121,18 @@
         <v>55.22</v>
       </c>
       <c r="F95">
-        <v>6.902</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>6.9020000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B96">
         <v>5113</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="D96">
         <v>174</v>
@@ -2981,35 +3144,35 @@
         <v>6.569</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B97">
         <v>1211</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>9.460000000000001</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="F97">
-        <v>9.460000000000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B98">
         <v>2515</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D98">
         <v>128</v>
@@ -3018,18 +3181,18 @@
         <v>834.98</v>
       </c>
       <c r="F98">
-        <v>6.523</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>6.5229999999999997</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99">
         <v>5101</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3041,15 +3204,15 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100">
         <v>5113</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -3061,15 +3224,15 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101">
         <v>5209</v>
       </c>
       <c r="C101" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D101">
         <v>163</v>
@@ -3078,18 +3241,18 @@
         <v>1058.52</v>
       </c>
       <c r="F101">
-        <v>6.494</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>6.4939999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102">
         <v>5448</v>
       </c>
       <c r="C102" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D102">
         <v>61</v>
@@ -3101,15 +3264,15 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B103">
         <v>5408</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D103">
         <v>106</v>
@@ -3121,35 +3284,35 @@
         <v>6.141</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B104">
         <v>1121</v>
       </c>
       <c r="C104" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D104">
         <v>96</v>
       </c>
       <c r="E104">
-        <v>698.5599999999999</v>
+        <v>698.56</v>
       </c>
       <c r="F104">
-        <v>7.277</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>7.2770000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B105">
         <v>2515</v>
       </c>
       <c r="C105" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -3158,18 +3321,18 @@
         <v>46.78</v>
       </c>
       <c r="F105">
-        <v>6.683</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>6.6829999999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B106">
         <v>5209</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -3181,75 +3344,75 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B107">
         <v>5305</v>
       </c>
       <c r="C107" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D107">
         <v>145</v>
       </c>
       <c r="E107">
-        <v>871.4400000000001</v>
+        <v>871.44</v>
       </c>
       <c r="F107">
         <v>6.01</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B108">
         <v>5111</v>
       </c>
       <c r="C108" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D108">
         <v>45</v>
       </c>
       <c r="E108">
-        <v>291.1</v>
+        <v>291.10000000000002</v>
       </c>
       <c r="F108">
-        <v>6.469</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>6.4690000000000003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B109">
         <v>5122</v>
       </c>
       <c r="C109" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D109">
         <v>6</v>
       </c>
       <c r="E109">
-        <v>35.12</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="F109">
-        <v>5.853</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>5.8529999999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B110">
         <v>5204</v>
       </c>
       <c r="C110" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -3261,35 +3424,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B111">
         <v>5205</v>
       </c>
       <c r="C111" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D111">
         <v>153</v>
       </c>
       <c r="E111">
-        <v>1098.6</v>
+        <v>1098.5999999999999</v>
       </c>
       <c r="F111">
         <v>7.18</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B112">
         <v>5408</v>
       </c>
       <c r="C112" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3301,15 +3464,15 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B113">
         <v>5122</v>
       </c>
       <c r="C113" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="D113">
         <v>76</v>
@@ -3318,18 +3481,18 @@
         <v>568.98</v>
       </c>
       <c r="F113">
-        <v>7.487</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>7.4870000000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B114">
         <v>1121</v>
       </c>
       <c r="C114" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3341,15 +3504,15 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B115">
         <v>3314</v>
       </c>
       <c r="C115" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D115">
         <v>107</v>
@@ -3358,18 +3521,18 @@
         <v>679.78</v>
       </c>
       <c r="F115">
-        <v>6.353</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>6.3529999999999998</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B116">
         <v>5305</v>
       </c>
       <c r="C116" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D116">
         <v>98</v>
@@ -3378,18 +3541,18 @@
         <v>558.48</v>
       </c>
       <c r="F116">
-        <v>5.699</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>5.6989999999999998</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B117">
         <v>5207</v>
       </c>
       <c r="C117" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D117">
         <v>62</v>
@@ -3398,38 +3561,38 @@
         <v>410.82</v>
       </c>
       <c r="F117">
-        <v>6.626</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>6.6260000000000003</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B118">
         <v>5203</v>
       </c>
       <c r="C118" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D118">
         <v>183</v>
       </c>
       <c r="E118">
-        <v>1264.1</v>
+        <v>1264.0999999999999</v>
       </c>
       <c r="F118">
-        <v>6.908</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>6.9080000000000004</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B119">
         <v>5105</v>
       </c>
       <c r="C119" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D119">
         <v>215</v>
@@ -3441,15 +3604,15 @@
         <v>6.944</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B120">
         <v>5504</v>
       </c>
       <c r="C120" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D120">
         <v>75</v>
@@ -3458,18 +3621,18 @@
         <v>489.96</v>
       </c>
       <c r="F120">
-        <v>6.533</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>6.5330000000000004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B121">
         <v>2214</v>
       </c>
       <c r="C121" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D121">
         <v>195</v>
@@ -3481,15 +3644,15 @@
         <v>7.508</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B122">
         <v>2214</v>
       </c>
       <c r="C122" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D122">
         <v>80</v>
@@ -3501,55 +3664,55 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B123">
         <v>2214</v>
       </c>
       <c r="C123" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D123">
         <v>8</v>
       </c>
       <c r="E123">
-        <v>67.04000000000001</v>
+        <v>67.040000000000006</v>
       </c>
       <c r="F123">
-        <v>8.380000000000001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B124">
         <v>2214</v>
       </c>
       <c r="C124" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D124">
         <v>10</v>
       </c>
       <c r="E124">
-        <v>68.95999999999999</v>
+        <v>68.959999999999994</v>
       </c>
       <c r="F124">
-        <v>6.896</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>6.8959999999999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B125">
         <v>3403</v>
       </c>
       <c r="C125" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D125">
         <v>94</v>
@@ -3558,18 +3721,18 @@
         <v>627.72</v>
       </c>
       <c r="F125">
-        <v>6.678</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>6.6779999999999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B126">
         <v>5115</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D126">
         <v>33</v>
@@ -3578,18 +3741,18 @@
         <v>242.14</v>
       </c>
       <c r="F126">
-        <v>7.338</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>7.3380000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B127">
         <v>5409</v>
       </c>
       <c r="C127" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D127">
         <v>41</v>
@@ -3598,18 +3761,18 @@
         <v>296.12</v>
       </c>
       <c r="F127">
-        <v>7.222</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>7.2220000000000004</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B128">
         <v>2214</v>
       </c>
       <c r="C128" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3621,15 +3784,15 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B129">
         <v>4117</v>
       </c>
       <c r="C129" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D129">
         <v>72</v>
@@ -3638,18 +3801,18 @@
         <v>462.78</v>
       </c>
       <c r="F129">
-        <v>6.427</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>6.4269999999999996</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B130">
         <v>5115</v>
       </c>
       <c r="C130" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D130">
         <v>55</v>
@@ -3658,38 +3821,38 @@
         <v>360.9</v>
       </c>
       <c r="F130">
-        <v>6.562</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>6.5620000000000003</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B131">
         <v>5202</v>
       </c>
       <c r="C131" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D131">
         <v>48</v>
       </c>
       <c r="E131">
-        <v>261.1</v>
+        <v>261.10000000000002</v>
       </c>
       <c r="F131">
         <v>5.44</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B132">
         <v>3110</v>
       </c>
       <c r="C132" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D132">
         <v>156</v>
@@ -3698,18 +3861,18 @@
         <v>980.74</v>
       </c>
       <c r="F132">
-        <v>6.287</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>6.2869999999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B133">
         <v>5202</v>
       </c>
       <c r="C133" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D133">
         <v>163</v>
@@ -3718,18 +3881,18 @@
         <v>1011.08</v>
       </c>
       <c r="F133">
-        <v>6.203</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>6.2030000000000003</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B134">
         <v>3110</v>
       </c>
       <c r="C134" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -3741,15 +3904,15 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B135">
         <v>5202</v>
       </c>
       <c r="C135" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -3761,15 +3924,15 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B136">
         <v>1135</v>
       </c>
       <c r="C136" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D136">
         <v>23</v>
@@ -3778,38 +3941,38 @@
         <v>132.38</v>
       </c>
       <c r="F136">
-        <v>5.756</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>5.7560000000000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B137">
         <v>4111</v>
       </c>
       <c r="C137" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D137">
         <v>48</v>
       </c>
       <c r="E137">
-        <v>327.54</v>
+        <v>327.54000000000002</v>
       </c>
       <c r="F137">
-        <v>6.824</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <v>6.8239999999999998</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B138">
         <v>4117</v>
       </c>
       <c r="C138" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3821,15 +3984,15 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B139">
         <v>5202</v>
       </c>
       <c r="C139" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -3838,18 +4001,18 @@
         <v>21.76</v>
       </c>
       <c r="F139">
-        <v>7.253</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>7.2530000000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B140">
         <v>5624</v>
       </c>
       <c r="C140" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D140">
         <v>103</v>
@@ -3858,18 +4021,18 @@
         <v>688.24</v>
       </c>
       <c r="F140">
-        <v>6.682</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>6.6820000000000004</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B141">
         <v>4111</v>
       </c>
       <c r="C141" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3881,15 +4044,15 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B142">
         <v>5624</v>
       </c>
       <c r="C142" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D142">
         <v>74</v>
@@ -3898,18 +4061,18 @@
         <v>478.5</v>
       </c>
       <c r="F142">
-        <v>6.466</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>6.4660000000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B143">
         <v>3110</v>
       </c>
       <c r="C143" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -3921,15 +4084,15 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B144">
         <v>4317</v>
       </c>
       <c r="C144" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D144">
         <v>54</v>
@@ -3941,15 +4104,15 @@
         <v>6.774</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B145">
         <v>5601</v>
       </c>
       <c r="C145" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D145">
         <v>85</v>
@@ -3958,38 +4121,38 @@
         <v>403.56</v>
       </c>
       <c r="F145">
-        <v>4.748</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>4.7480000000000002</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B146">
         <v>5624</v>
       </c>
       <c r="C146" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D146">
         <v>2</v>
       </c>
       <c r="E146">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="F146">
-        <v>8.029999999999999</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>8.0299999999999994</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B147">
         <v>1223</v>
       </c>
       <c r="C147" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D147">
         <v>49</v>
@@ -3998,18 +4161,18 @@
         <v>274</v>
       </c>
       <c r="F147">
-        <v>5.592</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>5.5919999999999996</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B148">
         <v>5601</v>
       </c>
       <c r="C148" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D148">
         <v>34</v>
@@ -4018,18 +4181,18 @@
         <v>148.04</v>
       </c>
       <c r="F148">
-        <v>4.354</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+        <v>4.3540000000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B149">
         <v>5621</v>
       </c>
       <c r="C149" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D149">
         <v>152</v>
@@ -4038,18 +4201,18 @@
         <v>1055.94</v>
       </c>
       <c r="F149">
-        <v>6.947</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>6.9470000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B150">
         <v>5601</v>
       </c>
       <c r="C150" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -4061,15 +4224,15 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B151">
         <v>5621</v>
       </c>
       <c r="C151" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -4081,15 +4244,15 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B152">
         <v>5664</v>
       </c>
       <c r="C152" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -4101,15 +4264,15 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B153">
         <v>3491</v>
       </c>
       <c r="C153" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D153">
         <v>85</v>
@@ -4118,18 +4281,18 @@
         <v>591.46</v>
       </c>
       <c r="F153">
-        <v>6.958</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>6.9580000000000002</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B154">
         <v>4317</v>
       </c>
       <c r="C154" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D154">
         <v>8</v>
@@ -4141,15 +4304,15 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B155">
         <v>5458</v>
       </c>
       <c r="C155" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D155">
         <v>268</v>
@@ -4158,18 +4321,18 @@
         <v>1818.92</v>
       </c>
       <c r="F155">
-        <v>6.787</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>6.7869999999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B156">
         <v>4317</v>
       </c>
       <c r="C156" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -4178,18 +4341,18 @@
         <v>88.7</v>
       </c>
       <c r="F156">
-        <v>5.544</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
+        <v>5.5439999999999996</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B157">
         <v>5458</v>
       </c>
       <c r="C157" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -4201,15 +4364,15 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B158">
         <v>5621</v>
       </c>
       <c r="C158" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -4221,15 +4384,15 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B159">
         <v>2220</v>
       </c>
       <c r="C159" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D159">
         <v>96</v>
@@ -4238,18 +4401,18 @@
         <v>641.16</v>
       </c>
       <c r="F159">
-        <v>6.679</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>6.6790000000000003</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B160">
         <v>5601</v>
       </c>
       <c r="C160" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -4258,18 +4421,18 @@
         <v>20.78</v>
       </c>
       <c r="F160">
-        <v>4.156</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+        <v>4.1559999999999997</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B161">
         <v>2220</v>
       </c>
       <c r="C161" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D161">
         <v>193</v>
@@ -4278,18 +4441,18 @@
         <v>1462.46</v>
       </c>
       <c r="F161">
-        <v>7.578</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>7.5780000000000003</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B162">
         <v>2403</v>
       </c>
       <c r="C162" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D162">
         <v>8</v>
@@ -4298,18 +4461,18 @@
         <v>25.9</v>
       </c>
       <c r="F162">
-        <v>3.237</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+        <v>3.2370000000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B163">
         <v>5458</v>
       </c>
       <c r="C163" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -4318,18 +4481,18 @@
         <v>49.24</v>
       </c>
       <c r="F163">
-        <v>8.207000000000001</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
+        <v>8.2070000000000007</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B164">
         <v>2220</v>
       </c>
       <c r="C164" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D164">
         <v>54</v>
@@ -4341,15 +4504,15 @@
         <v>6.508</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B165">
         <v>5601</v>
       </c>
       <c r="C165" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -4361,15 +4524,15 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B166">
         <v>2220</v>
       </c>
       <c r="C166" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D166">
         <v>44</v>
@@ -4378,18 +4541,18 @@
         <v>313.92</v>
       </c>
       <c r="F166">
-        <v>7.135</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
+        <v>7.1349999999999998</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B167">
         <v>5662</v>
       </c>
       <c r="C167" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D167">
         <v>89</v>
@@ -4398,18 +4561,18 @@
         <v>516.64</v>
       </c>
       <c r="F167">
-        <v>5.805</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
+        <v>5.8049999999999997</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B168">
         <v>2220</v>
       </c>
       <c r="C168" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -4418,18 +4581,18 @@
         <v>31.62</v>
       </c>
       <c r="F168">
-        <v>7.905</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
+        <v>7.9050000000000002</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B169">
         <v>2521</v>
       </c>
       <c r="C169" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D169">
         <v>42</v>
@@ -4438,18 +4601,18 @@
         <v>230.1</v>
       </c>
       <c r="F169">
-        <v>5.479</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+        <v>5.4790000000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B170">
         <v>2512</v>
       </c>
       <c r="C170" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D170">
         <v>78</v>
@@ -4458,38 +4621,38 @@
         <v>483.46</v>
       </c>
       <c r="F170">
-        <v>6.198</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
+        <v>6.1980000000000004</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B171">
         <v>2514</v>
       </c>
       <c r="C171" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D171">
         <v>18</v>
       </c>
       <c r="E171">
-        <v>97.95999999999999</v>
+        <v>97.96</v>
       </c>
       <c r="F171">
-        <v>5.442</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
+        <v>5.4420000000000002</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B172">
         <v>2514</v>
       </c>
       <c r="C172" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D172">
         <v>155</v>
@@ -4498,18 +4661,18 @@
         <v>1063.98</v>
       </c>
       <c r="F172">
-        <v>6.864</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
+        <v>6.8639999999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B173">
         <v>2512</v>
       </c>
       <c r="C173" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4521,15 +4684,15 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B174">
         <v>3106</v>
       </c>
       <c r="C174" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D174">
         <v>40</v>
@@ -4538,18 +4701,18 @@
         <v>252.6</v>
       </c>
       <c r="F174">
-        <v>6.315</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
+        <v>6.3150000000000004</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B175">
         <v>4240</v>
       </c>
       <c r="C175" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D175">
         <v>37</v>
@@ -4558,18 +4721,18 @@
         <v>152.6</v>
       </c>
       <c r="F175">
-        <v>4.124</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
+        <v>4.1239999999999997</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B176">
         <v>5661</v>
       </c>
       <c r="C176" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D176">
         <v>42</v>
@@ -4578,18 +4741,18 @@
         <v>301.36</v>
       </c>
       <c r="F176">
-        <v>7.175</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
+        <v>7.1749999999999998</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B177">
         <v>5661</v>
       </c>
       <c r="C177" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D177">
         <v>48</v>
@@ -4598,18 +4761,18 @@
         <v>328.38</v>
       </c>
       <c r="F177">
-        <v>6.841</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
+        <v>6.8410000000000002</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B178">
         <v>5663</v>
       </c>
       <c r="C178" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D178">
         <v>30</v>
@@ -4618,18 +4781,18 @@
         <v>186.26</v>
       </c>
       <c r="F178">
-        <v>6.209</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
+        <v>6.2089999999999996</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B179">
         <v>5664</v>
       </c>
       <c r="C179" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D179">
         <v>114</v>
@@ -4638,18 +4801,18 @@
         <v>734.42</v>
       </c>
       <c r="F179">
-        <v>6.442</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
+        <v>6.4420000000000002</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B180">
         <v>5663</v>
       </c>
       <c r="C180" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D180">
         <v>114</v>
@@ -4658,18 +4821,18 @@
         <v>693.86</v>
       </c>
       <c r="F180">
-        <v>6.086</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
+        <v>6.0860000000000003</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B181">
         <v>2514</v>
       </c>
       <c r="C181" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4681,15 +4844,15 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B182">
         <v>5208</v>
       </c>
       <c r="C182" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="D182">
         <v>66</v>
@@ -4698,18 +4861,18 @@
         <v>428.16</v>
       </c>
       <c r="F182">
-        <v>6.487</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>6.4870000000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B183">
         <v>5208</v>
       </c>
       <c r="C183" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -4718,18 +4881,18 @@
         <v>37.72</v>
       </c>
       <c r="F183">
-        <v>6.287</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
+        <v>6.2869999999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B184">
         <v>5663</v>
       </c>
       <c r="C184" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -4741,15 +4904,15 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B185">
         <v>5664</v>
       </c>
       <c r="C185" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4761,15 +4924,15 @@
         <v>10.68</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B186">
         <v>1107</v>
       </c>
       <c r="C186" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D186">
         <v>161</v>
@@ -4778,18 +4941,18 @@
         <v>1007.24</v>
       </c>
       <c r="F186">
-        <v>6.256</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
+        <v>6.2560000000000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B187">
         <v>4240</v>
       </c>
       <c r="C187" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4801,15 +4964,15 @@
         <v>11.38</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B188">
         <v>4241</v>
       </c>
       <c r="C188" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D188">
         <v>24</v>
@@ -4821,15 +4984,15 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B189">
         <v>5208</v>
       </c>
       <c r="C189" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="D189">
         <v>10</v>
@@ -4838,38 +5001,38 @@
         <v>70.02</v>
       </c>
       <c r="F189">
-        <v>7.002</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
+        <v>7.0019999999999998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B190">
         <v>4241</v>
       </c>
       <c r="C190" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D190">
         <v>3</v>
       </c>
       <c r="E190">
-        <v>9.140000000000001</v>
+        <v>9.14</v>
       </c>
       <c r="F190">
         <v>3.05</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B191">
         <v>4412</v>
       </c>
       <c r="C191" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D191">
         <v>4</v>
@@ -4881,15 +5044,15 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B192">
         <v>5208</v>
       </c>
       <c r="C192" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -4901,35 +5064,35 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B193">
         <v>4412</v>
       </c>
       <c r="C193" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D193">
         <v>116</v>
       </c>
       <c r="E193">
-        <v>668.9400000000001</v>
+        <v>668.94</v>
       </c>
       <c r="F193">
-        <v>5.767</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
+        <v>5.7670000000000003</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B194">
         <v>1107</v>
       </c>
       <c r="C194" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4941,15 +5104,15 @@
         <v>11.96</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B195">
         <v>3115</v>
       </c>
       <c r="C195" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D195">
         <v>148</v>
@@ -4958,18 +5121,18 @@
         <v>1025.28</v>
       </c>
       <c r="F195">
-        <v>6.928</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
+        <v>6.9279999999999999</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B196">
         <v>5440</v>
       </c>
       <c r="C196" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D196">
         <v>114</v>
@@ -4978,18 +5141,18 @@
         <v>657.4</v>
       </c>
       <c r="F196">
-        <v>5.767</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
+        <v>5.7670000000000003</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B197">
         <v>5441</v>
       </c>
       <c r="C197" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D197">
         <v>57</v>
@@ -5001,15 +5164,15 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B198">
         <v>3115</v>
       </c>
       <c r="C198" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D198">
         <v>40</v>
@@ -5018,18 +5181,18 @@
         <v>282.88</v>
       </c>
       <c r="F198">
-        <v>7.072</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
+        <v>7.0720000000000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B199">
         <v>5208</v>
       </c>
       <c r="C199" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -5038,18 +5201,18 @@
         <v>31.92</v>
       </c>
       <c r="F199">
-        <v>6.384</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
+        <v>6.3840000000000003</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B200">
         <v>5440</v>
       </c>
       <c r="C200" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D200">
         <v>111</v>
@@ -5058,18 +5221,18 @@
         <v>608.96</v>
       </c>
       <c r="F200">
-        <v>5.486</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
+        <v>5.4859999999999998</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B201">
         <v>3115</v>
       </c>
       <c r="C201" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D201">
         <v>6</v>
@@ -5081,15 +5244,15 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B202">
         <v>4129</v>
       </c>
       <c r="C202" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D202">
         <v>89</v>
@@ -5098,18 +5261,18 @@
         <v>527.22</v>
       </c>
       <c r="F202">
-        <v>5.924</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
+        <v>5.9240000000000004</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B203">
         <v>4129</v>
       </c>
       <c r="C203" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D203">
         <v>80</v>
@@ -5118,18 +5281,18 @@
         <v>498.2</v>
       </c>
       <c r="F203">
-        <v>6.228</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>6.2279999999999998</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B204">
         <v>3317</v>
       </c>
       <c r="C204" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D204">
         <v>204</v>
@@ -5138,18 +5301,18 @@
         <v>1262.5</v>
       </c>
       <c r="F204">
-        <v>6.189</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+        <v>6.1890000000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B205">
         <v>3317</v>
       </c>
       <c r="C205" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -5158,18 +5321,18 @@
         <v>20.78</v>
       </c>
       <c r="F205">
-        <v>6.927</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+        <v>6.9269999999999996</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B206">
         <v>1215</v>
       </c>
       <c r="C206" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D206">
         <v>151</v>
@@ -5178,38 +5341,38 @@
         <v>975.84</v>
       </c>
       <c r="F206">
-        <v>6.463</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
+        <v>6.4630000000000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B207">
         <v>1215</v>
       </c>
       <c r="C207" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D207">
         <v>2</v>
       </c>
       <c r="E207">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="F207">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B208">
         <v>3317</v>
       </c>
       <c r="C208" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -5221,15 +5384,15 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B209">
         <v>4239</v>
       </c>
       <c r="C209" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="D209">
         <v>48</v>
@@ -5238,18 +5401,18 @@
         <v>205.3</v>
       </c>
       <c r="F209">
-        <v>4.277</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
+        <v>4.2770000000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B210">
         <v>4209</v>
       </c>
       <c r="C210" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D210">
         <v>69</v>
@@ -5258,18 +5421,18 @@
         <v>529.66</v>
       </c>
       <c r="F210">
-        <v>7.676</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
+        <v>7.6760000000000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B211">
         <v>4209</v>
       </c>
       <c r="C211" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -5281,15 +5444,15 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B212" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="C212" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D212">
         <v>137</v>
@@ -5298,38 +5461,38 @@
         <v>906.34</v>
       </c>
       <c r="F212">
-        <v>6.616</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
+        <v>6.6159999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B213" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="C213" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D213">
         <v>178</v>
       </c>
       <c r="E213">
-        <v>1032.1</v>
+        <v>1032.0999999999999</v>
       </c>
       <c r="F213">
         <v>5.798</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B214" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="C214" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D214">
         <v>22</v>
@@ -5341,15 +5504,15 @@
         <v>4.431</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B215" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C215" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D215">
         <v>29</v>
@@ -5358,18 +5521,18 @@
         <v>183.84</v>
       </c>
       <c r="F215">
-        <v>6.339</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
+        <v>6.3390000000000004</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B216" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="C216" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -5381,35 +5544,35 @@
         <v>6.968</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B217" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="C217" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="D217">
         <v>1</v>
       </c>
       <c r="E217">
-        <v>8.539999999999999</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="F217">
-        <v>8.539999999999999</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
+        <v>8.5399999999999991</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B218" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="C218" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -5421,15 +5584,15 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B219" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="C219" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D219">
         <v>216</v>
@@ -5438,18 +5601,18 @@
         <v>1188.18</v>
       </c>
       <c r="F219">
-        <v>5.501</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
+        <v>5.5010000000000003</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B220" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="C220" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -5458,18 +5621,18 @@
         <v>19.54</v>
       </c>
       <c r="F220">
-        <v>6.513</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
+        <v>6.5129999999999999</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B221" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="C221" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5481,15 +5644,15 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B222" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="C222" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D222">
         <v>263</v>
@@ -5498,18 +5661,18 @@
         <v>1489.22</v>
       </c>
       <c r="F222">
-        <v>5.662</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
+        <v>5.6619999999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B223" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="C223" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D223">
         <v>38</v>
@@ -5518,18 +5681,18 @@
         <v>243.56</v>
       </c>
       <c r="F223">
-        <v>6.409</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
+        <v>6.4089999999999998</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B224" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="C224" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D224">
         <v>152</v>
@@ -5538,18 +5701,18 @@
         <v>1015.74</v>
       </c>
       <c r="F224">
-        <v>6.683</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
+        <v>6.6829999999999998</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B225" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="C225" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D225">
         <v>184</v>
@@ -5558,18 +5721,18 @@
         <v>1268.3</v>
       </c>
       <c r="F225">
-        <v>6.893</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
+        <v>6.8929999999999998</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B226" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="C226" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D226">
         <v>2</v>
@@ -5581,15 +5744,15 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B227" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="C227" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D227">
         <v>2</v>
@@ -5601,15 +5764,15 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B228" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="C228" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D228">
         <v>2</v>
@@ -5621,15 +5784,15 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B229" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="C229" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D229">
         <v>44</v>
@@ -5638,18 +5801,18 @@
         <v>242.26</v>
       </c>
       <c r="F229">
-        <v>5.506</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
+        <v>5.5060000000000002</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B230" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C230" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D230">
         <v>36</v>
@@ -5658,18 +5821,18 @@
         <v>220.28</v>
       </c>
       <c r="F230">
-        <v>6.119</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
+        <v>6.1189999999999998</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B231" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="C231" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D231">
         <v>12</v>
@@ -5678,18 +5841,18 @@
         <v>52.38</v>
       </c>
       <c r="F231">
-        <v>4.365</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
+        <v>4.3650000000000002</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B232" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="C232" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5701,15 +5864,15 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B233" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="C233" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D233">
         <v>2</v>
@@ -5721,15 +5884,15 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B234" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C234" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5738,18 +5901,18 @@
         <v>251.82</v>
       </c>
       <c r="F234">
-        <v>6.142</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>6.1420000000000003</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B235" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C235" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D235">
         <v>83</v>
@@ -5758,18 +5921,18 @@
         <v>604.46</v>
       </c>
       <c r="F235">
-        <v>7.283</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
+        <v>7.2830000000000004</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B236" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C236" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D236">
         <v>55</v>
@@ -5778,18 +5941,18 @@
         <v>349.1</v>
       </c>
       <c r="F236">
-        <v>6.347</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
+        <v>6.3470000000000004</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B237" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C237" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D237">
         <v>52</v>
@@ -5801,15 +5964,15 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B238" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C238" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D238">
         <v>137</v>
@@ -5818,18 +5981,18 @@
         <v>841.64</v>
       </c>
       <c r="F238">
-        <v>6.143</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
+        <v>6.1429999999999998</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B239" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C239" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -5841,35 +6004,35 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B240" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C240" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D240">
         <v>110</v>
       </c>
       <c r="E240">
-        <v>651.9400000000001</v>
+        <v>651.94000000000005</v>
       </c>
       <c r="F240">
-        <v>5.927</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
+        <v>5.9269999999999996</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B241" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C241" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D241">
         <v>194</v>
@@ -5878,18 +6041,18 @@
         <v>1319.78</v>
       </c>
       <c r="F241">
-        <v>6.803</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
+        <v>6.8029999999999999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B242" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C242" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D242">
         <v>4</v>
@@ -5898,18 +6061,18 @@
         <v>31.22</v>
       </c>
       <c r="F242">
-        <v>7.805</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
+        <v>7.8049999999999997</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B243" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C243" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D243">
         <v>2</v>
@@ -5921,35 +6084,35 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B244" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C244" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D244">
         <v>142</v>
       </c>
       <c r="E244">
-        <v>959.0599999999999</v>
+        <v>959.06</v>
       </c>
       <c r="F244">
-        <v>6.754</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
+        <v>6.7539999999999996</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B245" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C245" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D245">
         <v>28</v>
@@ -5958,18 +6121,18 @@
         <v>198.2</v>
       </c>
       <c r="F245">
-        <v>7.079</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
+        <v>7.0789999999999997</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B246" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C246" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D246">
         <v>153</v>
@@ -5981,15 +6144,15 @@
         <v>7.101</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B247" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="C247" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D247">
         <v>138</v>
@@ -6001,15 +6164,15 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B248" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C248" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D248">
         <v>153</v>
@@ -6018,18 +6181,18 @@
         <v>973.72</v>
       </c>
       <c r="F248">
-        <v>6.364</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
+        <v>6.3639999999999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B249" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C249" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D249">
         <v>30</v>
@@ -6038,18 +6201,18 @@
         <v>184.64</v>
       </c>
       <c r="F249">
-        <v>6.155</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
+        <v>6.1550000000000002</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B250" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="C250" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -6061,15 +6224,15 @@
         <v>10.62</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B251" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C251" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D251">
         <v>102</v>
@@ -6078,18 +6241,18 @@
         <v>705.24</v>
       </c>
       <c r="F251">
-        <v>6.914</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
+        <v>6.9139999999999997</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B252" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C252" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -6101,15 +6264,15 @@
         <v>11.42</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B253" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C253" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -6121,35 +6284,35 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B254" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C254" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D254">
         <v>24</v>
       </c>
       <c r="E254">
-        <v>159.2</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="F254">
         <v>6.633</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B255" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C255" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -6161,15 +6324,15 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B256" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C256" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D256">
         <v>102</v>
@@ -6178,18 +6341,18 @@
         <v>688</v>
       </c>
       <c r="F256">
-        <v>6.745</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+        <v>6.7450000000000001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B257" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C257" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D257">
         <v>142</v>
@@ -6198,18 +6361,18 @@
         <v>1368.72</v>
       </c>
       <c r="F257">
-        <v>9.638999999999999</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+        <v>9.6389999999999993</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B258" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C258" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D258">
         <v>4</v>
@@ -6218,18 +6381,18 @@
         <v>31.7</v>
       </c>
       <c r="F258">
-        <v>7.925</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>7.9249999999999998</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B259" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C259" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -6241,15 +6404,15 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B260" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C260" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D260">
         <v>5</v>
@@ -6258,18 +6421,18 @@
         <v>30.06</v>
       </c>
       <c r="F260">
-        <v>6.012</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>6.0119999999999996</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B261" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C261" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D261">
         <v>2</v>
@@ -6281,35 +6444,35 @@
         <v>7.59</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B262" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C262" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D262">
         <v>118</v>
       </c>
       <c r="E262">
-        <v>779.3200000000001</v>
+        <v>779.32</v>
       </c>
       <c r="F262">
-        <v>6.604</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+        <v>6.6040000000000001</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B263" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C263" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D263">
         <v>2</v>
@@ -6321,15 +6484,15 @@
         <v>10.46</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B264" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C264" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D264">
         <v>76</v>
@@ -6341,15 +6504,15 @@
         <v>6.125</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B265" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C265" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D265">
         <v>6</v>
@@ -6361,15 +6524,15 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B266" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C266" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D266">
         <v>210</v>
@@ -6378,18 +6541,18 @@
         <v>1339.1</v>
       </c>
       <c r="F266">
-        <v>6.377</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>6.3769999999999998</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B267" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C267" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -6401,15 +6564,15 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B268" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C268" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -6421,15 +6584,15 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B269" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C269" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D269">
         <v>157</v>
@@ -6438,18 +6601,18 @@
         <v>986.16</v>
       </c>
       <c r="F269">
-        <v>6.281</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
+        <v>6.2809999999999997</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B270" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C270" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -6461,15 +6624,15 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B271" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C271" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D271">
         <v>5</v>
@@ -6478,18 +6641,18 @@
         <v>33.94</v>
       </c>
       <c r="F271">
-        <v>6.788</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
+        <v>6.7880000000000003</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B272" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C272" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D272">
         <v>129</v>
@@ -6498,18 +6661,18 @@
         <v>1016.3</v>
       </c>
       <c r="F272">
-        <v>7.878</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
+        <v>7.8780000000000001</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B273" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="C273" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D273">
         <v>93</v>
@@ -6518,18 +6681,18 @@
         <v>559.24</v>
       </c>
       <c r="F273">
-        <v>6.013</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
+        <v>6.0129999999999999</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B274" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C274" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D274">
         <v>102</v>
@@ -6541,15 +6704,15 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B275" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C275" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -6561,35 +6724,35 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B276" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C276" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D276">
         <v>1</v>
       </c>
       <c r="E276">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F276">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B277" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C277" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D277">
         <v>2</v>
@@ -6601,15 +6764,15 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B278" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C278" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D278">
         <v>102</v>
@@ -6621,35 +6784,35 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B279" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="C279" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D279">
         <v>202</v>
       </c>
       <c r="E279">
-        <v>1184.6</v>
+        <v>1184.5999999999999</v>
       </c>
       <c r="F279">
-        <v>5.864</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+        <v>5.8639999999999999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B280" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C280" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D280">
         <v>1</v>
@@ -6661,15 +6824,15 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B281" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="C281" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D281">
         <v>205</v>
@@ -6678,18 +6841,18 @@
         <v>1424.26</v>
       </c>
       <c r="F281">
-        <v>6.948</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+        <v>6.9480000000000004</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B282" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C282" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D282">
         <v>1</v>
@@ -6701,15 +6864,15 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B283" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C283" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D283">
         <v>9</v>
@@ -6718,58 +6881,58 @@
         <v>55.42</v>
       </c>
       <c r="F283">
-        <v>6.158</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>6.1580000000000004</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B284" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="C284" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D284">
         <v>1</v>
       </c>
       <c r="E284">
-        <v>8.460000000000001</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="F284">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+        <v>8.4600000000000009</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B285" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="C285" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D285">
         <v>1</v>
       </c>
       <c r="E285">
-        <v>8.640000000000001</v>
+        <v>8.64</v>
       </c>
       <c r="F285">
-        <v>8.640000000000001</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B286" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C286" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -6781,15 +6944,15 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B287" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C287" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D287">
         <v>180</v>
@@ -6798,18 +6961,18 @@
         <v>1311.9</v>
       </c>
       <c r="F287">
-        <v>7.288</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+        <v>7.2880000000000003</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B288" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C288" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D288">
         <v>2</v>
@@ -6821,15 +6984,15 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B289" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C289" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D289">
         <v>2</v>
@@ -6841,15 +7004,15 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B290" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C290" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D290">
         <v>96</v>
@@ -6858,38 +7021,38 @@
         <v>627.34</v>
       </c>
       <c r="F290">
-        <v>6.535</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
+        <v>6.5350000000000001</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B291" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C291" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D291">
         <v>6</v>
       </c>
       <c r="E291">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="F291">
-        <v>6.283</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
+        <v>6.2830000000000004</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B292" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="C292" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D292">
         <v>51</v>
@@ -6898,18 +7061,18 @@
         <v>332.16</v>
       </c>
       <c r="F292">
-        <v>6.513</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
+        <v>6.5129999999999999</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B293" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C293" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D293">
         <v>4</v>
@@ -6921,15 +7084,15 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B294" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C294" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D294">
         <v>136</v>
@@ -6938,18 +7101,18 @@
         <v>946.72</v>
       </c>
       <c r="F294">
-        <v>6.961</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+        <v>6.9610000000000003</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B295" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C295" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D295">
         <v>35</v>
@@ -6958,18 +7121,18 @@
         <v>230.6</v>
       </c>
       <c r="F295">
-        <v>6.589</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
+        <v>6.5890000000000004</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B296" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C296" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D296">
         <v>59</v>
@@ -6981,15 +7144,15 @@
         <v>5.984</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B297" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C297" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D297">
         <v>17</v>
@@ -6998,18 +7161,18 @@
         <v>116.7</v>
       </c>
       <c r="F297">
-        <v>6.865</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
+        <v>6.8650000000000002</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B298" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C298" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D298">
         <v>106</v>
@@ -7018,18 +7181,18 @@
         <v>733.38</v>
       </c>
       <c r="F298">
-        <v>6.919</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
+        <v>6.9189999999999996</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B299" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C299" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D299">
         <v>247</v>
@@ -7038,18 +7201,18 @@
         <v>1511.22</v>
       </c>
       <c r="F299">
-        <v>6.118</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
+        <v>6.1180000000000003</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B300" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C300" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D300">
         <v>2</v>
@@ -7061,15 +7224,15 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B301" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C301" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D301">
         <v>66</v>
@@ -7078,18 +7241,18 @@
         <v>424.06</v>
       </c>
       <c r="F301">
-        <v>6.425</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
+        <v>6.4249999999999998</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B302" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C302" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -7101,15 +7264,15 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B303" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C303" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D303">
         <v>3</v>
@@ -7121,15 +7284,15 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B304" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C304" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D304">
         <v>7</v>
@@ -7141,35 +7304,35 @@
         <v>6.069</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B305" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C305" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D305">
         <v>5</v>
       </c>
       <c r="E305">
-        <v>37.38</v>
+        <v>37.380000000000003</v>
       </c>
       <c r="F305">
         <v>7.476</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B306" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C306" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D306">
         <v>30</v>
@@ -7178,18 +7341,18 @@
         <v>123.36</v>
       </c>
       <c r="F306">
-        <v>4.112</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
+        <v>4.1120000000000001</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B307" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C307" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D307">
         <v>192</v>
@@ -7198,18 +7361,18 @@
         <v>1154.76</v>
       </c>
       <c r="F307">
-        <v>6.014</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
+        <v>6.0140000000000002</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B308" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C308" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D308">
         <v>88</v>
@@ -7218,18 +7381,18 @@
         <v>528.22</v>
       </c>
       <c r="F308">
-        <v>6.003</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
+        <v>6.0030000000000001</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B309" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C309" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D309">
         <v>91</v>
@@ -7238,18 +7401,18 @@
         <v>378.34</v>
       </c>
       <c r="F309">
-        <v>4.158</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
+        <v>4.1580000000000004</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B310" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C310" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D310">
         <v>1</v>
@@ -7261,15 +7424,15 @@
         <v>13.14</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B311" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C311" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="D311">
         <v>72</v>
@@ -7278,18 +7441,18 @@
         <v>424.58</v>
       </c>
       <c r="F311">
-        <v>5.897</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
+        <v>5.8970000000000002</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B312" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C312" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D312">
         <v>70</v>
@@ -7298,18 +7461,18 @@
         <v>438.7</v>
       </c>
       <c r="F312">
-        <v>6.267</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
+        <v>6.2670000000000003</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B313" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C313" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D313">
         <v>24</v>
@@ -7318,18 +7481,18 @@
         <v>102.52</v>
       </c>
       <c r="F313">
-        <v>4.272</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
+        <v>4.2720000000000002</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B314" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="C314" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D314">
         <v>143</v>
@@ -7338,18 +7501,18 @@
         <v>981.1</v>
       </c>
       <c r="F314">
-        <v>6.861</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
+        <v>6.8609999999999998</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B315" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C315" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D315">
         <v>96</v>
@@ -7358,18 +7521,18 @@
         <v>573.04</v>
       </c>
       <c r="F315">
-        <v>5.969</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
+        <v>5.9690000000000003</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B316" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C316" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D316">
         <v>3</v>
@@ -7381,15 +7544,15 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B317" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C317" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D317">
         <v>5</v>
@@ -7401,15 +7564,15 @@
         <v>5.444</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B318" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C318" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D318">
         <v>2</v>
@@ -7421,15 +7584,15 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B319" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C319" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D319">
         <v>102</v>
@@ -7438,18 +7601,18 @@
         <v>660.1</v>
       </c>
       <c r="F319">
-        <v>6.472</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
+        <v>6.4720000000000004</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B320" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C320" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D320">
         <v>1</v>
@@ -7461,15 +7624,15 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B321" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C321" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D321">
         <v>4</v>
@@ -7481,15 +7644,15 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B322" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="C322" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D322">
         <v>199</v>
@@ -7498,18 +7661,18 @@
         <v>1393.88</v>
       </c>
       <c r="F322">
-        <v>7.004</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6">
+        <v>7.0039999999999996</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B323" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="C323" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D323">
         <v>6</v>
@@ -7521,15 +7684,15 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B324" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C324" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D324">
         <v>184</v>
@@ -7541,15 +7704,15 @@
         <v>7.069</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B325" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="C325" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="D325">
         <v>18</v>
@@ -7558,18 +7721,18 @@
         <v>42.36</v>
       </c>
       <c r="F325">
-        <v>2.353</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
+        <v>2.3530000000000002</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B326" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="C326" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D326">
         <v>1</v>
@@ -7581,15 +7744,15 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B327" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C327" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D327">
         <v>310</v>
@@ -7598,18 +7761,18 @@
         <v>1950.6</v>
       </c>
       <c r="F327">
-        <v>6.292</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
+        <v>6.2919999999999998</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B328" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C328" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D328">
         <v>7</v>
@@ -7618,7 +7781,907 @@
         <v>52.54</v>
       </c>
       <c r="F328">
-        <v>7.506</v>
+        <v>7.5060000000000002</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>166</v>
+      </c>
+      <c r="B329" t="s">
+        <v>243</v>
+      </c>
+      <c r="C329" t="s">
+        <v>266</v>
+      </c>
+      <c r="D329">
+        <v>3</v>
+      </c>
+      <c r="E329">
+        <v>25.9</v>
+      </c>
+      <c r="F329">
+        <v>8.6329999999999991</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>167</v>
+      </c>
+      <c r="B330" t="s">
+        <v>242</v>
+      </c>
+      <c r="C330" t="s">
+        <v>269</v>
+      </c>
+      <c r="D330">
+        <v>36</v>
+      </c>
+      <c r="E330">
+        <v>70.78</v>
+      </c>
+      <c r="F330">
+        <v>1.966</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>167</v>
+      </c>
+      <c r="B331" t="s">
+        <v>244</v>
+      </c>
+      <c r="C331" t="s">
+        <v>266</v>
+      </c>
+      <c r="D331">
+        <v>17</v>
+      </c>
+      <c r="E331">
+        <v>116.8</v>
+      </c>
+      <c r="F331">
+        <v>6.8710000000000004</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>168</v>
+      </c>
+      <c r="B332" t="s">
+        <v>242</v>
+      </c>
+      <c r="C332" t="s">
+        <v>269</v>
+      </c>
+      <c r="D332">
+        <v>6</v>
+      </c>
+      <c r="E332">
+        <v>11.24</v>
+      </c>
+      <c r="F332">
+        <v>1.873</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>168</v>
+      </c>
+      <c r="B333" t="s">
+        <v>244</v>
+      </c>
+      <c r="C333" t="s">
+        <v>266</v>
+      </c>
+      <c r="D333">
+        <v>40</v>
+      </c>
+      <c r="E333">
+        <v>287.18</v>
+      </c>
+      <c r="F333">
+        <v>7.1790000000000003</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>169</v>
+      </c>
+      <c r="B334" t="s">
+        <v>242</v>
+      </c>
+      <c r="C334" t="s">
+        <v>269</v>
+      </c>
+      <c r="D334">
+        <v>11</v>
+      </c>
+      <c r="E334">
+        <v>24.26</v>
+      </c>
+      <c r="F334">
+        <v>2.2050000000000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>169</v>
+      </c>
+      <c r="B335" t="s">
+        <v>245</v>
+      </c>
+      <c r="C335" t="s">
+        <v>266</v>
+      </c>
+      <c r="D335">
+        <v>202</v>
+      </c>
+      <c r="E335">
+        <v>1300.18</v>
+      </c>
+      <c r="F335">
+        <v>6.4370000000000003</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>170</v>
+      </c>
+      <c r="B336" t="s">
+        <v>246</v>
+      </c>
+      <c r="C336" t="s">
+        <v>268</v>
+      </c>
+      <c r="D336">
+        <v>60</v>
+      </c>
+      <c r="E336">
+        <v>366.6</v>
+      </c>
+      <c r="F336">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>171</v>
+      </c>
+      <c r="B337" t="s">
+        <v>247</v>
+      </c>
+      <c r="C337" t="s">
+        <v>266</v>
+      </c>
+      <c r="D337">
+        <v>128</v>
+      </c>
+      <c r="E337">
+        <v>780.74</v>
+      </c>
+      <c r="F337">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>172</v>
+      </c>
+      <c r="B338" t="s">
+        <v>248</v>
+      </c>
+      <c r="C338" t="s">
+        <v>268</v>
+      </c>
+      <c r="D338">
+        <v>177</v>
+      </c>
+      <c r="E338">
+        <v>1102.8599999999999</v>
+      </c>
+      <c r="F338">
+        <v>6.2309999999999999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>173</v>
+      </c>
+      <c r="B339" t="s">
+        <v>249</v>
+      </c>
+      <c r="C339" t="s">
+        <v>268</v>
+      </c>
+      <c r="D339">
+        <v>135</v>
+      </c>
+      <c r="E339">
+        <v>2046.8</v>
+      </c>
+      <c r="F339">
+        <v>15.161</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>173</v>
+      </c>
+      <c r="B340" t="s">
+        <v>248</v>
+      </c>
+      <c r="C340" t="s">
+        <v>268</v>
+      </c>
+      <c r="D340">
+        <v>6</v>
+      </c>
+      <c r="E340">
+        <v>36.020000000000003</v>
+      </c>
+      <c r="F340">
+        <v>6.0030000000000001</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>174</v>
+      </c>
+      <c r="B341" t="s">
+        <v>249</v>
+      </c>
+      <c r="C341" t="s">
+        <v>268</v>
+      </c>
+      <c r="D341">
+        <v>2</v>
+      </c>
+      <c r="E341">
+        <v>14.98</v>
+      </c>
+      <c r="F341">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>175</v>
+      </c>
+      <c r="B342" t="s">
+        <v>249</v>
+      </c>
+      <c r="C342" t="s">
+        <v>268</v>
+      </c>
+      <c r="D342">
+        <v>4</v>
+      </c>
+      <c r="E342">
+        <v>21.7</v>
+      </c>
+      <c r="F342">
+        <v>5.4249999999999998</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>175</v>
+      </c>
+      <c r="B343" t="s">
+        <v>248</v>
+      </c>
+      <c r="C343" t="s">
+        <v>268</v>
+      </c>
+      <c r="D343">
+        <v>6</v>
+      </c>
+      <c r="E343">
+        <v>44.98</v>
+      </c>
+      <c r="F343">
+        <v>7.4969999999999999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>176</v>
+      </c>
+      <c r="B344" t="s">
+        <v>250</v>
+      </c>
+      <c r="C344" t="s">
+        <v>266</v>
+      </c>
+      <c r="D344">
+        <v>134</v>
+      </c>
+      <c r="E344">
+        <v>976.88</v>
+      </c>
+      <c r="F344">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>177</v>
+      </c>
+      <c r="B345" t="s">
+        <v>250</v>
+      </c>
+      <c r="C345" t="s">
+        <v>266</v>
+      </c>
+      <c r="D345">
+        <v>2</v>
+      </c>
+      <c r="E345">
+        <v>17.3</v>
+      </c>
+      <c r="F345">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>177</v>
+      </c>
+      <c r="B346" t="s">
+        <v>251</v>
+      </c>
+      <c r="C346" t="s">
+        <v>266</v>
+      </c>
+      <c r="D346">
+        <v>156</v>
+      </c>
+      <c r="E346">
+        <v>868.48</v>
+      </c>
+      <c r="F346">
+        <v>5.5670000000000002</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>178</v>
+      </c>
+      <c r="B347" t="s">
+        <v>250</v>
+      </c>
+      <c r="C347" t="s">
+        <v>266</v>
+      </c>
+      <c r="D347">
+        <v>4</v>
+      </c>
+      <c r="E347">
+        <v>25.28</v>
+      </c>
+      <c r="F347">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>179</v>
+      </c>
+      <c r="B348" t="s">
+        <v>252</v>
+      </c>
+      <c r="C348" t="s">
+        <v>269</v>
+      </c>
+      <c r="D348">
+        <v>60</v>
+      </c>
+      <c r="E348">
+        <v>347.86</v>
+      </c>
+      <c r="F348">
+        <v>5.798</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>180</v>
+      </c>
+      <c r="B349" t="s">
+        <v>252</v>
+      </c>
+      <c r="C349" t="s">
+        <v>269</v>
+      </c>
+      <c r="D349">
+        <v>106</v>
+      </c>
+      <c r="E349">
+        <v>596.52</v>
+      </c>
+      <c r="F349">
+        <v>5.6280000000000001</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>180</v>
+      </c>
+      <c r="B350" t="s">
+        <v>253</v>
+      </c>
+      <c r="C350" t="s">
+        <v>268</v>
+      </c>
+      <c r="D350">
+        <v>90</v>
+      </c>
+      <c r="E350">
+        <v>531.62</v>
+      </c>
+      <c r="F350">
+        <v>5.907</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>181</v>
+      </c>
+      <c r="B351" t="s">
+        <v>253</v>
+      </c>
+      <c r="C351" t="s">
+        <v>268</v>
+      </c>
+      <c r="D351">
+        <v>48</v>
+      </c>
+      <c r="E351">
+        <v>316.76</v>
+      </c>
+      <c r="F351">
+        <v>6.5990000000000002</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>181</v>
+      </c>
+      <c r="B352" t="s">
+        <v>254</v>
+      </c>
+      <c r="C352" t="s">
+        <v>268</v>
+      </c>
+      <c r="D352">
+        <v>60</v>
+      </c>
+      <c r="E352">
+        <v>327.48</v>
+      </c>
+      <c r="F352">
+        <v>5.4580000000000002</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>182</v>
+      </c>
+      <c r="B353" t="s">
+        <v>254</v>
+      </c>
+      <c r="C353" t="s">
+        <v>268</v>
+      </c>
+      <c r="D353">
+        <v>51</v>
+      </c>
+      <c r="E353">
+        <v>338.26</v>
+      </c>
+      <c r="F353">
+        <v>6.633</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>183</v>
+      </c>
+      <c r="B354" t="s">
+        <v>255</v>
+      </c>
+      <c r="C354" t="s">
+        <v>268</v>
+      </c>
+      <c r="D354">
+        <v>89</v>
+      </c>
+      <c r="E354">
+        <v>509.94</v>
+      </c>
+      <c r="F354">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>184</v>
+      </c>
+      <c r="B355" t="s">
+        <v>256</v>
+      </c>
+      <c r="C355" t="s">
+        <v>269</v>
+      </c>
+      <c r="D355">
+        <v>94</v>
+      </c>
+      <c r="E355">
+        <v>583.48</v>
+      </c>
+      <c r="F355">
+        <v>6.2069999999999999</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>184</v>
+      </c>
+      <c r="B356" t="s">
+        <v>252</v>
+      </c>
+      <c r="C356" t="s">
+        <v>269</v>
+      </c>
+      <c r="D356">
+        <v>4</v>
+      </c>
+      <c r="E356">
+        <v>26.28</v>
+      </c>
+      <c r="F356">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>184</v>
+      </c>
+      <c r="B357" t="s">
+        <v>253</v>
+      </c>
+      <c r="C357" t="s">
+        <v>266</v>
+      </c>
+      <c r="D357">
+        <v>10</v>
+      </c>
+      <c r="E357">
+        <v>65</v>
+      </c>
+      <c r="F357">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>185</v>
+      </c>
+      <c r="B358" t="s">
+        <v>254</v>
+      </c>
+      <c r="C358" t="s">
+        <v>268</v>
+      </c>
+      <c r="D358">
+        <v>1</v>
+      </c>
+      <c r="E358">
+        <v>10.94</v>
+      </c>
+      <c r="F358">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>186</v>
+      </c>
+      <c r="B359" t="s">
+        <v>257</v>
+      </c>
+      <c r="C359" t="s">
+        <v>274</v>
+      </c>
+      <c r="D359">
+        <v>12</v>
+      </c>
+      <c r="E359">
+        <v>57.2</v>
+      </c>
+      <c r="F359">
+        <v>4.7670000000000003</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>186</v>
+      </c>
+      <c r="B360" t="s">
+        <v>258</v>
+      </c>
+      <c r="C360" t="s">
+        <v>269</v>
+      </c>
+      <c r="D360">
+        <v>102</v>
+      </c>
+      <c r="E360">
+        <v>681.1</v>
+      </c>
+      <c r="F360">
+        <v>6.6769999999999996</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>186</v>
+      </c>
+      <c r="B361" t="s">
+        <v>256</v>
+      </c>
+      <c r="C361" t="s">
+        <v>269</v>
+      </c>
+      <c r="D361">
+        <v>2</v>
+      </c>
+      <c r="E361">
+        <v>16</v>
+      </c>
+      <c r="F361">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>187</v>
+      </c>
+      <c r="B362" t="s">
+        <v>257</v>
+      </c>
+      <c r="C362" t="s">
+        <v>266</v>
+      </c>
+      <c r="D362">
+        <v>88</v>
+      </c>
+      <c r="E362">
+        <v>443.68</v>
+      </c>
+      <c r="F362">
+        <v>5.0419999999999998</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>188</v>
+      </c>
+      <c r="B363" t="s">
+        <v>259</v>
+      </c>
+      <c r="C363" t="s">
+        <v>266</v>
+      </c>
+      <c r="D363">
+        <v>125</v>
+      </c>
+      <c r="E363">
+        <v>770.34</v>
+      </c>
+      <c r="F363">
+        <v>6.1630000000000003</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>189</v>
+      </c>
+      <c r="B364" t="s">
+        <v>260</v>
+      </c>
+      <c r="C364" t="s">
+        <v>275</v>
+      </c>
+      <c r="D364">
+        <v>90</v>
+      </c>
+      <c r="E364">
+        <v>480.12</v>
+      </c>
+      <c r="F364">
+        <v>5.335</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>190</v>
+      </c>
+      <c r="B365" t="s">
+        <v>251</v>
+      </c>
+      <c r="C365" t="s">
+        <v>266</v>
+      </c>
+      <c r="D365">
+        <v>60</v>
+      </c>
+      <c r="E365">
+        <v>297.66000000000003</v>
+      </c>
+      <c r="F365">
+        <v>4.9610000000000003</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>190</v>
+      </c>
+      <c r="B366" t="s">
+        <v>261</v>
+      </c>
+      <c r="C366" t="s">
+        <v>266</v>
+      </c>
+      <c r="D366">
+        <v>22</v>
+      </c>
+      <c r="E366">
+        <v>81</v>
+      </c>
+      <c r="F366">
+        <v>3.6819999999999999</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>191</v>
+      </c>
+      <c r="B367" t="s">
+        <v>259</v>
+      </c>
+      <c r="C367" t="s">
+        <v>266</v>
+      </c>
+      <c r="D367">
+        <v>2</v>
+      </c>
+      <c r="E367">
+        <v>10.08</v>
+      </c>
+      <c r="F367">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>191</v>
+      </c>
+      <c r="B368" t="s">
+        <v>262</v>
+      </c>
+      <c r="C368" t="s">
+        <v>274</v>
+      </c>
+      <c r="D368">
+        <v>112</v>
+      </c>
+      <c r="E368">
+        <v>443.3</v>
+      </c>
+      <c r="F368">
+        <v>3.9580000000000002</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>192</v>
+      </c>
+      <c r="B369" t="s">
+        <v>259</v>
+      </c>
+      <c r="C369" t="s">
+        <v>266</v>
+      </c>
+      <c r="D369">
+        <v>2</v>
+      </c>
+      <c r="E369">
+        <v>15.04</v>
+      </c>
+      <c r="F369">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>192</v>
+      </c>
+      <c r="B370" t="s">
+        <v>262</v>
+      </c>
+      <c r="C370" t="s">
+        <v>266</v>
+      </c>
+      <c r="D370">
+        <v>42</v>
+      </c>
+      <c r="E370">
+        <v>158.97999999999999</v>
+      </c>
+      <c r="F370">
+        <v>3.7850000000000001</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>193</v>
+      </c>
+      <c r="B371" t="s">
+        <v>262</v>
+      </c>
+      <c r="C371" t="s">
+        <v>266</v>
+      </c>
+      <c r="D371">
+        <v>3</v>
+      </c>
+      <c r="E371">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="F371">
+        <v>5.4130000000000003</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>193</v>
+      </c>
+      <c r="B372" t="s">
+        <v>263</v>
+      </c>
+      <c r="C372" t="s">
+        <v>266</v>
+      </c>
+      <c r="D372">
+        <v>6</v>
+      </c>
+      <c r="E372">
+        <v>39.6</v>
+      </c>
+      <c r="F372">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>194</v>
+      </c>
+      <c r="B373" t="s">
+        <v>263</v>
+      </c>
+      <c r="C373" t="s">
+        <v>266</v>
+      </c>
+      <c r="D373">
+        <v>82</v>
+      </c>
+      <c r="E373">
+        <v>508.5</v>
+      </c>
+      <c r="F373">
+        <v>6.2009999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2772"/>
+  <dimension ref="A1:G2804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81376,6 +81376,998 @@
         </is>
       </c>
     </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>CO62175</t>
+        </is>
+      </c>
+      <c r="D2773" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2773" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="F2773" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="G2773" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2774" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2774" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="F2774" t="n">
+        <v>6.047</v>
+      </c>
+      <c r="G2774" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2775" t="n">
+        <v>112</v>
+      </c>
+      <c r="E2775" t="n">
+        <v>645.1799999999999</v>
+      </c>
+      <c r="F2775" t="n">
+        <v>5.761</v>
+      </c>
+      <c r="G2775" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>N25</t>
+        </is>
+      </c>
+      <c r="D2776" t="n">
+        <v>203</v>
+      </c>
+      <c r="E2776" t="n">
+        <v>1335.08</v>
+      </c>
+      <c r="F2776" t="n">
+        <v>6.577</v>
+      </c>
+      <c r="G2776" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2777" t="n">
+        <v>117</v>
+      </c>
+      <c r="E2777" t="n">
+        <v>788.5</v>
+      </c>
+      <c r="F2777" t="n">
+        <v>6.739</v>
+      </c>
+      <c r="G2777" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2778" t="n">
+        <v>64</v>
+      </c>
+      <c r="E2778" t="n">
+        <v>388.04</v>
+      </c>
+      <c r="F2778" t="n">
+        <v>6.063</v>
+      </c>
+      <c r="G2778" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2779" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2779" t="n">
+        <v>387.26</v>
+      </c>
+      <c r="F2779" t="n">
+        <v>7.307</v>
+      </c>
+      <c r="G2779" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2780" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2780" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="F2780" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="G2780" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr">
+        <is>
+          <t>N25</t>
+        </is>
+      </c>
+      <c r="D2781" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2781" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F2781" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G2781" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2782" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2782" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="F2782" t="n">
+        <v>4.507</v>
+      </c>
+      <c r="G2782" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2783" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2783" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="F2783" t="n">
+        <v>6.078</v>
+      </c>
+      <c r="G2783" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2784" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2784" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="F2784" t="n">
+        <v>6.078</v>
+      </c>
+      <c r="G2784" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2785" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2785" t="n">
+        <v>415.98</v>
+      </c>
+      <c r="F2785" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="G2785" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2786" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2786" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="F2786" t="n">
+        <v>7.157</v>
+      </c>
+      <c r="G2786" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2787" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2787" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="F2787" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G2787" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2788" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2788" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="F2788" t="n">
+        <v>7.506</v>
+      </c>
+      <c r="G2788" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2789" t="n">
+        <v>107</v>
+      </c>
+      <c r="E2789" t="n">
+        <v>812.24</v>
+      </c>
+      <c r="F2789" t="n">
+        <v>7.591</v>
+      </c>
+      <c r="G2789" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2790" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2790" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F2790" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="G2790" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2791" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2791" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="F2791" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G2791" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2792" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2792" t="n">
+        <v>282.18</v>
+      </c>
+      <c r="F2792" t="n">
+        <v>6.271</v>
+      </c>
+      <c r="G2792" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2793" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2793" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="F2793" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="G2793" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2794" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2794" t="n">
+        <v>259.48</v>
+      </c>
+      <c r="F2794" t="n">
+        <v>7.208</v>
+      </c>
+      <c r="G2794" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2795" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2795" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="F2795" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="G2795" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2796" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2796" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F2796" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="G2796" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2797" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2797" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="F2797" t="n">
+        <v>7.318</v>
+      </c>
+      <c r="G2797" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2798" t="n">
+        <v>121</v>
+      </c>
+      <c r="E2798" t="n">
+        <v>648.04</v>
+      </c>
+      <c r="F2798" t="n">
+        <v>5.356</v>
+      </c>
+      <c r="G2798" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2799" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2799" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="F2799" t="n">
+        <v>6.261</v>
+      </c>
+      <c r="G2799" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2800" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2800" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="F2800" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G2800" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2801" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2801" t="n">
+        <v>156.62</v>
+      </c>
+      <c r="F2801" t="n">
+        <v>6.526</v>
+      </c>
+      <c r="G2801" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2802" t="n">
+        <v>59</v>
+      </c>
+      <c r="E2802" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="F2802" t="n">
+        <v>6.387</v>
+      </c>
+      <c r="G2802" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2803" t="n">
+        <v>142</v>
+      </c>
+      <c r="E2803" t="n">
+        <v>1007.58</v>
+      </c>
+      <c r="F2803" t="n">
+        <v>7.096</v>
+      </c>
+      <c r="G2803" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2804" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2804" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F2804" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="G2804" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2804"/>
+  <dimension ref="A1:G2832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82368,6 +82368,874 @@
         </is>
       </c>
     </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2805" t="n">
+        <v>166</v>
+      </c>
+      <c r="E2805" t="n">
+        <v>984.6799999999999</v>
+      </c>
+      <c r="F2805" t="n">
+        <v>5.932</v>
+      </c>
+      <c r="G2805" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2806" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2806" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="F2806" t="n">
+        <v>7.369</v>
+      </c>
+      <c r="G2806" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2807" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2807" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F2807" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G2807" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2808" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2808" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="F2808" t="n">
+        <v>7.088</v>
+      </c>
+      <c r="G2808" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="C2809" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2809" t="n">
+        <v>64</v>
+      </c>
+      <c r="E2809" t="n">
+        <v>507.02</v>
+      </c>
+      <c r="F2809" t="n">
+        <v>7.922</v>
+      </c>
+      <c r="G2809" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B2810" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="C2810" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2810" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2810" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="F2810" t="n">
+        <v>6.877</v>
+      </c>
+      <c r="G2810" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="C2811" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2811" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2811" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="F2811" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="G2811" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B2812" t="inlineStr">
+        <is>
+          <t>5492</t>
+        </is>
+      </c>
+      <c r="C2812" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2812" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2812" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="F2812" t="n">
+        <v>7.913</v>
+      </c>
+      <c r="G2812" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="C2813" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2813" t="n">
+        <v>95</v>
+      </c>
+      <c r="E2813" t="n">
+        <v>577.8</v>
+      </c>
+      <c r="F2813" t="n">
+        <v>6.082</v>
+      </c>
+      <c r="G2813" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B2814" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="C2814" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2814" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2814" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="F2814" t="n">
+        <v>7.215</v>
+      </c>
+      <c r="G2814" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="C2815" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="D2815" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2815" t="n">
+        <v>308.94</v>
+      </c>
+      <c r="F2815" t="n">
+        <v>5.829</v>
+      </c>
+      <c r="G2815" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B2816" t="inlineStr">
+        <is>
+          <t>5492</t>
+        </is>
+      </c>
+      <c r="C2816" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2816" t="n">
+        <v>58</v>
+      </c>
+      <c r="E2816" t="n">
+        <v>430.48</v>
+      </c>
+      <c r="F2816" t="n">
+        <v>7.422</v>
+      </c>
+      <c r="G2816" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="C2817" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2817" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2817" t="n">
+        <v>189.52</v>
+      </c>
+      <c r="F2817" t="n">
+        <v>6.114</v>
+      </c>
+      <c r="G2817" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2818" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="C2818" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="D2818" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2818" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="F2818" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G2818" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="C2819" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2819" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2819" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="F2819" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="G2819" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2820" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="C2820" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2820" t="n">
+        <v>109</v>
+      </c>
+      <c r="E2820" t="n">
+        <v>747.9400000000001</v>
+      </c>
+      <c r="F2820" t="n">
+        <v>6.862</v>
+      </c>
+      <c r="G2820" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="C2821" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2821" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2821" t="n">
+        <v>136.32</v>
+      </c>
+      <c r="F2821" t="n">
+        <v>7.573</v>
+      </c>
+      <c r="G2821" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B2822" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C2822" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2822" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2822" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F2822" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G2822" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="C2823" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2823" t="n">
+        <v>77</v>
+      </c>
+      <c r="E2823" t="n">
+        <v>541.38</v>
+      </c>
+      <c r="F2823" t="n">
+        <v>7.031</v>
+      </c>
+      <c r="G2823" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B2824" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="C2824" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2824" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2824" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="F2824" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G2824" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="C2825" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2825" t="n">
+        <v>133</v>
+      </c>
+      <c r="E2825" t="n">
+        <v>885.34</v>
+      </c>
+      <c r="F2825" t="n">
+        <v>6.657</v>
+      </c>
+      <c r="G2825" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B2826" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="C2826" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2826" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2826" t="n">
+        <v>434.66</v>
+      </c>
+      <c r="F2826" t="n">
+        <v>9.055</v>
+      </c>
+      <c r="G2826" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="C2827" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2827" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2827" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="F2827" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="G2827" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B2828" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="C2828" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2828" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2828" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F2828" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G2828" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="C2829" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2829" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2829" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="F2829" t="n">
+        <v>8.327</v>
+      </c>
+      <c r="G2829" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B2830" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="C2830" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2830" t="n">
+        <v>121</v>
+      </c>
+      <c r="E2830" t="n">
+        <v>850.48</v>
+      </c>
+      <c r="F2830" t="n">
+        <v>7.029</v>
+      </c>
+      <c r="G2830" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="C2831" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D2831" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2831" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="F2831" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G2831" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B2832" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="C2832" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2832" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2832" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="F2832" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="G2832" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2832"/>
+  <dimension ref="A1:G2851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83236,6 +83236,595 @@
         </is>
       </c>
     </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="C2833" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2833" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2833" t="n">
+        <v>437.68</v>
+      </c>
+      <c r="F2833" t="n">
+        <v>7.059</v>
+      </c>
+      <c r="G2833" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2834" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="C2834" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2834" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2834" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F2834" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="G2834" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>5403</t>
+        </is>
+      </c>
+      <c r="C2835" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2835" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2835" t="n">
+        <v>422.8</v>
+      </c>
+      <c r="F2835" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="G2835" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2836" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="C2836" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2836" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2836" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2836" t="n">
+        <v>6.889</v>
+      </c>
+      <c r="G2836" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C2837" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2837" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2837" t="n">
+        <v>280.38</v>
+      </c>
+      <c r="F2837" t="n">
+        <v>7.788</v>
+      </c>
+      <c r="G2837" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2838" t="inlineStr">
+        <is>
+          <t>5207</t>
+        </is>
+      </c>
+      <c r="C2838" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2838" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2838" t="n">
+        <v>148</v>
+      </c>
+      <c r="F2838" t="n">
+        <v>7.048</v>
+      </c>
+      <c r="G2838" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C2839" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2839" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2839" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="F2839" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G2839" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2840" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="C2840" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2840" t="n">
+        <v>43</v>
+      </c>
+      <c r="E2840" t="n">
+        <v>311.62</v>
+      </c>
+      <c r="F2840" t="n">
+        <v>7.247</v>
+      </c>
+      <c r="G2840" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>5207</t>
+        </is>
+      </c>
+      <c r="C2841" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2841" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2841" t="n">
+        <v>156.28</v>
+      </c>
+      <c r="F2841" t="n">
+        <v>7.814</v>
+      </c>
+      <c r="G2841" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2842" t="inlineStr">
+        <is>
+          <t>5403</t>
+        </is>
+      </c>
+      <c r="C2842" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2842" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2842" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="F2842" t="n">
+        <v>6.973</v>
+      </c>
+      <c r="G2842" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>5449</t>
+        </is>
+      </c>
+      <c r="C2843" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2843" t="n">
+        <v>71</v>
+      </c>
+      <c r="E2843" t="n">
+        <v>423.14</v>
+      </c>
+      <c r="F2843" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G2843" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2844" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="C2844" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2844" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2844" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="F2844" t="n">
+        <v>5.952</v>
+      </c>
+      <c r="G2844" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="C2845" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2845" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2845" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="F2845" t="n">
+        <v>7.248</v>
+      </c>
+      <c r="G2845" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B2846" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="C2846" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2846" t="n">
+        <v>81</v>
+      </c>
+      <c r="E2846" t="n">
+        <v>549.1</v>
+      </c>
+      <c r="F2846" t="n">
+        <v>6.779</v>
+      </c>
+      <c r="G2846" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>5207</t>
+        </is>
+      </c>
+      <c r="C2847" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2847" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2847" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F2847" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G2847" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B2848" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="C2848" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2848" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2848" t="n">
+        <v>507.74</v>
+      </c>
+      <c r="F2848" t="n">
+        <v>6.681</v>
+      </c>
+      <c r="G2848" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="C2849" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2849" t="n">
+        <v>144</v>
+      </c>
+      <c r="E2849" t="n">
+        <v>753.6799999999999</v>
+      </c>
+      <c r="F2849" t="n">
+        <v>5.234</v>
+      </c>
+      <c r="G2849" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B2850" t="inlineStr">
+        <is>
+          <t>4118</t>
+        </is>
+      </c>
+      <c r="C2850" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2850" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2850" t="n">
+        <v>129.88</v>
+      </c>
+      <c r="F2850" t="n">
+        <v>5.904</v>
+      </c>
+      <c r="G2850" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C2851" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2851" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2851" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2851" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="G2851" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2851"/>
+  <dimension ref="A1:G2858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83825,6 +83825,223 @@
         </is>
       </c>
     </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B2852" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="C2852" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2852" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2852" t="n">
+        <v>170.96</v>
+      </c>
+      <c r="F2852" t="n">
+        <v>7.123</v>
+      </c>
+      <c r="G2852" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C2853" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2853" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2853" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="F2853" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G2853" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B2854" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C2854" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2854" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2854" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="F2854" t="n">
+        <v>7.133</v>
+      </c>
+      <c r="G2854" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="C2855" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2855" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2855" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="F2855" t="n">
+        <v>7.134</v>
+      </c>
+      <c r="G2855" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2856" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="C2856" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2856" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2856" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="F2856" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="G2856" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C2857" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2857" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2857" t="n">
+        <v>197.72</v>
+      </c>
+      <c r="F2857" t="n">
+        <v>8.238</v>
+      </c>
+      <c r="G2857" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2858" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="C2858" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2858" t="n">
+        <v>249</v>
+      </c>
+      <c r="E2858" t="n">
+        <v>1652.66</v>
+      </c>
+      <c r="F2858" t="n">
+        <v>6.637</v>
+      </c>
+      <c r="G2858" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2858"/>
+  <dimension ref="A1:G2880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84042,6 +84042,688 @@
         </is>
       </c>
     </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="C2859" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2859" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2859" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="F2859" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="G2859" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2860" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="C2860" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2860" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2860" t="n">
+        <v>661.52</v>
+      </c>
+      <c r="F2860" t="n">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="G2860" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="C2861" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2861" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2861" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="F2861" t="n">
+        <v>8.553000000000001</v>
+      </c>
+      <c r="G2861" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2862" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C2862" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2862" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2862" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F2862" t="n">
+        <v>5.894</v>
+      </c>
+      <c r="G2862" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="C2863" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2863" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2863" t="n">
+        <v>660.24</v>
+      </c>
+      <c r="F2863" t="n">
+        <v>8.465</v>
+      </c>
+      <c r="G2863" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2864" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C2864" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2864" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2864" t="n">
+        <v>163.54</v>
+      </c>
+      <c r="F2864" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G2864" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2865" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2865" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2865" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="F2865" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="G2865" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2866" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2866" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2866" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2866" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="F2866" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G2866" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C2867" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2867" t="n">
+        <v>112</v>
+      </c>
+      <c r="E2867" t="n">
+        <v>804.88</v>
+      </c>
+      <c r="F2867" t="n">
+        <v>7.186</v>
+      </c>
+      <c r="G2867" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C2868" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2868" t="n">
+        <v>51</v>
+      </c>
+      <c r="E2868" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="F2868" t="n">
+        <v>7.347</v>
+      </c>
+      <c r="G2868" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="C2869" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2869" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2869" t="n">
+        <v>205.35</v>
+      </c>
+      <c r="F2869" t="n">
+        <v>7.081</v>
+      </c>
+      <c r="G2869" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2870" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="C2870" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2870" t="n">
+        <v>52</v>
+      </c>
+      <c r="E2870" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="F2870" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="G2870" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="C2871" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2871" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2871" t="n">
+        <v>432.36</v>
+      </c>
+      <c r="F2871" t="n">
+        <v>5.543</v>
+      </c>
+      <c r="G2871" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B2872" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C2872" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2872" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2872" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F2872" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G2872" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="C2873" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2873" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2873" t="n">
+        <v>252.05</v>
+      </c>
+      <c r="F2873" t="n">
+        <v>7.413</v>
+      </c>
+      <c r="G2873" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2874" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="C2874" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2874" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2874" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="F2874" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="G2874" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
+      <c r="C2875" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2875" t="n">
+        <v>65</v>
+      </c>
+      <c r="E2875" t="n">
+        <v>511.77</v>
+      </c>
+      <c r="F2875" t="n">
+        <v>7.873</v>
+      </c>
+      <c r="G2875" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2876" t="inlineStr">
+        <is>
+          <t>5193</t>
+        </is>
+      </c>
+      <c r="C2876" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2876" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2876" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="F2876" t="n">
+        <v>5.687</v>
+      </c>
+      <c r="G2876" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+      <c r="C2877" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2877" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2877" t="n">
+        <v>108.51</v>
+      </c>
+      <c r="F2877" t="n">
+        <v>6.383</v>
+      </c>
+      <c r="G2877" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2878" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="C2878" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2878" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2878" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="F2878" t="n">
+        <v>7.253</v>
+      </c>
+      <c r="G2878" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>5624</t>
+        </is>
+      </c>
+      <c r="C2879" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2879" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2879" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="F2879" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G2879" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2880" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2880" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2880" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2880" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F2880" t="n">
+        <v>6.585</v>
+      </c>
+      <c r="G2880" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
